--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -36367,7 +36367,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-08-30 | 524 只</t>
+          <t>截至: 2026-08-31 | 524 只</t>
         </is>
       </c>
     </row>

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>136.98</v>
+        <v>136.38</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>1.4</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>81.39</v>
@@ -9014,26 +9014,28 @@
       <c r="R124" s="2" t="inlineStr"/>
       <c r="S124" s="2" t="inlineStr"/>
       <c r="T124" s="2" t="inlineStr"/>
-      <c r="U124" s="2" t="n">
-        <v>1</v>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="V124" s="2" t="inlineStr"/>
       <c r="W124" s="2" t="inlineStr"/>
       <c r="X124" s="2" t="inlineStr"/>
       <c r="Y124" s="2" t="n">
-        <v>20.06</v>
+        <v>19.95</v>
       </c>
       <c r="Z124" s="2" t="n">
-        <v>-2.47</v>
+        <v>-2.89</v>
       </c>
       <c r="AA124" s="2" t="n">
-        <v>-2.38</v>
+        <v>-2.81</v>
       </c>
       <c r="AB124" s="2" t="n">
-        <v>-1.78</v>
+        <v>-2.21</v>
       </c>
       <c r="AC124" s="2" t="n">
-        <v>-4.78</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="125">
@@ -11954,7 +11956,7 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>308.98</v>
+        <v>307.82</v>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
@@ -11965,10 +11967,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>106.81</v>
+        <v>105.79</v>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
@@ -11986,7 +11988,7 @@
       <c r="O167" s="2" t="inlineStr"/>
       <c r="P167" s="2" t="inlineStr"/>
       <c r="Q167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R167" s="2" t="inlineStr"/>
       <c r="S167" s="2" t="inlineStr"/>
@@ -11998,19 +12000,19 @@
       <c r="W167" s="2" t="inlineStr"/>
       <c r="X167" s="2" t="inlineStr"/>
       <c r="Y167" s="2" t="n">
-        <v>23.36</v>
+        <v>23.24</v>
       </c>
       <c r="Z167" s="2" t="n">
-        <v>8.58</v>
+        <v>8.17</v>
       </c>
       <c r="AA167" s="2" t="n">
-        <v>9.24</v>
+        <v>8.83</v>
       </c>
       <c r="AB167" s="2" t="n">
-        <v>3.73</v>
+        <v>3.32</v>
       </c>
       <c r="AC167" s="2" t="n">
-        <v>17.52</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="168">
@@ -19642,30 +19644,24 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>-3.16</v>
+        <v>2.53</v>
       </c>
       <c r="F279" s="2" t="n">
-        <v>-41.2</v>
+        <v>9.4</v>
       </c>
       <c r="G279" s="2" t="n">
-        <v>-19.42</v>
-      </c>
-      <c r="H279" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>34.95</v>
+      </c>
+      <c r="H279" s="2" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr"/>
       <c r="J279" s="2" t="inlineStr"/>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
-      <c r="M279" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M279" s="2" t="inlineStr"/>
       <c r="N279" s="2" t="inlineStr"/>
       <c r="O279" s="2" t="inlineStr"/>
       <c r="P279" s="2" t="inlineStr"/>
@@ -19680,25 +19676,23 @@
       <c r="U279" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V279" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="V279" s="2" t="inlineStr"/>
       <c r="W279" s="2" t="inlineStr"/>
       <c r="X279" s="2" t="inlineStr"/>
       <c r="Y279" s="2" t="n">
-        <v>-33.44</v>
+        <v>43.28</v>
       </c>
       <c r="Z279" s="2" t="n">
-        <v>-43.96</v>
+        <v>7.47</v>
       </c>
       <c r="AA279" s="2" t="n">
-        <v>-41.45</v>
+        <v>12.1</v>
       </c>
       <c r="AB279" s="2" t="n">
-        <v>-1.02</v>
+        <v>-3.19</v>
       </c>
       <c r="AC279" s="2" t="n">
-        <v>-2.37</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="280">

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -8574,7 +8574,7 @@
         <v>4.62</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>62.56</v>
@@ -8605,19 +8605,19 @@
       <c r="W118" s="2" t="inlineStr"/>
       <c r="X118" s="2" t="inlineStr"/>
       <c r="Y118" s="2" t="n">
-        <v>50.72</v>
+        <v>50.94</v>
       </c>
       <c r="Z118" s="2" t="n">
-        <v>13.46</v>
+        <v>13.23</v>
       </c>
       <c r="AA118" s="2" t="n">
-        <v>17.62</v>
+        <v>17.39</v>
       </c>
       <c r="AB118" s="2" t="n">
-        <v>-2.93</v>
+        <v>-3.24</v>
       </c>
       <c r="AC118" s="2" t="n">
-        <v>-1.27</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="119">
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>12.41</v>
@@ -10188,19 +10188,19 @@
       <c r="W141" s="2" t="inlineStr"/>
       <c r="X141" s="2" t="inlineStr"/>
       <c r="Y141" s="2" t="n">
-        <v>12.97</v>
+        <v>12.91</v>
       </c>
       <c r="Z141" s="2" t="n">
-        <v>-11.57</v>
+        <v>-11.81</v>
       </c>
       <c r="AA141" s="2" t="n">
-        <v>-8.32</v>
+        <v>-8.56</v>
       </c>
       <c r="AB141" s="2" t="n">
-        <v>-4.32</v>
+        <v>-4.55</v>
       </c>
       <c r="AC141" s="2" t="n">
-        <v>-5.79</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="142">
@@ -35455,7 +35455,7 @@
         <v>1.15</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G511" s="2" t="n">
         <v>10.19</v>
@@ -35480,19 +35480,19 @@
       <c r="W511" s="2" t="inlineStr"/>
       <c r="X511" s="2" t="inlineStr"/>
       <c r="Y511" s="2" t="n">
-        <v>16.58</v>
+        <v>16.98</v>
       </c>
       <c r="Z511" s="2" t="n">
-        <v>-5.96</v>
+        <v>-6.25</v>
       </c>
       <c r="AA511" s="2" t="n">
-        <v>-1.67</v>
+        <v>-1.97</v>
       </c>
       <c r="AB511" s="2" t="n">
-        <v>-2.79</v>
+        <v>-3.21</v>
       </c>
       <c r="AC511" s="2" t="n">
-        <v>-3.6</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="512">

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>158.635</v>
+        <v>158.64</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>-9</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-2.02</v>
+        <v>-2.01</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         <v>-11.01</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>-13.8</v>
+        <v>-13.79</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AC20" s="2" t="n">
         <v>-7.74</v>
@@ -2737,7 +2737,7 @@
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="n">
-        <v>79.06999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="Z32" s="2" t="n">
         <v>26.27</v>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>357.895</v>
+        <v>357.9</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>-10.21</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>-18.53</v>
+        <v>-18.52</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>-2.85</v>
@@ -5802,7 +5802,7 @@
         <v>-13.8</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-6.98</v>
+        <v>-7.04</v>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
@@ -7403,7 +7403,9 @@
       <c r="U100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="W100" s="2" t="inlineStr"/>
       <c r="X100" s="2" t="inlineStr"/>
       <c r="Y100" s="2" t="n">
@@ -13121,7 +13123,7 @@
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>150.995</v>
+        <v>151</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
@@ -13135,7 +13137,7 @@
         <v>10.5</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>104.53</v>
+        <v>104.55</v>
       </c>
       <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
@@ -13162,10 +13164,10 @@
         <v>27.31</v>
       </c>
       <c r="Z184" s="2" t="n">
-        <v>6.26</v>
+        <v>6.27</v>
       </c>
       <c r="AA184" s="2" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AB184" s="2" t="n">
         <v>3.38</v>
@@ -14026,7 +14028,7 @@
         <v>2.2</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>109.3</v>
+        <v>109.28</v>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
@@ -16638,7 +16640,7 @@
         <v>3.4</v>
       </c>
       <c r="G235" s="2" t="n">
-        <v>-4.81</v>
+        <v>-4.8</v>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
       <c r="I235" s="2" t="inlineStr"/>
@@ -17265,7 +17267,7 @@
         <v>-0.7</v>
       </c>
       <c r="G244" s="2" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="2" t="inlineStr"/>
@@ -21660,7 +21662,7 @@
       </c>
       <c r="X307" s="2" t="inlineStr"/>
       <c r="Y307" s="2" t="n">
-        <v>22.27</v>
+        <v>22.28</v>
       </c>
       <c r="Z307" s="2" t="n">
         <v>4.69</v>
@@ -21687,7 +21689,7 @@
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>227.835</v>
+        <v>227.84</v>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
@@ -28066,37 +28068,47 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>TPR US</t>
+          <t>TRGP US</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>122.14</v>
+        <v>290.05</v>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>0.23</v>
+        <v>5.68</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>-14.4</v>
+        <v>13.6</v>
       </c>
       <c r="G402" s="2" t="n">
-        <v>-9.859999999999999</v>
+        <v>38.96</v>
       </c>
       <c r="H402" s="2" t="inlineStr"/>
-      <c r="I402" s="2" t="inlineStr"/>
-      <c r="J402" s="2" t="inlineStr"/>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K402" s="2" t="inlineStr"/>
       <c r="L402" s="2" t="inlineStr"/>
-      <c r="M402" s="2" t="inlineStr"/>
+      <c r="M402" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N402" s="2" t="inlineStr"/>
       <c r="O402" s="2" t="inlineStr"/>
       <c r="P402" s="2" t="inlineStr"/>
@@ -28106,83 +28118,73 @@
       <c r="R402" s="2" t="inlineStr"/>
       <c r="S402" s="2" t="inlineStr"/>
       <c r="T402" s="2" t="inlineStr"/>
-      <c r="U402" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="V402" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="W402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V402" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W402" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X402" s="2" t="inlineStr"/>
       <c r="Y402" s="2" t="n">
-        <v>20.54</v>
+        <v>69.63</v>
       </c>
       <c r="Z402" s="2" t="n">
-        <v>-15.2</v>
+        <v>21.01</v>
       </c>
       <c r="AA402" s="2" t="n">
-        <v>-5.7</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB402" s="2" t="n">
-        <v>-2.09</v>
+        <v>-0.18</v>
       </c>
       <c r="AC402" s="2" t="n">
-        <v>-27.58</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>TRGP US</t>
+          <t>TRI US</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>290.05</v>
+        <v>105.68</v>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>5.68</v>
+        <v>-2.07</v>
       </c>
       <c r="F403" s="2" t="n">
-        <v>13.6</v>
+        <v>15.8</v>
       </c>
       <c r="G403" s="2" t="n">
-        <v>38.96</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="H403" s="2" t="inlineStr"/>
-      <c r="I403" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
-      <c r="J403" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I403" s="2" t="inlineStr"/>
+      <c r="J403" s="2" t="inlineStr"/>
       <c r="K403" s="2" t="inlineStr"/>
       <c r="L403" s="2" t="inlineStr"/>
-      <c r="M403" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M403" s="2" t="inlineStr"/>
       <c r="N403" s="2" t="inlineStr"/>
-      <c r="O403" s="2" t="inlineStr"/>
+      <c r="O403" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P403" s="2" t="inlineStr"/>
       <c r="Q403" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R403" s="2" t="inlineStr"/>
       <c r="S403" s="2" t="inlineStr"/>
@@ -28193,53 +28195,49 @@
       <c r="V403" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="W403" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="W403" s="2" t="inlineStr"/>
       <c r="X403" s="2" t="inlineStr"/>
       <c r="Y403" s="2" t="n">
-        <v>69.63</v>
+        <v>-33.69</v>
       </c>
       <c r="Z403" s="2" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="AA403" s="2" t="n">
-        <v>8.109999999999999</v>
-      </c>
+        <v>-13.05</v>
+      </c>
+      <c r="AA403" s="2" t="n"/>
       <c r="AB403" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.82</v>
       </c>
       <c r="AC403" s="2" t="n">
-        <v>10.96</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>TRI US</t>
+          <t>TRMB US</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>105.68</v>
+        <v>59.47</v>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>-2.07</v>
+        <v>-3.45</v>
       </c>
       <c r="F404" s="2" t="n">
-        <v>15.8</v>
+        <v>-1.4</v>
       </c>
       <c r="G404" s="2" t="n">
-        <v>89.18000000000001</v>
+        <v>106.71</v>
       </c>
       <c r="H404" s="2" t="inlineStr"/>
       <c r="I404" s="2" t="inlineStr"/>
@@ -28248,65 +28246,67 @@
       <c r="L404" s="2" t="inlineStr"/>
       <c r="M404" s="2" t="inlineStr"/>
       <c r="N404" s="2" t="inlineStr"/>
-      <c r="O404" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P404" s="2" t="inlineStr"/>
+      <c r="O404" s="2" t="inlineStr"/>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>+13/-13</t>
+        </is>
+      </c>
       <c r="Q404" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R404" s="2" t="inlineStr"/>
       <c r="S404" s="2" t="inlineStr"/>
       <c r="T404" s="2" t="inlineStr"/>
-      <c r="U404" s="2" t="n">
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V404" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W404" s="2" t="inlineStr"/>
       <c r="X404" s="2" t="inlineStr"/>
       <c r="Y404" s="2" t="n">
-        <v>-33.69</v>
+        <v>-37.57</v>
       </c>
       <c r="Z404" s="2" t="n">
-        <v>-13.05</v>
-      </c>
-      <c r="AA404" s="2" t="n"/>
+        <v>-20.74</v>
+      </c>
+      <c r="AA404" s="2" t="n">
+        <v>-29.04</v>
+      </c>
       <c r="AB404" s="2" t="n">
-        <v>0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="AC404" s="2" t="n">
-        <v>9.06</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>TRMB US</t>
+          <t>TRV US</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>59.47</v>
+        <v>369.35</v>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>-3.45</v>
+        <v>3.96</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>-1.4</v>
+        <v>15.2</v>
       </c>
       <c r="G405" s="2" t="n">
-        <v>106.71</v>
+        <v>75.8</v>
       </c>
       <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="2" t="inlineStr"/>
@@ -28316,66 +28316,64 @@
       <c r="M405" s="2" t="inlineStr"/>
       <c r="N405" s="2" t="inlineStr"/>
       <c r="O405" s="2" t="inlineStr"/>
-      <c r="P405" s="2" t="inlineStr">
-        <is>
-          <t>+13/-13</t>
-        </is>
-      </c>
+      <c r="P405" s="2" t="inlineStr"/>
       <c r="Q405" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R405" s="2" t="inlineStr"/>
       <c r="S405" s="2" t="inlineStr"/>
       <c r="T405" s="2" t="inlineStr"/>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="V405" s="2" t="inlineStr"/>
-      <c r="W405" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="W405" s="2" t="inlineStr"/>
       <c r="X405" s="2" t="inlineStr"/>
       <c r="Y405" s="2" t="n">
-        <v>-37.57</v>
+        <v>35.77</v>
       </c>
       <c r="Z405" s="2" t="n">
-        <v>-20.74</v>
+        <v>11.5</v>
       </c>
       <c r="AA405" s="2" t="n">
-        <v>-29.04</v>
+        <v>11.43</v>
       </c>
       <c r="AB405" s="2" t="n">
-        <v>-1.36</v>
+        <v>-0.58</v>
       </c>
       <c r="AC405" s="2" t="n">
-        <v>3.47</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>TRV US</t>
+          <t>TSCO US</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>369.35</v>
+        <v>34.99</v>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>3.96</v>
+        <v>-5.31</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>15.2</v>
+        <v>-7.7</v>
       </c>
       <c r="G406" s="2" t="n">
-        <v>75.8</v>
+        <v>104.9</v>
       </c>
       <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="2" t="inlineStr"/>
@@ -28387,48 +28385,46 @@
       <c r="O406" s="2" t="inlineStr"/>
       <c r="P406" s="2" t="inlineStr"/>
       <c r="Q406" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R406" s="2" t="inlineStr"/>
       <c r="S406" s="2" t="inlineStr"/>
       <c r="T406" s="2" t="inlineStr"/>
-      <c r="U406" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="U406" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V406" s="2" t="inlineStr"/>
       <c r="W406" s="2" t="inlineStr"/>
       <c r="X406" s="2" t="inlineStr"/>
       <c r="Y406" s="2" t="n">
-        <v>35.77</v>
+        <v>-60.15</v>
       </c>
       <c r="Z406" s="2" t="n">
-        <v>11.5</v>
+        <v>-28.45</v>
       </c>
       <c r="AA406" s="2" t="n">
-        <v>11.43</v>
+        <v>-19.22</v>
       </c>
       <c r="AB406" s="2" t="n">
-        <v>-0.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC406" s="2" t="n">
-        <v>-5.33</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>TSCO US</t>
+          <t>TSLA US</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>34.99</v>
+        <v>354.08</v>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
@@ -28436,13 +28432,13 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>-5.31</v>
+        <v>-2.98</v>
       </c>
       <c r="F407" s="2" t="n">
-        <v>-7.7</v>
+        <v>-8</v>
       </c>
       <c r="G407" s="2" t="n">
-        <v>104.9</v>
+        <v>21.62</v>
       </c>
       <c r="H407" s="2" t="inlineStr"/>
       <c r="I407" s="2" t="inlineStr"/>
@@ -28460,61 +28456,67 @@
       <c r="S407" s="2" t="inlineStr"/>
       <c r="T407" s="2" t="inlineStr"/>
       <c r="U407" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V407" s="2" t="inlineStr"/>
       <c r="W407" s="2" t="inlineStr"/>
       <c r="X407" s="2" t="inlineStr"/>
       <c r="Y407" s="2" t="n">
-        <v>-60.15</v>
+        <v>-17.77</v>
       </c>
       <c r="Z407" s="2" t="n">
-        <v>-28.45</v>
+        <v>-20.6</v>
       </c>
       <c r="AA407" s="2" t="n">
-        <v>-19.22</v>
+        <v>-11.05</v>
       </c>
       <c r="AB407" s="2" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AC407" s="2" t="n">
-        <v>5.58</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>TSLA US</t>
+          <t>TSN US</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>354.08</v>
+        <v>51.42</v>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>-2.98</v>
+        <v>-0.68</v>
       </c>
       <c r="F408" s="2" t="n">
-        <v>-8</v>
+        <v>-14.6</v>
       </c>
       <c r="G408" s="2" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="H408" s="2" t="inlineStr"/>
+        <v>7.15</v>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr"/>
       <c r="K408" s="2" t="inlineStr"/>
       <c r="L408" s="2" t="inlineStr"/>
-      <c r="M408" s="2" t="inlineStr"/>
+      <c r="M408" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N408" s="2" t="inlineStr"/>
       <c r="O408" s="2" t="inlineStr"/>
       <c r="P408" s="2" t="inlineStr"/>
@@ -28524,41 +28526,39 @@
       <c r="R408" s="2" t="inlineStr"/>
       <c r="S408" s="2" t="inlineStr"/>
       <c r="T408" s="2" t="inlineStr"/>
-      <c r="U408" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U408" s="2" t="inlineStr"/>
       <c r="V408" s="2" t="inlineStr"/>
       <c r="W408" s="2" t="inlineStr"/>
       <c r="X408" s="2" t="inlineStr"/>
       <c r="Y408" s="2" t="n">
-        <v>-17.77</v>
+        <v>3.03</v>
       </c>
       <c r="Z408" s="2" t="n">
-        <v>-20.6</v>
+        <v>-18.88</v>
       </c>
       <c r="AA408" s="2" t="n">
-        <v>-11.05</v>
+        <v>-14.36</v>
       </c>
       <c r="AB408" s="2" t="n">
-        <v>1.26</v>
+        <v>-5.25</v>
       </c>
       <c r="AC408" s="2" t="n">
-        <v>6.78</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>TSN US</t>
+          <t>TT US</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>51.42</v>
+        <v>447.9</v>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
@@ -28566,26 +28566,20 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>-0.68</v>
+        <v>2.06</v>
       </c>
       <c r="F409" s="2" t="n">
-        <v>-14.6</v>
+        <v>-2.3</v>
       </c>
       <c r="G409" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H409" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>13.22</v>
+      </c>
+      <c r="H409" s="2" t="inlineStr"/>
       <c r="I409" s="2" t="inlineStr"/>
       <c r="J409" s="2" t="inlineStr"/>
       <c r="K409" s="2" t="inlineStr"/>
       <c r="L409" s="2" t="inlineStr"/>
-      <c r="M409" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M409" s="2" t="inlineStr"/>
       <c r="N409" s="2" t="inlineStr"/>
       <c r="O409" s="2" t="inlineStr"/>
       <c r="P409" s="2" t="inlineStr"/>
@@ -28595,60 +28589,76 @@
       <c r="R409" s="2" t="inlineStr"/>
       <c r="S409" s="2" t="inlineStr"/>
       <c r="T409" s="2" t="inlineStr"/>
-      <c r="U409" s="2" t="inlineStr"/>
-      <c r="V409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V409" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="W409" s="2" t="inlineStr"/>
       <c r="X409" s="2" t="inlineStr"/>
       <c r="Y409" s="2" t="n">
-        <v>3.03</v>
+        <v>8.35</v>
       </c>
       <c r="Z409" s="2" t="n">
-        <v>-18.88</v>
+        <v>-6.33</v>
       </c>
       <c r="AA409" s="2" t="n">
-        <v>-14.36</v>
+        <v>-2.72</v>
       </c>
       <c r="AB409" s="2" t="n">
-        <v>-5.25</v>
+        <v>0.09</v>
       </c>
       <c r="AC409" s="2" t="n">
-        <v>-8.109999999999999</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>TT US</t>
+          <t>TTD US</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Trade Desk (The)</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>447.9</v>
+        <v>14.43</v>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>2.06</v>
+        <v>-12.35</v>
       </c>
       <c r="F410" s="2" t="n">
-        <v>-2.3</v>
+        <v>-31</v>
       </c>
       <c r="G410" s="2" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="H410" s="2" t="inlineStr"/>
-      <c r="I410" s="2" t="inlineStr"/>
+        <v>4.73</v>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="J410" s="2" t="inlineStr"/>
       <c r="K410" s="2" t="inlineStr"/>
       <c r="L410" s="2" t="inlineStr"/>
-      <c r="M410" s="2" t="inlineStr"/>
+      <c r="M410" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N410" s="2" t="inlineStr"/>
       <c r="O410" s="2" t="inlineStr"/>
       <c r="P410" s="2" t="inlineStr"/>
@@ -28658,136 +28668,126 @@
       <c r="R410" s="2" t="inlineStr"/>
       <c r="S410" s="2" t="inlineStr"/>
       <c r="T410" s="2" t="inlineStr"/>
-      <c r="U410" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V410" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U410" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="V410" s="2" t="inlineStr"/>
       <c r="W410" s="2" t="inlineStr"/>
       <c r="X410" s="2" t="inlineStr"/>
       <c r="Y410" s="2" t="n">
-        <v>8.35</v>
+        <v>-142.86</v>
       </c>
       <c r="Z410" s="2" t="n">
-        <v>-6.33</v>
+        <v>-56.73</v>
       </c>
       <c r="AA410" s="2" t="n">
-        <v>-2.72</v>
+        <v>-50.84</v>
       </c>
       <c r="AB410" s="2" t="n">
-        <v>0.09</v>
+        <v>3.72</v>
       </c>
       <c r="AC410" s="2" t="n">
-        <v>-5.73</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TTD US</t>
+          <t>TTWO US</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>14.43</v>
+        <v>214.69</v>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-12.35</v>
+        <v>-0.66</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>-31</v>
+        <v>-3.3</v>
       </c>
       <c r="G411" s="2" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="H411" s="2" t="inlineStr"/>
+      <c r="I411" s="2" t="inlineStr"/>
       <c r="J411" s="2" t="inlineStr"/>
       <c r="K411" s="2" t="inlineStr"/>
       <c r="L411" s="2" t="inlineStr"/>
-      <c r="M411" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M411" s="2" t="inlineStr"/>
       <c r="N411" s="2" t="inlineStr"/>
       <c r="O411" s="2" t="inlineStr"/>
-      <c r="P411" s="2" t="inlineStr"/>
+      <c r="P411" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q411" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R411" s="2" t="inlineStr"/>
       <c r="S411" s="2" t="inlineStr"/>
       <c r="T411" s="2" t="inlineStr"/>
       <c r="U411" s="2" t="inlineStr">
         <is>
-          <t>预-1</t>
+          <t>预1</t>
         </is>
       </c>
       <c r="V411" s="2" t="inlineStr"/>
       <c r="W411" s="2" t="inlineStr"/>
       <c r="X411" s="2" t="inlineStr"/>
       <c r="Y411" s="2" t="n">
-        <v>-142.86</v>
+        <v>-12.05</v>
       </c>
       <c r="Z411" s="2" t="n">
-        <v>-56.73</v>
+        <v>-15.95</v>
       </c>
       <c r="AA411" s="2" t="n">
-        <v>-50.84</v>
+        <v>-6.35</v>
       </c>
       <c r="AB411" s="2" t="n">
-        <v>3.72</v>
+        <v>-7.71</v>
       </c>
       <c r="AC411" s="2" t="n">
-        <v>6.65</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TTWO US</t>
+          <t>TXN US</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>214.69</v>
+        <v>258.44</v>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>-0.66</v>
+        <v>4.09</v>
       </c>
       <c r="F412" s="2" t="n">
-        <v>-3.3</v>
+        <v>0.5</v>
       </c>
       <c r="G412" s="2" t="n">
-        <v>0.37</v>
+        <v>-4.38</v>
       </c>
       <c r="H412" s="2" t="inlineStr"/>
       <c r="I412" s="2" t="inlineStr"/>
@@ -28797,66 +28797,66 @@
       <c r="M412" s="2" t="inlineStr"/>
       <c r="N412" s="2" t="inlineStr"/>
       <c r="O412" s="2" t="inlineStr"/>
-      <c r="P412" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P412" s="2" t="inlineStr"/>
       <c r="Q412" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R412" s="2" t="inlineStr"/>
       <c r="S412" s="2" t="inlineStr"/>
       <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr">
+      <c r="U412" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V412" s="2" t="inlineStr">
         <is>
           <t>预1</t>
         </is>
       </c>
-      <c r="V412" s="2" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
       <c r="X412" s="2" t="inlineStr"/>
       <c r="Y412" s="2" t="n">
-        <v>-12.05</v>
+        <v>54.79</v>
       </c>
       <c r="Z412" s="2" t="n">
-        <v>-15.95</v>
+        <v>6.46</v>
       </c>
       <c r="AA412" s="2" t="n">
-        <v>-6.35</v>
+        <v>-2.52</v>
       </c>
       <c r="AB412" s="2" t="n">
-        <v>-7.71</v>
+        <v>-0.41</v>
       </c>
       <c r="AC412" s="2" t="n">
-        <v>-10.7</v>
+        <v>-12.22</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TXN US</t>
+          <t>TXT US</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>258.44</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>4.09</v>
+        <v>-1.15</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>0.5</v>
+        <v>-12.8</v>
       </c>
       <c r="G413" s="2" t="n">
-        <v>-4.38</v>
+        <v>-9.73</v>
       </c>
       <c r="H413" s="2" t="inlineStr"/>
       <c r="I413" s="2" t="inlineStr"/>
@@ -28866,7 +28866,9 @@
       <c r="M413" s="2" t="inlineStr"/>
       <c r="N413" s="2" t="inlineStr"/>
       <c r="O413" s="2" t="inlineStr"/>
-      <c r="P413" s="2" t="inlineStr"/>
+      <c r="P413" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q413" s="2" t="n">
         <v>0</v>
       </c>
@@ -28876,56 +28878,52 @@
       <c r="U413" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V413" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="V413" s="2" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>
       <c r="X413" s="2" t="inlineStr"/>
       <c r="Y413" s="2" t="n">
-        <v>54.79</v>
+        <v>-2.58</v>
       </c>
       <c r="Z413" s="2" t="n">
-        <v>6.46</v>
+        <v>-18.51</v>
       </c>
       <c r="AA413" s="2" t="n">
-        <v>-2.52</v>
+        <v>-15.34</v>
       </c>
       <c r="AB413" s="2" t="n">
-        <v>-0.41</v>
+        <v>-3.89</v>
       </c>
       <c r="AC413" s="2" t="n">
-        <v>-12.22</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TXT US</t>
+          <t>TYL US</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>79.06999999999999</v>
+        <v>364.03</v>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-1.15</v>
+        <v>-3.32</v>
       </c>
       <c r="F414" s="2" t="n">
-        <v>-12.8</v>
+        <v>11.4</v>
       </c>
       <c r="G414" s="2" t="n">
-        <v>-9.73</v>
+        <v>108.82</v>
       </c>
       <c r="H414" s="2" t="inlineStr"/>
       <c r="I414" s="2" t="inlineStr"/>
@@ -28936,7 +28934,7 @@
       <c r="N414" s="2" t="inlineStr"/>
       <c r="O414" s="2" t="inlineStr"/>
       <c r="P414" s="2" t="n">
-        <v>9</v>
+        <v>-9</v>
       </c>
       <c r="Q414" s="2" t="n">
         <v>0</v>
@@ -28945,54 +28943,58 @@
       <c r="S414" s="2" t="inlineStr"/>
       <c r="T414" s="2" t="inlineStr"/>
       <c r="U414" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V414" s="2" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="V414" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W414" s="2" t="inlineStr"/>
       <c r="X414" s="2" t="inlineStr"/>
       <c r="Y414" s="2" t="n">
-        <v>-2.58</v>
+        <v>-33.73</v>
       </c>
       <c r="Z414" s="2" t="n">
-        <v>-18.51</v>
+        <v>-15.25</v>
       </c>
       <c r="AA414" s="2" t="n">
-        <v>-15.34</v>
+        <v>-24.11</v>
       </c>
       <c r="AB414" s="2" t="n">
-        <v>-3.89</v>
+        <v>-2.16</v>
       </c>
       <c r="AC414" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>TYL US</t>
+          <t>UAL US</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>364.03</v>
+        <v>111.38</v>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>-3.32</v>
+        <v>0.57</v>
       </c>
       <c r="F415" s="2" t="n">
-        <v>11.4</v>
+        <v>2.7</v>
       </c>
       <c r="G415" s="2" t="n">
-        <v>108.82</v>
+        <v>-8.82</v>
       </c>
       <c r="H415" s="2" t="inlineStr"/>
       <c r="I415" s="2" t="inlineStr"/>
@@ -29003,7 +29005,7 @@
       <c r="N415" s="2" t="inlineStr"/>
       <c r="O415" s="2" t="inlineStr"/>
       <c r="P415" s="2" t="n">
-        <v>-9</v>
+        <v>13</v>
       </c>
       <c r="Q415" s="2" t="n">
         <v>0</v>
@@ -29012,58 +29014,58 @@
       <c r="S415" s="2" t="inlineStr"/>
       <c r="T415" s="2" t="inlineStr"/>
       <c r="U415" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V415" s="2" t="inlineStr">
         <is>
-          <t>预-1</t>
+          <t>预1</t>
         </is>
       </c>
       <c r="W415" s="2" t="inlineStr"/>
       <c r="X415" s="2" t="inlineStr"/>
       <c r="Y415" s="2" t="n">
-        <v>-33.73</v>
+        <v>15.4</v>
       </c>
       <c r="Z415" s="2" t="n">
-        <v>-15.25</v>
+        <v>-4.36</v>
       </c>
       <c r="AA415" s="2" t="n">
-        <v>-24.11</v>
+        <v>-0.76</v>
       </c>
       <c r="AB415" s="2" t="n">
-        <v>-2.16</v>
+        <v>0.86</v>
       </c>
       <c r="AC415" s="2" t="n">
-        <v>16.54</v>
+        <v>-14.73</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>UAL US</t>
+          <t>UHS US</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>111.38</v>
+        <v>169.65</v>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.57</v>
+        <v>-2.52</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>2.7</v>
+        <v>-2.7</v>
       </c>
       <c r="G416" s="2" t="n">
-        <v>-8.82</v>
+        <v>111.95</v>
       </c>
       <c r="H416" s="2" t="inlineStr"/>
       <c r="I416" s="2" t="inlineStr"/>
@@ -29072,69 +29074,67 @@
       <c r="L416" s="2" t="inlineStr"/>
       <c r="M416" s="2" t="inlineStr"/>
       <c r="N416" s="2" t="inlineStr"/>
-      <c r="O416" s="2" t="inlineStr"/>
-      <c r="P416" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="O416" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P416" s="2" t="inlineStr"/>
       <c r="Q416" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R416" s="2" t="inlineStr"/>
       <c r="S416" s="2" t="inlineStr"/>
       <c r="T416" s="2" t="inlineStr"/>
-      <c r="U416" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V416" s="2" t="inlineStr">
+      <c r="U416" s="2" t="inlineStr">
         <is>
           <t>预1</t>
         </is>
       </c>
+      <c r="V416" s="2" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>
       <c r="X416" s="2" t="inlineStr"/>
       <c r="Y416" s="2" t="n">
-        <v>15.4</v>
+        <v>-38.91</v>
       </c>
       <c r="Z416" s="2" t="n">
-        <v>-4.36</v>
+        <v>-18.96</v>
       </c>
       <c r="AA416" s="2" t="n">
-        <v>-0.76</v>
+        <v>-21.27</v>
       </c>
       <c r="AB416" s="2" t="n">
-        <v>0.86</v>
+        <v>-0.58</v>
       </c>
       <c r="AC416" s="2" t="n">
-        <v>-14.73</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>UHS US</t>
+          <t>ULTA US</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>169.65</v>
+        <v>564.12</v>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>-2.52</v>
+        <v>-2.99</v>
       </c>
       <c r="F417" s="2" t="n">
-        <v>-2.7</v>
+        <v>4.5</v>
       </c>
       <c r="G417" s="2" t="n">
-        <v>111.95</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H417" s="2" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr"/>
@@ -29143,67 +29143,65 @@
       <c r="L417" s="2" t="inlineStr"/>
       <c r="M417" s="2" t="inlineStr"/>
       <c r="N417" s="2" t="inlineStr"/>
-      <c r="O417" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P417" s="2" t="inlineStr"/>
+      <c r="O417" s="2" t="inlineStr"/>
+      <c r="P417" s="2" t="n">
+        <v>-13</v>
+      </c>
       <c r="Q417" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R417" s="2" t="inlineStr"/>
       <c r="S417" s="2" t="inlineStr"/>
       <c r="T417" s="2" t="inlineStr"/>
-      <c r="U417" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="V417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W417" s="2" t="inlineStr"/>
       <c r="X417" s="2" t="inlineStr"/>
       <c r="Y417" s="2" t="n">
-        <v>-38.91</v>
+        <v>5.84</v>
       </c>
       <c r="Z417" s="2" t="n">
-        <v>-18.96</v>
+        <v>-6.95</v>
       </c>
       <c r="AA417" s="2" t="n">
-        <v>-21.27</v>
+        <v>4.21</v>
       </c>
       <c r="AB417" s="2" t="n">
-        <v>-0.58</v>
+        <v>7.81</v>
       </c>
       <c r="AC417" s="2" t="n">
-        <v>-0.04</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>ULTA US</t>
+          <t>UNH US</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>564.12</v>
+        <v>397.14</v>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>-2.99</v>
+        <v>2.65</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>4.5</v>
+        <v>11.1</v>
       </c>
       <c r="G418" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>-13.85</v>
       </c>
       <c r="H418" s="2" t="inlineStr"/>
       <c r="I418" s="2" t="inlineStr"/>
@@ -29213,50 +29211,52 @@
       <c r="M418" s="2" t="inlineStr"/>
       <c r="N418" s="2" t="inlineStr"/>
       <c r="O418" s="2" t="inlineStr"/>
-      <c r="P418" s="2" t="n">
-        <v>-13</v>
-      </c>
+      <c r="P418" s="2" t="inlineStr"/>
       <c r="Q418" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R418" s="2" t="inlineStr"/>
       <c r="S418" s="2" t="inlineStr"/>
       <c r="T418" s="2" t="inlineStr"/>
-      <c r="U418" s="2" t="inlineStr"/>
-      <c r="V418" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W418" s="2" t="inlineStr"/>
+      <c r="U418" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X418" s="2" t="inlineStr"/>
       <c r="Y418" s="2" t="n">
-        <v>5.84</v>
+        <v>28.06</v>
       </c>
       <c r="Z418" s="2" t="n">
-        <v>-6.95</v>
+        <v>4.82</v>
       </c>
       <c r="AA418" s="2" t="n">
-        <v>4.21</v>
+        <v>1.17</v>
       </c>
       <c r="AB418" s="2" t="n">
-        <v>7.81</v>
+        <v>0.79</v>
       </c>
       <c r="AC418" s="2" t="n">
-        <v>1.38</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>UNH US</t>
+          <t>UNP US</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>397.14</v>
+        <v>289.62</v>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
@@ -29264,153 +29264,153 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>2.65</v>
+        <v>3.71</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>11.1</v>
+        <v>8.1</v>
       </c>
       <c r="G419" s="2" t="n">
-        <v>-13.85</v>
+        <v>81.27</v>
       </c>
       <c r="H419" s="2" t="inlineStr"/>
       <c r="I419" s="2" t="inlineStr"/>
-      <c r="J419" s="2" t="inlineStr"/>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K419" s="2" t="inlineStr"/>
       <c r="L419" s="2" t="inlineStr"/>
-      <c r="M419" s="2" t="inlineStr"/>
+      <c r="M419" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N419" s="2" t="inlineStr"/>
       <c r="O419" s="2" t="inlineStr"/>
-      <c r="P419" s="2" t="inlineStr"/>
+      <c r="P419" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q419" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R419" s="2" t="inlineStr"/>
       <c r="S419" s="2" t="inlineStr"/>
       <c r="T419" s="2" t="inlineStr"/>
-      <c r="U419" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U419" s="2" t="inlineStr"/>
       <c r="V419" s="2" t="inlineStr"/>
-      <c r="W419" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="W419" s="2" t="inlineStr"/>
       <c r="X419" s="2" t="inlineStr"/>
       <c r="Y419" s="2" t="n">
-        <v>28.06</v>
+        <v>37.48</v>
       </c>
       <c r="Z419" s="2" t="n">
-        <v>4.82</v>
+        <v>6.1</v>
       </c>
       <c r="AA419" s="2" t="n">
-        <v>1.17</v>
+        <v>10.24</v>
       </c>
       <c r="AB419" s="2" t="n">
-        <v>0.79</v>
+        <v>-6.37</v>
       </c>
       <c r="AC419" s="2" t="n">
-        <v>-3.38</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>UNP US</t>
+          <t>UPS US</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>289.62</v>
+        <v>102.29</v>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>3.71</v>
+        <v>0.22</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>8.1</v>
+        <v>-1.4</v>
       </c>
       <c r="G420" s="2" t="n">
-        <v>81.27</v>
+        <v>-14.23</v>
       </c>
       <c r="H420" s="2" t="inlineStr"/>
       <c r="I420" s="2" t="inlineStr"/>
-      <c r="J420" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J420" s="2" t="inlineStr"/>
       <c r="K420" s="2" t="inlineStr"/>
       <c r="L420" s="2" t="inlineStr"/>
-      <c r="M420" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M420" s="2" t="inlineStr"/>
       <c r="N420" s="2" t="inlineStr"/>
       <c r="O420" s="2" t="inlineStr"/>
-      <c r="P420" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P420" s="2" t="inlineStr"/>
       <c r="Q420" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R420" s="2" t="inlineStr"/>
       <c r="S420" s="2" t="inlineStr"/>
       <c r="T420" s="2" t="inlineStr"/>
       <c r="U420" s="2" t="inlineStr"/>
-      <c r="V420" s="2" t="inlineStr"/>
-      <c r="W420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="W420" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X420" s="2" t="inlineStr"/>
       <c r="Y420" s="2" t="n">
-        <v>37.48</v>
+        <v>16.95</v>
       </c>
       <c r="Z420" s="2" t="n">
-        <v>6.1</v>
+        <v>-4.52</v>
       </c>
       <c r="AA420" s="2" t="n">
-        <v>10.24</v>
+        <v>-0.73</v>
       </c>
       <c r="AB420" s="2" t="n">
-        <v>-6.37</v>
+        <v>-3.06</v>
       </c>
       <c r="AC420" s="2" t="n">
-        <v>-1.46</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>UPS US</t>
+          <t>URI US</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>United Rentals</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>102.29</v>
+        <v>1009.86</v>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.22</v>
+        <v>2.6</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>-1.4</v>
+        <v>6</v>
       </c>
       <c r="G421" s="2" t="n">
-        <v>-14.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H421" s="2" t="inlineStr"/>
       <c r="I421" s="2" t="inlineStr"/>
@@ -29420,52 +29420,50 @@
       <c r="M421" s="2" t="inlineStr"/>
       <c r="N421" s="2" t="inlineStr"/>
       <c r="O421" s="2" t="inlineStr"/>
-      <c r="P421" s="2" t="inlineStr"/>
+      <c r="P421" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q421" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R421" s="2" t="inlineStr"/>
       <c r="S421" s="2" t="inlineStr"/>
       <c r="T421" s="2" t="inlineStr"/>
-      <c r="U421" s="2" t="inlineStr"/>
-      <c r="V421" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="W421" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="U421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr"/>
       <c r="X421" s="2" t="inlineStr"/>
       <c r="Y421" s="2" t="n">
-        <v>16.95</v>
+        <v>23.71</v>
       </c>
       <c r="Z421" s="2" t="n">
-        <v>-4.52</v>
+        <v>0.06</v>
       </c>
       <c r="AA421" s="2" t="n">
-        <v>-0.73</v>
+        <v>3.75</v>
       </c>
       <c r="AB421" s="2" t="n">
-        <v>-3.06</v>
+        <v>-1.86</v>
       </c>
       <c r="AC421" s="2" t="n">
-        <v>-0.49</v>
+        <v>-14.23</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>URI US</t>
+          <t>USB US</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>United Rentals</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>1009.86</v>
+        <v>63.37</v>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
@@ -29473,13 +29471,13 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="G422" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="H422" s="2" t="inlineStr"/>
       <c r="I422" s="2" t="inlineStr"/>
@@ -29489,9 +29487,7 @@
       <c r="M422" s="2" t="inlineStr"/>
       <c r="N422" s="2" t="inlineStr"/>
       <c r="O422" s="2" t="inlineStr"/>
-      <c r="P422" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P422" s="2" t="inlineStr"/>
       <c r="Q422" s="2" t="n">
         <v>0</v>
       </c>
@@ -29505,34 +29501,34 @@
       <c r="W422" s="2" t="inlineStr"/>
       <c r="X422" s="2" t="inlineStr"/>
       <c r="Y422" s="2" t="n">
-        <v>23.71</v>
+        <v>39.1</v>
       </c>
       <c r="Z422" s="2" t="n">
-        <v>0.06</v>
+        <v>7.31</v>
       </c>
       <c r="AA422" s="2" t="n">
-        <v>3.75</v>
+        <v>7.21</v>
       </c>
       <c r="AB422" s="2" t="n">
-        <v>-1.86</v>
+        <v>1.19</v>
       </c>
       <c r="AC422" s="2" t="n">
-        <v>-14.23</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>USB US</t>
+          <t>V US</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>63.37</v>
+        <v>375.07</v>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
@@ -29540,64 +29536,74 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>10.2</v>
+        <v>12.9</v>
       </c>
       <c r="G423" s="2" t="n">
-        <v>98.41</v>
-      </c>
-      <c r="H423" s="2" t="inlineStr"/>
+        <v>95.8</v>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr"/>
       <c r="K423" s="2" t="inlineStr"/>
       <c r="L423" s="2" t="inlineStr"/>
-      <c r="M423" s="2" t="inlineStr"/>
+      <c r="M423" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N423" s="2" t="inlineStr"/>
-      <c r="O423" s="2" t="inlineStr"/>
+      <c r="O423" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P423" s="2" t="inlineStr"/>
       <c r="Q423" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R423" s="2" t="inlineStr"/>
       <c r="S423" s="2" t="inlineStr"/>
       <c r="T423" s="2" t="inlineStr"/>
-      <c r="U423" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V423" s="2" t="inlineStr"/>
-      <c r="W423" s="2" t="inlineStr"/>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W423" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X423" s="2" t="inlineStr"/>
       <c r="Y423" s="2" t="n">
-        <v>39.1</v>
+        <v>17.65</v>
       </c>
       <c r="Z423" s="2" t="n">
-        <v>7.31</v>
+        <v>2.37</v>
       </c>
       <c r="AA423" s="2" t="n">
-        <v>7.21</v>
+        <v>2.52</v>
       </c>
       <c r="AB423" s="2" t="n">
-        <v>1.19</v>
+        <v>-1.67</v>
       </c>
       <c r="AC423" s="2" t="n">
-        <v>-1.75</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>V US</t>
+          <t>VEEV US</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>375.07</v>
+        <v>275.09</v>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
@@ -29605,26 +29611,20 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>1.56</v>
+        <v>2.42</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>12.9</v>
+        <v>46.3</v>
       </c>
       <c r="G424" s="2" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="H424" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+        <v>104.52</v>
+      </c>
+      <c r="H424" s="2" t="inlineStr"/>
       <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr"/>
       <c r="K424" s="2" t="inlineStr"/>
       <c r="L424" s="2" t="inlineStr"/>
-      <c r="M424" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M424" s="2" t="inlineStr"/>
       <c r="N424" s="2" t="inlineStr"/>
       <c r="O424" s="2" t="n">
         <v>-9</v>
@@ -29636,57 +29636,59 @@
       <c r="R424" s="2" t="inlineStr"/>
       <c r="S424" s="2" t="inlineStr"/>
       <c r="T424" s="2" t="inlineStr"/>
-      <c r="U424" s="2" t="inlineStr"/>
-      <c r="V424" s="2" t="n">
+      <c r="U424" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="W424" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="V424" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="W424" s="2" t="inlineStr"/>
       <c r="X424" s="2" t="inlineStr"/>
       <c r="Y424" s="2" t="n">
-        <v>17.65</v>
+        <v>-6.93</v>
       </c>
       <c r="Z424" s="2" t="n">
-        <v>2.37</v>
+        <v>14.96</v>
       </c>
       <c r="AA424" s="2" t="n">
-        <v>2.52</v>
+        <v>11.42</v>
       </c>
       <c r="AB424" s="2" t="n">
-        <v>-1.67</v>
+        <v>-0.38</v>
       </c>
       <c r="AC424" s="2" t="n">
-        <v>4.92</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>VEEV US</t>
+          <t>VICI US</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>275.09</v>
+        <v>25.42</v>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>2.42</v>
+        <v>-0.6</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>46.3</v>
+        <v>-7</v>
       </c>
       <c r="G425" s="2" t="n">
-        <v>104.52</v>
+        <v>0.63</v>
       </c>
       <c r="H425" s="2" t="inlineStr"/>
       <c r="I425" s="2" t="inlineStr"/>
@@ -29695,81 +29697,81 @@
       <c r="L425" s="2" t="inlineStr"/>
       <c r="M425" s="2" t="inlineStr"/>
       <c r="N425" s="2" t="inlineStr"/>
-      <c r="O425" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P425" s="2" t="inlineStr"/>
+      <c r="O425" s="2" t="inlineStr"/>
+      <c r="P425" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q425" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R425" s="2" t="inlineStr"/>
       <c r="S425" s="2" t="inlineStr"/>
       <c r="T425" s="2" t="inlineStr"/>
-      <c r="U425" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V425" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
       <c r="W425" s="2" t="inlineStr"/>
       <c r="X425" s="2" t="inlineStr"/>
       <c r="Y425" s="2" t="n">
-        <v>-6.93</v>
+        <v>-16.17</v>
       </c>
       <c r="Z425" s="2" t="n">
-        <v>14.96</v>
+        <v>-16.93</v>
       </c>
       <c r="AA425" s="2" t="n">
-        <v>11.42</v>
+        <v>-12.52</v>
       </c>
       <c r="AB425" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.9</v>
       </c>
       <c r="AC425" s="2" t="n">
-        <v>21.54</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>VICI US</t>
+          <t>VLO US</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>25.42</v>
+        <v>370.72</v>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>-0.6</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>-7</v>
+        <v>42.8</v>
       </c>
       <c r="G426" s="2" t="n">
-        <v>0.63</v>
+        <v>103.03</v>
       </c>
       <c r="H426" s="2" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr"/>
-      <c r="J426" s="2" t="inlineStr"/>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K426" s="2" t="inlineStr"/>
       <c r="L426" s="2" t="inlineStr"/>
-      <c r="M426" s="2" t="inlineStr"/>
+      <c r="M426" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N426" s="2" t="inlineStr"/>
-      <c r="O426" s="2" t="inlineStr"/>
-      <c r="P426" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="O426" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P426" s="2" t="inlineStr"/>
       <c r="Q426" s="2" t="n">
         <v>0</v>
       </c>
@@ -29781,66 +29783,62 @@
       <c r="W426" s="2" t="inlineStr"/>
       <c r="X426" s="2" t="inlineStr"/>
       <c r="Y426" s="2" t="n">
-        <v>-16.17</v>
+        <v>106.19</v>
       </c>
       <c r="Z426" s="2" t="n">
-        <v>-16.93</v>
+        <v>53.38</v>
       </c>
       <c r="AA426" s="2" t="n">
-        <v>-12.52</v>
+        <v>37.18</v>
       </c>
       <c r="AB426" s="2" t="n">
-        <v>-0.9</v>
+        <v>5.19</v>
       </c>
       <c r="AC426" s="2" t="n">
-        <v>-1.42</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>VLO US</t>
+          <t>VLTO US</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>370.72</v>
+        <v>96.31</v>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>42.8</v>
+        <v>5.9</v>
       </c>
       <c r="G427" s="2" t="n">
-        <v>103.03</v>
+        <v>86.87</v>
       </c>
       <c r="H427" s="2" t="inlineStr"/>
       <c r="I427" s="2" t="inlineStr"/>
-      <c r="J427" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J427" s="2" t="inlineStr"/>
       <c r="K427" s="2" t="inlineStr"/>
       <c r="L427" s="2" t="inlineStr"/>
-      <c r="M427" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M427" s="2" t="inlineStr"/>
       <c r="N427" s="2" t="inlineStr"/>
       <c r="O427" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="P427" s="2" t="inlineStr"/>
+        <v>-9</v>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q427" s="2" t="n">
         <v>0</v>
       </c>
@@ -29852,48 +29850,48 @@
       <c r="W427" s="2" t="inlineStr"/>
       <c r="X427" s="2" t="inlineStr"/>
       <c r="Y427" s="2" t="n">
-        <v>106.19</v>
+        <v>-0.53</v>
       </c>
       <c r="Z427" s="2" t="n">
-        <v>53.38</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AA427" s="2" t="n">
-        <v>37.18</v>
+        <v>-4.77</v>
       </c>
       <c r="AB427" s="2" t="n">
-        <v>5.19</v>
+        <v>-1.73</v>
       </c>
       <c r="AC427" s="2" t="n">
-        <v>22.85</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>VLTO US</t>
+          <t>VMC US</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>96.31</v>
+        <v>262.63</v>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>-0.39</v>
+        <v>-1.18</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>5.9</v>
+        <v>-7.9</v>
       </c>
       <c r="G428" s="2" t="n">
-        <v>86.87</v>
+        <v>3.12</v>
       </c>
       <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr"/>
@@ -29902,65 +29900,65 @@
       <c r="L428" s="2" t="inlineStr"/>
       <c r="M428" s="2" t="inlineStr"/>
       <c r="N428" s="2" t="inlineStr"/>
-      <c r="O428" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P428" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="O428" s="2" t="inlineStr"/>
+      <c r="P428" s="2" t="inlineStr"/>
       <c r="Q428" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R428" s="2" t="inlineStr"/>
       <c r="S428" s="2" t="inlineStr"/>
       <c r="T428" s="2" t="inlineStr"/>
-      <c r="U428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="V428" s="2" t="inlineStr"/>
       <c r="W428" s="2" t="inlineStr"/>
       <c r="X428" s="2" t="inlineStr"/>
       <c r="Y428" s="2" t="n">
-        <v>-0.53</v>
+        <v>-10</v>
       </c>
       <c r="Z428" s="2" t="n">
-        <v>-8.029999999999999</v>
+        <v>-17.15</v>
       </c>
       <c r="AA428" s="2" t="n">
-        <v>-4.77</v>
+        <v>-16.24</v>
       </c>
       <c r="AB428" s="2" t="n">
-        <v>-1.73</v>
+        <v>-3.39</v>
       </c>
       <c r="AC428" s="2" t="n">
-        <v>0.62</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>VMC US</t>
+          <t>VRSK US</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>262.63</v>
+        <v>185.79</v>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>-1.18</v>
+        <v>-2.3</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>-7.9</v>
+        <v>0.2</v>
       </c>
       <c r="G429" s="2" t="n">
-        <v>3.12</v>
+        <v>12.2</v>
       </c>
       <c r="H429" s="2" t="inlineStr"/>
       <c r="I429" s="2" t="inlineStr"/>
@@ -29970,64 +29968,68 @@
       <c r="M429" s="2" t="inlineStr"/>
       <c r="N429" s="2" t="inlineStr"/>
       <c r="O429" s="2" t="inlineStr"/>
-      <c r="P429" s="2" t="inlineStr"/>
+      <c r="P429" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q429" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R429" s="2" t="inlineStr"/>
       <c r="S429" s="2" t="inlineStr"/>
       <c r="T429" s="2" t="inlineStr"/>
-      <c r="U429" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="V429" s="2" t="inlineStr"/>
+      <c r="U429" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V429" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W429" s="2" t="inlineStr"/>
       <c r="X429" s="2" t="inlineStr"/>
       <c r="Y429" s="2" t="n">
-        <v>-10</v>
+        <v>-16.07</v>
       </c>
       <c r="Z429" s="2" t="n">
-        <v>-17.15</v>
+        <v>-16.85</v>
       </c>
       <c r="AA429" s="2" t="n">
-        <v>-16.24</v>
+        <v>-14.01</v>
       </c>
       <c r="AB429" s="2" t="n">
-        <v>-3.39</v>
+        <v>-1.81</v>
       </c>
       <c r="AC429" s="2" t="n">
-        <v>-4.78</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>VRSK US</t>
+          <t>VRSN US</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>185.79</v>
+        <v>292.08</v>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>-2.3</v>
+        <v>2.1</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="G430" s="2" t="n">
-        <v>12.2</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="H430" s="2" t="inlineStr"/>
       <c r="I430" s="2" t="inlineStr"/>
@@ -30037,68 +30039,62 @@
       <c r="M430" s="2" t="inlineStr"/>
       <c r="N430" s="2" t="inlineStr"/>
       <c r="O430" s="2" t="inlineStr"/>
-      <c r="P430" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P430" s="2" t="inlineStr"/>
       <c r="Q430" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R430" s="2" t="inlineStr"/>
       <c r="S430" s="2" t="inlineStr"/>
       <c r="T430" s="2" t="inlineStr"/>
-      <c r="U430" s="2" t="n">
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V430" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="W430" s="2" t="inlineStr"/>
       <c r="X430" s="2" t="inlineStr"/>
       <c r="Y430" s="2" t="n">
-        <v>-16.07</v>
+        <v>21.43</v>
       </c>
       <c r="Z430" s="2" t="n">
-        <v>-16.85</v>
+        <v>2.32</v>
       </c>
       <c r="AA430" s="2" t="n">
-        <v>-14.01</v>
+        <v>-7.29</v>
       </c>
       <c r="AB430" s="2" t="n">
-        <v>-1.81</v>
+        <v>0.19</v>
       </c>
       <c r="AC430" s="2" t="n">
-        <v>1.53</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>VRSN US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>292.08</v>
+        <v>280.53</v>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>2.1</v>
+        <v>4.51</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>10</v>
+        <v>-1.8</v>
       </c>
       <c r="G431" s="2" t="n">
-        <v>76.79000000000001</v>
+        <v>32.75</v>
       </c>
       <c r="H431" s="2" t="inlineStr"/>
       <c r="I431" s="2" t="inlineStr"/>
@@ -30110,67 +30106,75 @@
       <c r="O431" s="2" t="inlineStr"/>
       <c r="P431" s="2" t="inlineStr"/>
       <c r="Q431" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R431" s="2" t="inlineStr"/>
       <c r="S431" s="2" t="inlineStr"/>
       <c r="T431" s="2" t="inlineStr"/>
       <c r="U431" s="2" t="inlineStr"/>
-      <c r="V431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W431" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X431" s="2" t="inlineStr"/>
       <c r="Y431" s="2" t="n">
-        <v>21.43</v>
+        <v>47.69</v>
       </c>
       <c r="Z431" s="2" t="n">
-        <v>2.32</v>
+        <v>8.48</v>
       </c>
       <c r="AA431" s="2" t="n">
-        <v>-7.29</v>
+        <v>13.17</v>
       </c>
       <c r="AB431" s="2" t="n">
-        <v>0.19</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AC431" s="2" t="n">
-        <v>0.89</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>VRTX US</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>280.53</v>
+        <v>546.12</v>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>4.51</v>
+        <v>2.21</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>-1.8</v>
+        <v>16</v>
       </c>
       <c r="G432" s="2" t="n">
-        <v>32.75</v>
+        <v>57.73</v>
       </c>
       <c r="H432" s="2" t="inlineStr"/>
       <c r="I432" s="2" t="inlineStr"/>
-      <c r="J432" s="2" t="inlineStr"/>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K432" s="2" t="inlineStr"/>
       <c r="L432" s="2" t="inlineStr"/>
-      <c r="M432" s="2" t="inlineStr"/>
+      <c r="M432" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N432" s="2" t="inlineStr"/>
       <c r="O432" s="2" t="inlineStr"/>
       <c r="P432" s="2" t="inlineStr"/>
@@ -30180,69 +30184,73 @@
       <c r="R432" s="2" t="inlineStr"/>
       <c r="S432" s="2" t="inlineStr"/>
       <c r="T432" s="2" t="inlineStr"/>
-      <c r="U432" s="2" t="inlineStr"/>
+      <c r="U432" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="V432" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W432" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="W432" s="2" t="inlineStr"/>
       <c r="X432" s="2" t="inlineStr"/>
       <c r="Y432" s="2" t="n">
-        <v>47.69</v>
+        <v>32.77</v>
       </c>
       <c r="Z432" s="2" t="n">
-        <v>8.48</v>
+        <v>9.82</v>
       </c>
       <c r="AA432" s="2" t="n">
-        <v>13.17</v>
+        <v>6.49</v>
       </c>
       <c r="AB432" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AC432" s="2" t="n">
-        <v>-0.08</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>VRTX US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>546.12</v>
+        <v>149.3</v>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>2.21</v>
+        <v>-1.82</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>16</v>
+        <v>-3.4</v>
       </c>
       <c r="G433" s="2" t="n">
-        <v>57.73</v>
+        <v>-6.77</v>
       </c>
       <c r="H433" s="2" t="inlineStr"/>
-      <c r="I433" s="2" t="inlineStr"/>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>顶背离</t>
+          <t>底背离</t>
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr"/>
       <c r="L433" s="2" t="inlineStr"/>
       <c r="M433" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N433" s="2" t="inlineStr"/>
       <c r="O433" s="2" t="inlineStr"/>
@@ -30253,74 +30261,60 @@
       <c r="R433" s="2" t="inlineStr"/>
       <c r="S433" s="2" t="inlineStr"/>
       <c r="T433" s="2" t="inlineStr"/>
-      <c r="U433" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V433" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U433" s="2" t="inlineStr"/>
+      <c r="V433" s="2" t="inlineStr"/>
       <c r="W433" s="2" t="inlineStr"/>
       <c r="X433" s="2" t="inlineStr"/>
       <c r="Y433" s="2" t="n">
-        <v>32.77</v>
+        <v>-26.71</v>
       </c>
       <c r="Z433" s="2" t="n">
-        <v>9.82</v>
+        <v>-18.17</v>
       </c>
       <c r="AA433" s="2" t="n">
-        <v>6.49</v>
+        <v>-7.95</v>
       </c>
       <c r="AB433" s="2" t="n">
-        <v>0.44</v>
+        <v>7.29</v>
       </c>
       <c r="AC433" s="2" t="n">
-        <v>9.41</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>VTRS US</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>149.3</v>
+        <v>16.88</v>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>-1.82</v>
+        <v>3.42</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>-3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G434" s="2" t="n">
-        <v>-6.77</v>
+        <v>18.9</v>
       </c>
       <c r="H434" s="2" t="inlineStr"/>
-      <c r="I434" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
-      <c r="J434" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+      <c r="I434" s="2" t="inlineStr"/>
+      <c r="J434" s="2" t="inlineStr"/>
       <c r="K434" s="2" t="inlineStr"/>
       <c r="L434" s="2" t="inlineStr"/>
-      <c r="M434" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M434" s="2" t="inlineStr"/>
       <c r="N434" s="2" t="inlineStr"/>
       <c r="O434" s="2" t="inlineStr"/>
       <c r="P434" s="2" t="inlineStr"/>
@@ -30330,39 +30324,45 @@
       <c r="R434" s="2" t="inlineStr"/>
       <c r="S434" s="2" t="inlineStr"/>
       <c r="T434" s="2" t="inlineStr"/>
-      <c r="U434" s="2" t="inlineStr"/>
+      <c r="U434" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="V434" s="2" t="inlineStr"/>
       <c r="W434" s="2" t="inlineStr"/>
-      <c r="X434" s="2" t="inlineStr"/>
+      <c r="X434" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y434" s="2" t="n">
-        <v>-26.71</v>
+        <v>56.9</v>
       </c>
       <c r="Z434" s="2" t="n">
-        <v>-18.17</v>
+        <v>14.49</v>
       </c>
       <c r="AA434" s="2" t="n">
-        <v>-7.95</v>
+        <v>10.72</v>
       </c>
       <c r="AB434" s="2" t="n">
-        <v>7.29</v>
+        <v>2.84</v>
       </c>
       <c r="AC434" s="2" t="n">
-        <v>8.1</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>VTRS US</t>
+          <t>VZ US</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>16.88</v>
+        <v>50.14</v>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
@@ -30370,68 +30370,78 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G435" s="2" t="n">
-        <v>18.9</v>
+        <v>110.73</v>
       </c>
       <c r="H435" s="2" t="inlineStr"/>
-      <c r="I435" s="2" t="inlineStr"/>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J435" s="2" t="inlineStr"/>
       <c r="K435" s="2" t="inlineStr"/>
-      <c r="L435" s="2" t="inlineStr"/>
-      <c r="M435" s="2" t="inlineStr"/>
-      <c r="N435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="O435" s="2" t="inlineStr"/>
-      <c r="P435" s="2" t="inlineStr"/>
+      <c r="P435" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q435" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R435" s="2" t="inlineStr"/>
       <c r="S435" s="2" t="inlineStr"/>
       <c r="T435" s="2" t="inlineStr"/>
-      <c r="U435" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="V435" s="2" t="inlineStr"/>
+      <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="W435" s="2" t="inlineStr"/>
-      <c r="X435" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="X435" s="2" t="inlineStr"/>
       <c r="Y435" s="2" t="n">
-        <v>56.9</v>
+        <v>33.02</v>
       </c>
       <c r="Z435" s="2" t="n">
-        <v>14.49</v>
+        <v>5.09</v>
       </c>
       <c r="AA435" s="2" t="n">
-        <v>10.72</v>
+        <v>16.78</v>
       </c>
       <c r="AB435" s="2" t="n">
-        <v>2.84</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC435" s="2" t="n">
-        <v>1.72</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>VZ US</t>
+          <t>WAB US</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>50.14</v>
+        <v>282.86</v>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
@@ -30439,92 +30449,82 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="G436" s="2" t="n">
-        <v>110.73</v>
+        <v>92.55</v>
       </c>
       <c r="H436" s="2" t="inlineStr"/>
-      <c r="I436" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr"/>
       <c r="K436" s="2" t="inlineStr"/>
-      <c r="L436" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
-      <c r="M436" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N436" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="L436" s="2" t="inlineStr"/>
+      <c r="M436" s="2" t="inlineStr"/>
+      <c r="N436" s="2" t="inlineStr"/>
       <c r="O436" s="2" t="inlineStr"/>
       <c r="P436" s="2" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="Q436" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R436" s="2" t="inlineStr"/>
       <c r="S436" s="2" t="inlineStr"/>
       <c r="T436" s="2" t="inlineStr"/>
-      <c r="U436" s="2" t="inlineStr"/>
-      <c r="V436" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U436" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="V436" s="2" t="inlineStr"/>
       <c r="W436" s="2" t="inlineStr"/>
       <c r="X436" s="2" t="inlineStr"/>
       <c r="Y436" s="2" t="n">
-        <v>33.02</v>
+        <v>40.03</v>
       </c>
       <c r="Z436" s="2" t="n">
-        <v>5.09</v>
+        <v>7.12</v>
       </c>
       <c r="AA436" s="2" t="n">
-        <v>16.78</v>
+        <v>11.46</v>
       </c>
       <c r="AB436" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.09</v>
       </c>
       <c r="AC436" s="2" t="n">
-        <v>6.97</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>WAB US</t>
+          <t>WAT US</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C437" s="2" t="n">
-        <v>282.86</v>
+        <v>409.38</v>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>3.46</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>6.3</v>
+        <v>16.6</v>
       </c>
       <c r="G437" s="2" t="n">
-        <v>92.55</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="H437" s="2" t="inlineStr"/>
       <c r="I437" s="2" t="inlineStr"/>
@@ -30534,52 +30534,48 @@
       <c r="M437" s="2" t="inlineStr"/>
       <c r="N437" s="2" t="inlineStr"/>
       <c r="O437" s="2" t="inlineStr"/>
-      <c r="P437" s="2" t="n">
-        <v>-13</v>
-      </c>
+      <c r="P437" s="2" t="inlineStr"/>
       <c r="Q437" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R437" s="2" t="inlineStr"/>
       <c r="S437" s="2" t="inlineStr"/>
       <c r="T437" s="2" t="inlineStr"/>
-      <c r="U437" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U437" s="2" t="inlineStr"/>
       <c r="V437" s="2" t="inlineStr"/>
-      <c r="W437" s="2" t="inlineStr"/>
+      <c r="W437" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X437" s="2" t="inlineStr"/>
       <c r="Y437" s="2" t="n">
-        <v>40.03</v>
+        <v>10.5</v>
       </c>
       <c r="Z437" s="2" t="n">
-        <v>7.12</v>
+        <v>5.4</v>
       </c>
       <c r="AA437" s="2" t="n">
-        <v>11.46</v>
+        <v>2.18</v>
       </c>
       <c r="AB437" s="2" t="n">
-        <v>-4.09</v>
+        <v>-1.78</v>
       </c>
       <c r="AC437" s="2" t="n">
-        <v>-4.85</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>WAT US</t>
+          <t>WBD US</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C438" s="2" t="n">
-        <v>409.38</v>
+        <v>28.25</v>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
@@ -30587,20 +30583,26 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>16.6</v>
+        <v>3.6</v>
       </c>
       <c r="G438" s="2" t="n">
-        <v>92.18000000000001</v>
+        <v>112.43</v>
       </c>
       <c r="H438" s="2" t="inlineStr"/>
-      <c r="I438" s="2" t="inlineStr"/>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J438" s="2" t="inlineStr"/>
       <c r="K438" s="2" t="inlineStr"/>
       <c r="L438" s="2" t="inlineStr"/>
-      <c r="M438" s="2" t="inlineStr"/>
+      <c r="M438" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N438" s="2" t="inlineStr"/>
       <c r="O438" s="2" t="inlineStr"/>
       <c r="P438" s="2" t="inlineStr"/>
@@ -30611,40 +30613,40 @@
       <c r="S438" s="2" t="inlineStr"/>
       <c r="T438" s="2" t="inlineStr"/>
       <c r="U438" s="2" t="inlineStr"/>
-      <c r="V438" s="2" t="inlineStr"/>
-      <c r="W438" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="V438" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W438" s="2" t="inlineStr"/>
       <c r="X438" s="2" t="inlineStr"/>
       <c r="Y438" s="2" t="n">
-        <v>10.5</v>
+        <v>27.49</v>
       </c>
       <c r="Z438" s="2" t="n">
-        <v>5.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA438" s="2" t="n">
-        <v>2.18</v>
+        <v>11.67</v>
       </c>
       <c r="AB438" s="2" t="n">
-        <v>-1.78</v>
+        <v>-2.99</v>
       </c>
       <c r="AC438" s="2" t="n">
-        <v>-0.15</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>WBD US</t>
+          <t>WDAY US</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="C439" s="2" t="n">
-        <v>28.25</v>
+        <v>195.79</v>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
@@ -30652,95 +30654,95 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>3.6</v>
+        <v>36.2</v>
       </c>
       <c r="G439" s="2" t="n">
-        <v>112.43</v>
+        <v>92.42</v>
       </c>
       <c r="H439" s="2" t="inlineStr"/>
-      <c r="I439" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I439" s="2" t="inlineStr"/>
       <c r="J439" s="2" t="inlineStr"/>
       <c r="K439" s="2" t="inlineStr"/>
       <c r="L439" s="2" t="inlineStr"/>
-      <c r="M439" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M439" s="2" t="inlineStr"/>
       <c r="N439" s="2" t="inlineStr"/>
-      <c r="O439" s="2" t="inlineStr"/>
+      <c r="O439" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P439" s="2" t="inlineStr"/>
       <c r="Q439" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R439" s="2" t="inlineStr"/>
       <c r="S439" s="2" t="inlineStr"/>
       <c r="T439" s="2" t="inlineStr"/>
-      <c r="U439" s="2" t="inlineStr"/>
-      <c r="V439" s="2" t="n">
+      <c r="U439" s="2" t="n">
         <v>-1</v>
       </c>
+      <c r="V439" s="2" t="inlineStr"/>
       <c r="W439" s="2" t="inlineStr"/>
       <c r="X439" s="2" t="inlineStr"/>
       <c r="Y439" s="2" t="n">
-        <v>27.49</v>
+        <v>-21.46</v>
       </c>
       <c r="Z439" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AA439" s="2" t="n">
-        <v>11.67</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AB439" s="2" t="n">
-        <v>-2.99</v>
+        <v>-3.9</v>
       </c>
       <c r="AC439" s="2" t="n">
-        <v>1.73</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>WDAY US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C440" s="2" t="n">
-        <v>195.79</v>
+        <v>105.94</v>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>36.2</v>
+        <v>-5.3</v>
       </c>
       <c r="G440" s="2" t="n">
-        <v>92.42</v>
-      </c>
-      <c r="H440" s="2" t="inlineStr"/>
+        <v>-1.62</v>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr"/>
       <c r="K440" s="2" t="inlineStr"/>
       <c r="L440" s="2" t="inlineStr"/>
-      <c r="M440" s="2" t="inlineStr"/>
+      <c r="M440" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N440" s="2" t="inlineStr"/>
-      <c r="O440" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O440" s="2" t="inlineStr"/>
       <c r="P440" s="2" t="inlineStr"/>
       <c r="Q440" s="2" t="n">
         <v>0</v>
@@ -30749,70 +30751,66 @@
       <c r="S440" s="2" t="inlineStr"/>
       <c r="T440" s="2" t="inlineStr"/>
       <c r="U440" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V440" s="2" t="inlineStr"/>
       <c r="W440" s="2" t="inlineStr"/>
       <c r="X440" s="2" t="inlineStr"/>
       <c r="Y440" s="2" t="n">
-        <v>-21.46</v>
+        <v>-2.77</v>
       </c>
       <c r="Z440" s="2" t="n">
-        <v>1.1</v>
+        <v>-12.11</v>
       </c>
       <c r="AA440" s="2" t="n">
-        <v>-9.279999999999999</v>
+        <v>-1.33</v>
       </c>
       <c r="AB440" s="2" t="n">
-        <v>-3.9</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC440" s="2" t="n">
-        <v>11.55</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>WELL US</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Welltower</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>105.94</v>
+        <v>236.17</v>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>0.29</v>
+        <v>3.35</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>-5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G441" s="2" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>63.35</v>
+      </c>
+      <c r="H441" s="2" t="inlineStr"/>
       <c r="I441" s="2" t="inlineStr"/>
       <c r="J441" s="2" t="inlineStr"/>
       <c r="K441" s="2" t="inlineStr"/>
       <c r="L441" s="2" t="inlineStr"/>
-      <c r="M441" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M441" s="2" t="inlineStr"/>
       <c r="N441" s="2" t="inlineStr"/>
       <c r="O441" s="2" t="inlineStr"/>
-      <c r="P441" s="2" t="inlineStr"/>
+      <c r="P441" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q441" s="2" t="n">
         <v>0</v>
       </c>
@@ -30820,54 +30818,56 @@
       <c r="S441" s="2" t="inlineStr"/>
       <c r="T441" s="2" t="inlineStr"/>
       <c r="U441" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V441" s="2" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="V441" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="W441" s="2" t="inlineStr"/>
       <c r="X441" s="2" t="inlineStr"/>
       <c r="Y441" s="2" t="n">
-        <v>-2.77</v>
+        <v>29.54</v>
       </c>
       <c r="Z441" s="2" t="n">
-        <v>-12.11</v>
+        <v>6.9</v>
       </c>
       <c r="AA441" s="2" t="n">
-        <v>-1.33</v>
+        <v>12.46</v>
       </c>
       <c r="AB441" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.36</v>
       </c>
       <c r="AC441" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>WELL US</t>
+          <t>WFC US</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Welltower</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C442" s="2" t="n">
-        <v>236.17</v>
+        <v>89.97</v>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>3.35</v>
+        <v>-0.45</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G442" s="2" t="n">
-        <v>63.35</v>
+        <v>41.04</v>
       </c>
       <c r="H442" s="2" t="inlineStr"/>
       <c r="I442" s="2" t="inlineStr"/>
@@ -30877,66 +30877,64 @@
       <c r="M442" s="2" t="inlineStr"/>
       <c r="N442" s="2" t="inlineStr"/>
       <c r="O442" s="2" t="inlineStr"/>
-      <c r="P442" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P442" s="2" t="inlineStr"/>
       <c r="Q442" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R442" s="2" t="inlineStr"/>
       <c r="S442" s="2" t="inlineStr"/>
       <c r="T442" s="2" t="inlineStr"/>
-      <c r="U442" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U442" s="2" t="inlineStr"/>
       <c r="V442" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W442" s="2" t="inlineStr"/>
-      <c r="X442" s="2" t="inlineStr"/>
+      <c r="X442" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y442" s="2" t="n">
-        <v>29.54</v>
+        <v>7.16</v>
       </c>
       <c r="Z442" s="2" t="n">
-        <v>6.9</v>
+        <v>-2.04</v>
       </c>
       <c r="AA442" s="2" t="n">
-        <v>12.46</v>
+        <v>-1.85</v>
       </c>
       <c r="AB442" s="2" t="n">
-        <v>-1.36</v>
+        <v>3.62</v>
       </c>
       <c r="AC442" s="2" t="n">
-        <v>-0.99</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>WFC US</t>
+          <t>WM US</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C443" s="2" t="n">
-        <v>89.97</v>
+        <v>218.99</v>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>-0.45</v>
+        <v>0.12</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>8.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G443" s="2" t="n">
-        <v>41.04</v>
+        <v>-4.75</v>
       </c>
       <c r="H443" s="2" t="inlineStr"/>
       <c r="I443" s="2" t="inlineStr"/>
@@ -30948,62 +30946,62 @@
       <c r="O443" s="2" t="inlineStr"/>
       <c r="P443" s="2" t="inlineStr"/>
       <c r="Q443" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R443" s="2" t="inlineStr"/>
       <c r="S443" s="2" t="inlineStr"/>
       <c r="T443" s="2" t="inlineStr"/>
-      <c r="U443" s="2" t="inlineStr"/>
-      <c r="V443" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U443" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="V443" s="2" t="inlineStr"/>
       <c r="W443" s="2" t="inlineStr"/>
-      <c r="X443" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="X443" s="2" t="inlineStr"/>
       <c r="Y443" s="2" t="n">
-        <v>7.16</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z443" s="2" t="n">
-        <v>-2.04</v>
+        <v>-9.82</v>
       </c>
       <c r="AA443" s="2" t="n">
-        <v>-1.85</v>
+        <v>-6.35</v>
       </c>
       <c r="AB443" s="2" t="n">
-        <v>3.62</v>
+        <v>-0.03</v>
       </c>
       <c r="AC443" s="2" t="n">
-        <v>3.94</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>WM US</t>
+          <t>WMB US</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="C444" s="2" t="n">
-        <v>218.99</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>0.12</v>
+        <v>2.21</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>-3.4</v>
+        <v>1.9</v>
       </c>
       <c r="G444" s="2" t="n">
-        <v>-4.75</v>
+        <v>25.75</v>
       </c>
       <c r="H444" s="2" t="inlineStr"/>
       <c r="I444" s="2" t="inlineStr"/>
@@ -31020,57 +31018,57 @@
       <c r="R444" s="2" t="inlineStr"/>
       <c r="S444" s="2" t="inlineStr"/>
       <c r="T444" s="2" t="inlineStr"/>
-      <c r="U444" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="U444" s="2" t="n">
+        <v>-1</v>
       </c>
       <c r="V444" s="2" t="inlineStr"/>
       <c r="W444" s="2" t="inlineStr"/>
-      <c r="X444" s="2" t="inlineStr"/>
+      <c r="X444" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y444" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>29.66</v>
       </c>
       <c r="Z444" s="2" t="n">
-        <v>-9.82</v>
+        <v>0.5</v>
       </c>
       <c r="AA444" s="2" t="n">
-        <v>-6.35</v>
+        <v>-11.06</v>
       </c>
       <c r="AB444" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.26</v>
       </c>
       <c r="AC444" s="2" t="n">
-        <v>-1.72</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>WMB US</t>
+          <t>WMT US</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C445" s="2" t="n">
-        <v>74.15000000000001</v>
+        <v>107.14</v>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>2.21</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>1.9</v>
+        <v>-10.6</v>
       </c>
       <c r="G445" s="2" t="n">
-        <v>25.75</v>
+        <v>8.68</v>
       </c>
       <c r="H445" s="2" t="inlineStr"/>
       <c r="I445" s="2" t="inlineStr"/>
@@ -31087,57 +31085,57 @@
       <c r="R445" s="2" t="inlineStr"/>
       <c r="S445" s="2" t="inlineStr"/>
       <c r="T445" s="2" t="inlineStr"/>
-      <c r="U445" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V445" s="2" t="inlineStr"/>
-      <c r="W445" s="2" t="inlineStr"/>
-      <c r="X445" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U445" s="2" t="inlineStr"/>
+      <c r="V445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X445" s="2" t="inlineStr"/>
       <c r="Y445" s="2" t="n">
-        <v>29.66</v>
+        <v>4.82</v>
       </c>
       <c r="Z445" s="2" t="n">
-        <v>0.5</v>
+        <v>-15.02</v>
       </c>
       <c r="AA445" s="2" t="n">
-        <v>-11.06</v>
+        <v>-10.26</v>
       </c>
       <c r="AB445" s="2" t="n">
-        <v>0.26</v>
+        <v>3.26</v>
       </c>
       <c r="AC445" s="2" t="n">
-        <v>4.87</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>WMT US</t>
+          <t>WRB US</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C446" s="2" t="n">
-        <v>107.14</v>
+        <v>69.14</v>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>-10.6</v>
+        <v>1</v>
       </c>
       <c r="G446" s="2" t="n">
-        <v>8.68</v>
+        <v>-5.79</v>
       </c>
       <c r="H446" s="2" t="inlineStr"/>
       <c r="I446" s="2" t="inlineStr"/>
@@ -31147,64 +31145,66 @@
       <c r="M446" s="2" t="inlineStr"/>
       <c r="N446" s="2" t="inlineStr"/>
       <c r="O446" s="2" t="inlineStr"/>
-      <c r="P446" s="2" t="inlineStr"/>
+      <c r="P446" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="Q446" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R446" s="2" t="inlineStr"/>
       <c r="S446" s="2" t="inlineStr"/>
       <c r="T446" s="2" t="inlineStr"/>
-      <c r="U446" s="2" t="inlineStr"/>
+      <c r="U446" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V446" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W446" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="W446" s="2" t="inlineStr"/>
       <c r="X446" s="2" t="inlineStr"/>
       <c r="Y446" s="2" t="n">
-        <v>4.82</v>
+        <v>-12.14</v>
       </c>
       <c r="Z446" s="2" t="n">
-        <v>-15.02</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="AA446" s="2" t="n">
-        <v>-10.26</v>
+        <v>-9.31</v>
       </c>
       <c r="AB446" s="2" t="n">
-        <v>3.26</v>
+        <v>1.19</v>
       </c>
       <c r="AC446" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>WRB US</t>
+          <t>WSM US</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C447" s="2" t="n">
-        <v>69.14</v>
+        <v>227.42</v>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>0.3</v>
+        <v>2.28</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G447" s="2" t="n">
-        <v>-5.79</v>
+        <v>75.94</v>
       </c>
       <c r="H447" s="2" t="inlineStr"/>
       <c r="I447" s="2" t="inlineStr"/>
@@ -31214,52 +31214,50 @@
       <c r="M447" s="2" t="inlineStr"/>
       <c r="N447" s="2" t="inlineStr"/>
       <c r="O447" s="2" t="inlineStr"/>
-      <c r="P447" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="P447" s="2" t="inlineStr"/>
       <c r="Q447" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R447" s="2" t="inlineStr"/>
       <c r="S447" s="2" t="inlineStr"/>
       <c r="T447" s="2" t="inlineStr"/>
-      <c r="U447" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V447" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U447" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="V447" s="2" t="inlineStr"/>
       <c r="W447" s="2" t="inlineStr"/>
       <c r="X447" s="2" t="inlineStr"/>
       <c r="Y447" s="2" t="n">
-        <v>-12.14</v>
+        <v>25.52</v>
       </c>
       <c r="Z447" s="2" t="n">
-        <v>-9.460000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="AA447" s="2" t="n">
-        <v>-9.31</v>
+        <v>15.1</v>
       </c>
       <c r="AB447" s="2" t="n">
-        <v>1.19</v>
+        <v>-3.57</v>
       </c>
       <c r="AC447" s="2" t="n">
-        <v>-1.41</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>WSM US</t>
+          <t>WST US</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C448" s="2" t="n">
-        <v>227.42</v>
+        <v>339.97</v>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
@@ -31267,13 +31265,13 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>2.28</v>
+        <v>4.04</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G448" s="2" t="n">
-        <v>75.94</v>
+        <v>11.88</v>
       </c>
       <c r="H448" s="2" t="inlineStr"/>
       <c r="I448" s="2" t="inlineStr"/>
@@ -31290,57 +31288,55 @@
       <c r="R448" s="2" t="inlineStr"/>
       <c r="S448" s="2" t="inlineStr"/>
       <c r="T448" s="2" t="inlineStr"/>
-      <c r="U448" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
+      <c r="U448" s="2" t="n">
+        <v>-1</v>
       </c>
       <c r="V448" s="2" t="inlineStr"/>
       <c r="W448" s="2" t="inlineStr"/>
       <c r="X448" s="2" t="inlineStr"/>
       <c r="Y448" s="2" t="n">
-        <v>25.52</v>
+        <v>32.7</v>
       </c>
       <c r="Z448" s="2" t="n">
-        <v>3.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA448" s="2" t="n">
-        <v>15.1</v>
+        <v>4.53</v>
       </c>
       <c r="AB448" s="2" t="n">
-        <v>-3.57</v>
+        <v>0.37</v>
       </c>
       <c r="AC448" s="2" t="n">
-        <v>-10.57</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>WST US</t>
+          <t>WTW US</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C449" s="2" t="n">
-        <v>339.97</v>
+        <v>334.74</v>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>4.04</v>
+        <v>0.73</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="G449" s="2" t="n">
-        <v>11.88</v>
+        <v>104.55</v>
       </c>
       <c r="H449" s="2" t="inlineStr"/>
       <c r="I449" s="2" t="inlineStr"/>
@@ -31349,7 +31345,9 @@
       <c r="L449" s="2" t="inlineStr"/>
       <c r="M449" s="2" t="inlineStr"/>
       <c r="N449" s="2" t="inlineStr"/>
-      <c r="O449" s="2" t="inlineStr"/>
+      <c r="O449" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P449" s="2" t="inlineStr"/>
       <c r="Q449" s="2" t="n">
         <v>1</v>
@@ -31357,55 +31355,53 @@
       <c r="R449" s="2" t="inlineStr"/>
       <c r="S449" s="2" t="inlineStr"/>
       <c r="T449" s="2" t="inlineStr"/>
-      <c r="U449" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U449" s="2" t="inlineStr"/>
       <c r="V449" s="2" t="inlineStr"/>
       <c r="W449" s="2" t="inlineStr"/>
       <c r="X449" s="2" t="inlineStr"/>
       <c r="Y449" s="2" t="n">
-        <v>32.7</v>
+        <v>8.35</v>
       </c>
       <c r="Z449" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>-0.17</v>
       </c>
       <c r="AA449" s="2" t="n">
-        <v>4.53</v>
+        <v>0.23</v>
       </c>
       <c r="AB449" s="2" t="n">
-        <v>0.37</v>
+        <v>-2.49</v>
       </c>
       <c r="AC449" s="2" t="n">
-        <v>-5.5</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>WTW US</t>
+          <t>WY US</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C450" s="2" t="n">
-        <v>334.74</v>
+        <v>23.02</v>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>0.73</v>
+        <v>-0.65</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>15</v>
+        <v>-4.1</v>
       </c>
       <c r="G450" s="2" t="n">
-        <v>104.55</v>
+        <v>73.33</v>
       </c>
       <c r="H450" s="2" t="inlineStr"/>
       <c r="I450" s="2" t="inlineStr"/>
@@ -31414,63 +31410,67 @@
       <c r="L450" s="2" t="inlineStr"/>
       <c r="M450" s="2" t="inlineStr"/>
       <c r="N450" s="2" t="inlineStr"/>
-      <c r="O450" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P450" s="2" t="inlineStr"/>
+      <c r="O450" s="2" t="inlineStr"/>
+      <c r="P450" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q450" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R450" s="2" t="inlineStr"/>
       <c r="S450" s="2" t="inlineStr"/>
       <c r="T450" s="2" t="inlineStr"/>
-      <c r="U450" s="2" t="inlineStr"/>
+      <c r="U450" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="V450" s="2" t="inlineStr"/>
       <c r="W450" s="2" t="inlineStr"/>
       <c r="X450" s="2" t="inlineStr"/>
       <c r="Y450" s="2" t="n">
-        <v>8.35</v>
+        <v>8.52</v>
       </c>
       <c r="Z450" s="2" t="n">
-        <v>-0.17</v>
+        <v>-11.42</v>
       </c>
       <c r="AA450" s="2" t="n">
-        <v>0.23</v>
+        <v>-6.76</v>
       </c>
       <c r="AB450" s="2" t="n">
-        <v>-2.49</v>
+        <v>-1.22</v>
       </c>
       <c r="AC450" s="2" t="n">
-        <v>-1.22</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>WY US</t>
+          <t>WYNN US</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C451" s="2" t="n">
-        <v>23.02</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>-0.65</v>
+        <v>-2.13</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>-4.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G451" s="2" t="n">
-        <v>73.33</v>
+        <v>12.26</v>
       </c>
       <c r="H451" s="2" t="inlineStr"/>
       <c r="I451" s="2" t="inlineStr"/>
@@ -31484,62 +31484,60 @@
         <v>9</v>
       </c>
       <c r="Q451" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R451" s="2" t="inlineStr"/>
       <c r="S451" s="2" t="inlineStr"/>
       <c r="T451" s="2" t="inlineStr"/>
-      <c r="U451" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
+      <c r="U451" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V451" s="2" t="inlineStr"/>
       <c r="W451" s="2" t="inlineStr"/>
       <c r="X451" s="2" t="inlineStr"/>
       <c r="Y451" s="2" t="n">
-        <v>8.52</v>
+        <v>-36.57</v>
       </c>
       <c r="Z451" s="2" t="n">
-        <v>-11.42</v>
+        <v>-24.35</v>
       </c>
       <c r="AA451" s="2" t="n">
-        <v>-6.76</v>
+        <v>-15.17</v>
       </c>
       <c r="AB451" s="2" t="n">
-        <v>-1.22</v>
+        <v>-2.42</v>
       </c>
       <c r="AC451" s="2" t="n">
-        <v>-6.77</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>WYNN US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C452" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>75.72</v>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-2.13</v>
+        <v>0.57</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>-10.3</v>
+        <v>-4.2</v>
       </c>
       <c r="G452" s="2" t="n">
-        <v>12.26</v>
+        <v>-4.88</v>
       </c>
       <c r="H452" s="2" t="inlineStr"/>
       <c r="I452" s="2" t="inlineStr"/>
@@ -31549,11 +31547,9 @@
       <c r="M452" s="2" t="inlineStr"/>
       <c r="N452" s="2" t="inlineStr"/>
       <c r="O452" s="2" t="inlineStr"/>
-      <c r="P452" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P452" s="2" t="inlineStr"/>
       <c r="Q452" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R452" s="2" t="inlineStr"/>
       <c r="S452" s="2" t="inlineStr"/>
@@ -31565,188 +31561,190 @@
       <c r="W452" s="2" t="inlineStr"/>
       <c r="X452" s="2" t="inlineStr"/>
       <c r="Y452" s="2" t="n">
-        <v>-36.57</v>
+        <v>-5.25</v>
       </c>
       <c r="Z452" s="2" t="n">
-        <v>-24.35</v>
+        <v>-11.16</v>
       </c>
       <c r="AA452" s="2" t="n">
-        <v>-15.17</v>
+        <v>-0.28</v>
       </c>
       <c r="AB452" s="2" t="n">
-        <v>-2.42</v>
+        <v>-0.78</v>
       </c>
       <c r="AC452" s="2" t="n">
-        <v>-6.35</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>XOM US</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C453" s="2" t="n">
-        <v>75.72</v>
+        <v>159.47</v>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>0.57</v>
+        <v>3.08</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>-4.2</v>
+        <v>5.8</v>
       </c>
       <c r="G453" s="2" t="n">
-        <v>-4.88</v>
+        <v>110.23</v>
       </c>
       <c r="H453" s="2" t="inlineStr"/>
-      <c r="I453" s="2" t="inlineStr"/>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J453" s="2" t="inlineStr"/>
       <c r="K453" s="2" t="inlineStr"/>
       <c r="L453" s="2" t="inlineStr"/>
-      <c r="M453" s="2" t="inlineStr"/>
+      <c r="M453" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N453" s="2" t="inlineStr"/>
       <c r="O453" s="2" t="inlineStr"/>
       <c r="P453" s="2" t="inlineStr"/>
       <c r="Q453" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R453" s="2" t="inlineStr"/>
       <c r="S453" s="2" t="inlineStr"/>
       <c r="T453" s="2" t="inlineStr"/>
-      <c r="U453" s="2" t="n">
-        <v>1</v>
+      <c r="U453" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="V453" s="2" t="inlineStr"/>
-      <c r="W453" s="2" t="inlineStr"/>
+      <c r="W453" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X453" s="2" t="inlineStr"/>
       <c r="Y453" s="2" t="n">
-        <v>-5.25</v>
+        <v>42.57</v>
       </c>
       <c r="Z453" s="2" t="n">
-        <v>-11.16</v>
+        <v>6.89</v>
       </c>
       <c r="AA453" s="2" t="n">
-        <v>-0.28</v>
+        <v>-4.93</v>
       </c>
       <c r="AB453" s="2" t="n">
-        <v>-0.78</v>
+        <v>1.32</v>
       </c>
       <c r="AC453" s="2" t="n">
-        <v>-1.7</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>XOM US</t>
+          <t>XYL US</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C454" s="2" t="n">
-        <v>159.47</v>
+        <v>105.69</v>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>3.08</v>
+        <v>-2.74</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>5.8</v>
+        <v>-10.8</v>
       </c>
       <c r="G454" s="2" t="n">
-        <v>110.23</v>
+        <v>-11.99</v>
       </c>
       <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I454" s="2" t="inlineStr"/>
       <c r="J454" s="2" t="inlineStr"/>
       <c r="K454" s="2" t="inlineStr"/>
       <c r="L454" s="2" t="inlineStr"/>
-      <c r="M454" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M454" s="2" t="inlineStr"/>
       <c r="N454" s="2" t="inlineStr"/>
       <c r="O454" s="2" t="inlineStr"/>
-      <c r="P454" s="2" t="inlineStr"/>
+      <c r="P454" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q454" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R454" s="2" t="inlineStr"/>
       <c r="S454" s="2" t="inlineStr"/>
       <c r="T454" s="2" t="inlineStr"/>
-      <c r="U454" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="U454" s="2" t="n">
+        <v>-1</v>
       </c>
       <c r="V454" s="2" t="inlineStr"/>
-      <c r="W454" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="W454" s="2" t="inlineStr"/>
       <c r="X454" s="2" t="inlineStr"/>
       <c r="Y454" s="2" t="n">
-        <v>42.57</v>
+        <v>-38.35</v>
       </c>
       <c r="Z454" s="2" t="n">
-        <v>6.89</v>
+        <v>-24.81</v>
       </c>
       <c r="AA454" s="2" t="n">
-        <v>-4.93</v>
+        <v>-22.17</v>
       </c>
       <c r="AB454" s="2" t="n">
-        <v>1.32</v>
+        <v>-3.42</v>
       </c>
       <c r="AC454" s="2" t="n">
-        <v>3.61</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>XYL US</t>
+          <t>XYZ US</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C455" s="2" t="n">
-        <v>105.69</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>-2.74</v>
+        <v>2.98</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>-10.8</v>
+        <v>17.9</v>
       </c>
       <c r="G455" s="2" t="n">
-        <v>-11.97</v>
+        <v>70.94</v>
       </c>
       <c r="H455" s="2" t="inlineStr"/>
       <c r="I455" s="2" t="inlineStr"/>
@@ -31756,64 +31754,64 @@
       <c r="M455" s="2" t="inlineStr"/>
       <c r="N455" s="2" t="inlineStr"/>
       <c r="O455" s="2" t="inlineStr"/>
-      <c r="P455" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P455" s="2" t="inlineStr"/>
       <c r="Q455" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R455" s="2" t="inlineStr"/>
       <c r="S455" s="2" t="inlineStr"/>
       <c r="T455" s="2" t="inlineStr"/>
       <c r="U455" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V455" s="2" t="inlineStr"/>
+      <c r="W455" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V455" s="2" t="inlineStr"/>
-      <c r="W455" s="2" t="inlineStr"/>
       <c r="X455" s="2" t="inlineStr"/>
       <c r="Y455" s="2" t="n">
-        <v>-38.35</v>
+        <v>36.21</v>
       </c>
       <c r="Z455" s="2" t="n">
-        <v>-24.81</v>
+        <v>8.18</v>
       </c>
       <c r="AA455" s="2" t="n">
-        <v>-22.17</v>
+        <v>8.24</v>
       </c>
       <c r="AB455" s="2" t="n">
-        <v>-3.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AC455" s="2" t="n">
-        <v>-7.15</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>XYZ US</t>
+          <t>YUM US</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C456" s="2" t="n">
-        <v>82.76000000000001</v>
+        <v>150.71</v>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>2.98</v>
+        <v>-0.2</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>17.9</v>
+        <v>-2.9</v>
       </c>
       <c r="G456" s="2" t="n">
-        <v>70.94</v>
+        <v>12.54</v>
       </c>
       <c r="H456" s="2" t="inlineStr"/>
       <c r="I456" s="2" t="inlineStr"/>
@@ -31823,64 +31821,66 @@
       <c r="M456" s="2" t="inlineStr"/>
       <c r="N456" s="2" t="inlineStr"/>
       <c r="O456" s="2" t="inlineStr"/>
-      <c r="P456" s="2" t="inlineStr"/>
+      <c r="P456" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="Q456" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R456" s="2" t="inlineStr"/>
       <c r="S456" s="2" t="inlineStr"/>
       <c r="T456" s="2" t="inlineStr"/>
-      <c r="U456" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V456" s="2" t="inlineStr"/>
-      <c r="W456" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U456" s="2" t="inlineStr"/>
+      <c r="V456" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="W456" s="2" t="inlineStr"/>
       <c r="X456" s="2" t="inlineStr"/>
       <c r="Y456" s="2" t="n">
-        <v>36.21</v>
+        <v>3.97</v>
       </c>
       <c r="Z456" s="2" t="n">
-        <v>8.18</v>
+        <v>-9.77</v>
       </c>
       <c r="AA456" s="2" t="n">
-        <v>8.24</v>
+        <v>0.67</v>
       </c>
       <c r="AB456" s="2" t="n">
-        <v>-0.85</v>
+        <v>-1.77</v>
       </c>
       <c r="AC456" s="2" t="n">
-        <v>6.51</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>YUM US</t>
+          <t>ZBRA US</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C457" s="2" t="n">
-        <v>150.71</v>
+        <v>362.74</v>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>-0.2</v>
+        <v>6.31</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>-2.9</v>
+        <v>39.9</v>
       </c>
       <c r="G457" s="2" t="n">
-        <v>12.54</v>
+        <v>102.22</v>
       </c>
       <c r="H457" s="2" t="inlineStr"/>
       <c r="I457" s="2" t="inlineStr"/>
@@ -31889,67 +31889,65 @@
       <c r="L457" s="2" t="inlineStr"/>
       <c r="M457" s="2" t="inlineStr"/>
       <c r="N457" s="2" t="inlineStr"/>
-      <c r="O457" s="2" t="inlineStr"/>
-      <c r="P457" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="O457" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P457" s="2" t="inlineStr"/>
       <c r="Q457" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R457" s="2" t="inlineStr"/>
       <c r="S457" s="2" t="inlineStr"/>
       <c r="T457" s="2" t="inlineStr"/>
-      <c r="U457" s="2" t="inlineStr"/>
-      <c r="V457" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U457" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V457" s="2" t="inlineStr"/>
       <c r="W457" s="2" t="inlineStr"/>
       <c r="X457" s="2" t="inlineStr"/>
       <c r="Y457" s="2" t="n">
-        <v>3.97</v>
+        <v>55.46</v>
       </c>
       <c r="Z457" s="2" t="n">
-        <v>-9.77</v>
+        <v>25.4</v>
       </c>
       <c r="AA457" s="2" t="n">
-        <v>0.67</v>
+        <v>13.57</v>
       </c>
       <c r="AB457" s="2" t="n">
-        <v>-1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AC457" s="2" t="n">
-        <v>1.31</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>ZBRA US</t>
+          <t>ZTS US</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C458" s="2" t="n">
-        <v>362.74</v>
+        <v>75.81</v>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>6.31</v>
+        <v>-6.24</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>39.9</v>
+        <v>-20.6</v>
       </c>
       <c r="G458" s="2" t="n">
-        <v>102.22</v>
+        <v>76.98</v>
       </c>
       <c r="H458" s="2" t="inlineStr"/>
       <c r="I458" s="2" t="inlineStr"/>
@@ -31958,9 +31956,7 @@
       <c r="L458" s="2" t="inlineStr"/>
       <c r="M458" s="2" t="inlineStr"/>
       <c r="N458" s="2" t="inlineStr"/>
-      <c r="O458" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O458" s="2" t="inlineStr"/>
       <c r="P458" s="2" t="inlineStr"/>
       <c r="Q458" s="2" t="n">
         <v>0</v>
@@ -31968,55 +31964,57 @@
       <c r="R458" s="2" t="inlineStr"/>
       <c r="S458" s="2" t="inlineStr"/>
       <c r="T458" s="2" t="inlineStr"/>
-      <c r="U458" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V458" s="2" t="inlineStr"/>
+      <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W458" s="2" t="inlineStr"/>
       <c r="X458" s="2" t="inlineStr"/>
       <c r="Y458" s="2" t="n">
-        <v>55.46</v>
+        <v>-53.02</v>
       </c>
       <c r="Z458" s="2" t="n">
-        <v>25.4</v>
+        <v>-37.6</v>
       </c>
       <c r="AA458" s="2" t="n">
-        <v>13.57</v>
+        <v>-39.49</v>
       </c>
       <c r="AB458" s="2" t="n">
-        <v>2.22</v>
+        <v>-0.26</v>
       </c>
       <c r="AC458" s="2" t="n">
-        <v>-3.54</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>ZTS US</t>
+          <t>ABBV US</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C459" s="2" t="n">
-        <v>75.81</v>
+        <v>256.46</v>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>-6.24</v>
+        <v>2.45</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>-20.6</v>
+        <v>12.6</v>
       </c>
       <c r="G459" s="2" t="n">
-        <v>76.98</v>
+        <v>81.87</v>
       </c>
       <c r="H459" s="2" t="inlineStr"/>
       <c r="I459" s="2" t="inlineStr"/>
@@ -32034,42 +32032,38 @@
       <c r="S459" s="2" t="inlineStr"/>
       <c r="T459" s="2" t="inlineStr"/>
       <c r="U459" s="2" t="inlineStr"/>
-      <c r="V459" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="V459" s="2" t="inlineStr"/>
       <c r="W459" s="2" t="inlineStr"/>
       <c r="X459" s="2" t="inlineStr"/>
       <c r="Y459" s="2" t="n">
-        <v>-53.02</v>
+        <v>19.01</v>
       </c>
       <c r="Z459" s="2" t="n">
-        <v>-37.6</v>
+        <v>4.37</v>
       </c>
       <c r="AA459" s="2" t="n">
-        <v>-39.49</v>
+        <v>1.14</v>
       </c>
       <c r="AB459" s="2" t="n">
-        <v>-0.26</v>
+        <v>0.18</v>
       </c>
       <c r="AC459" s="2" t="n">
-        <v>6.69</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>ABBV US</t>
+          <t>ABNB US</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C460" s="2" t="n">
-        <v>256.46</v>
+        <v>181.94</v>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
@@ -32077,13 +32071,13 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>2.45</v>
+        <v>4.97</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>12.6</v>
+        <v>27.4</v>
       </c>
       <c r="G460" s="2" t="n">
-        <v>81.87</v>
+        <v>103.21</v>
       </c>
       <c r="H460" s="2" t="inlineStr"/>
       <c r="I460" s="2" t="inlineStr"/>
@@ -32095,7 +32089,7 @@
       <c r="O460" s="2" t="inlineStr"/>
       <c r="P460" s="2" t="inlineStr"/>
       <c r="Q460" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R460" s="2" t="inlineStr"/>
       <c r="S460" s="2" t="inlineStr"/>
@@ -32105,48 +32099,48 @@
       <c r="W460" s="2" t="inlineStr"/>
       <c r="X460" s="2" t="inlineStr"/>
       <c r="Y460" s="2" t="n">
-        <v>19.01</v>
+        <v>58.69</v>
       </c>
       <c r="Z460" s="2" t="n">
-        <v>4.37</v>
+        <v>22.4</v>
       </c>
       <c r="AA460" s="2" t="n">
-        <v>1.14</v>
+        <v>35.97</v>
       </c>
       <c r="AB460" s="2" t="n">
-        <v>0.18</v>
+        <v>-5.69</v>
       </c>
       <c r="AC460" s="2" t="n">
-        <v>4.17</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>ABNB US</t>
+          <t>ACGL US</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Arch Capital Group</t>
         </is>
       </c>
       <c r="C461" s="2" t="n">
-        <v>181.94</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>4.97</v>
+        <v>0.75</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>27.4</v>
+        <v>1.3</v>
       </c>
       <c r="G461" s="2" t="n">
-        <v>103.21</v>
+        <v>3.36</v>
       </c>
       <c r="H461" s="2" t="inlineStr"/>
       <c r="I461" s="2" t="inlineStr"/>
@@ -32158,7 +32152,7 @@
       <c r="O461" s="2" t="inlineStr"/>
       <c r="P461" s="2" t="inlineStr"/>
       <c r="Q461" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R461" s="2" t="inlineStr"/>
       <c r="S461" s="2" t="inlineStr"/>
@@ -32168,48 +32162,48 @@
       <c r="W461" s="2" t="inlineStr"/>
       <c r="X461" s="2" t="inlineStr"/>
       <c r="Y461" s="2" t="n">
-        <v>58.69</v>
+        <v>9.02</v>
       </c>
       <c r="Z461" s="2" t="n">
-        <v>22.4</v>
+        <v>-5.57</v>
       </c>
       <c r="AA461" s="2" t="n">
-        <v>35.97</v>
+        <v>-5.53</v>
       </c>
       <c r="AB461" s="2" t="n">
-        <v>-5.69</v>
+        <v>-0.6</v>
       </c>
       <c r="AC461" s="2" t="n">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>ACGL US</t>
+          <t>ADM US</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Arch Capital Group</t>
+          <t>Archer Daniels Midland</t>
         </is>
       </c>
       <c r="C462" s="2" t="n">
-        <v>98.09999999999999</v>
+        <v>84.61</v>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>0.75</v>
+        <v>3.3</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>1.3</v>
+        <v>12.7</v>
       </c>
       <c r="G462" s="2" t="n">
-        <v>3.36</v>
+        <v>40.7</v>
       </c>
       <c r="H462" s="2" t="inlineStr"/>
       <c r="I462" s="2" t="inlineStr"/>
@@ -32231,48 +32225,48 @@
       <c r="W462" s="2" t="inlineStr"/>
       <c r="X462" s="2" t="inlineStr"/>
       <c r="Y462" s="2" t="n">
-        <v>9.02</v>
+        <v>50.43</v>
       </c>
       <c r="Z462" s="2" t="n">
-        <v>-5.57</v>
+        <v>12.73</v>
       </c>
       <c r="AA462" s="2" t="n">
-        <v>-5.53</v>
+        <v>18.76</v>
       </c>
       <c r="AB462" s="2" t="n">
-        <v>-0.6</v>
+        <v>3.64</v>
       </c>
       <c r="AC462" s="2" t="n">
-        <v>0.85</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>ADM US</t>
+          <t>ALNY US</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Archer Daniels Midland</t>
+          <t>Alnylam Pharmaceuticals</t>
         </is>
       </c>
       <c r="C463" s="2" t="n">
-        <v>84.61</v>
+        <v>266.11</v>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>3.3</v>
+        <v>-5.77</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>12.7</v>
+        <v>-9.4</v>
       </c>
       <c r="G463" s="2" t="n">
-        <v>40.7</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H463" s="2" t="inlineStr"/>
       <c r="I463" s="2" t="inlineStr"/>
@@ -32288,54 +32282,56 @@
       </c>
       <c r="R463" s="2" t="inlineStr"/>
       <c r="S463" s="2" t="inlineStr"/>
-      <c r="T463" s="2" t="inlineStr"/>
+      <c r="T463" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U463" s="2" t="inlineStr"/>
       <c r="V463" s="2" t="inlineStr"/>
       <c r="W463" s="2" t="inlineStr"/>
       <c r="X463" s="2" t="inlineStr"/>
       <c r="Y463" s="2" t="n">
-        <v>50.43</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="Z463" s="2" t="n">
-        <v>12.73</v>
+        <v>-31.27</v>
       </c>
       <c r="AA463" s="2" t="n">
-        <v>18.76</v>
+        <v>-33.44</v>
       </c>
       <c r="AB463" s="2" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AC463" s="2" t="n">
-        <v>10.69</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>ALNY US</t>
+          <t>AMCR US</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C464" s="2" t="n">
-        <v>266.11</v>
+        <v>45.15</v>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>-5.77</v>
+        <v>1.52</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>-9.4</v>
+        <v>7.9</v>
       </c>
       <c r="G464" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>96.45</v>
       </c>
       <c r="H464" s="2" t="inlineStr"/>
       <c r="I464" s="2" t="inlineStr"/>
@@ -32351,56 +32347,54 @@
       </c>
       <c r="R464" s="2" t="inlineStr"/>
       <c r="S464" s="2" t="inlineStr"/>
-      <c r="T464" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="T464" s="2" t="inlineStr"/>
       <c r="U464" s="2" t="inlineStr"/>
       <c r="V464" s="2" t="inlineStr"/>
       <c r="W464" s="2" t="inlineStr"/>
       <c r="X464" s="2" t="inlineStr"/>
       <c r="Y464" s="2" t="n">
-        <v>-78.43000000000001</v>
+        <v>17.01</v>
       </c>
       <c r="Z464" s="2" t="n">
-        <v>-31.27</v>
+        <v>0.75</v>
       </c>
       <c r="AA464" s="2" t="n">
-        <v>-33.44</v>
+        <v>2.01</v>
       </c>
       <c r="AB464" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>-1.95</v>
       </c>
       <c r="AC464" s="2" t="n">
-        <v>15.65</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>AMCR US</t>
+          <t>AON US</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C465" s="2" t="n">
-        <v>45.15</v>
+        <v>323.09</v>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>1.52</v>
+        <v>0.21</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>7.9</v>
+        <v>-2.9</v>
       </c>
       <c r="G465" s="2" t="n">
-        <v>96.45</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H465" s="2" t="inlineStr"/>
       <c r="I465" s="2" t="inlineStr"/>
@@ -32422,48 +32416,48 @@
       <c r="W465" s="2" t="inlineStr"/>
       <c r="X465" s="2" t="inlineStr"/>
       <c r="Y465" s="2" t="n">
-        <v>17.01</v>
+        <v>-8.5</v>
       </c>
       <c r="Z465" s="2" t="n">
-        <v>0.75</v>
+        <v>-13.1</v>
       </c>
       <c r="AA465" s="2" t="n">
-        <v>2.01</v>
+        <v>-12.92</v>
       </c>
       <c r="AB465" s="2" t="n">
-        <v>-1.95</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AC465" s="2" t="n">
-        <v>-3.43</v>
+        <v>-7.13</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>AON US</t>
+          <t>APP US</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="C466" s="2" t="n">
-        <v>323.09</v>
+        <v>320.56</v>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>0.21</v>
+        <v>-7.62</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>-2.9</v>
+        <v>-27</v>
       </c>
       <c r="G466" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="H466" s="2" t="inlineStr"/>
       <c r="I466" s="2" t="inlineStr"/>
@@ -32485,48 +32479,48 @@
       <c r="W466" s="2" t="inlineStr"/>
       <c r="X466" s="2" t="inlineStr"/>
       <c r="Y466" s="2" t="n">
-        <v>-8.5</v>
+        <v>-66.33</v>
       </c>
       <c r="Z466" s="2" t="n">
-        <v>-13.1</v>
+        <v>-43.25</v>
       </c>
       <c r="AA466" s="2" t="n">
-        <v>-12.92</v>
+        <v>-49</v>
       </c>
       <c r="AB466" s="2" t="n">
-        <v>-8.210000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AC466" s="2" t="n">
-        <v>-7.13</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>APP US</t>
+          <t>ARE US</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>Alexandria Real Estate Equities</t>
         </is>
       </c>
       <c r="C467" s="2" t="n">
-        <v>320.56</v>
+        <v>52.65</v>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>-7.62</v>
+        <v>-0.76</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>-27</v>
+        <v>7.3</v>
       </c>
       <c r="G467" s="2" t="n">
-        <v>-8.69</v>
+        <v>5.27</v>
       </c>
       <c r="H467" s="2" t="inlineStr"/>
       <c r="I467" s="2" t="inlineStr"/>
@@ -32548,48 +32542,48 @@
       <c r="W467" s="2" t="inlineStr"/>
       <c r="X467" s="2" t="inlineStr"/>
       <c r="Y467" s="2" t="n">
-        <v>-66.33</v>
+        <v>4.33</v>
       </c>
       <c r="Z467" s="2" t="n">
-        <v>-43.25</v>
+        <v>-10.72</v>
       </c>
       <c r="AA467" s="2" t="n">
-        <v>-49</v>
+        <v>-5.9</v>
       </c>
       <c r="AB467" s="2" t="n">
-        <v>0.96</v>
+        <v>2.91</v>
       </c>
       <c r="AC467" s="2" t="n">
-        <v>-2.41</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>ARE US</t>
+          <t>AXON US</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate Equities</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C468" s="2" t="n">
-        <v>52.65</v>
+        <v>515.67</v>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="G468" s="2" t="n">
-        <v>5.27</v>
+        <v>87.58</v>
       </c>
       <c r="H468" s="2" t="inlineStr"/>
       <c r="I468" s="2" t="inlineStr"/>
@@ -32611,48 +32605,48 @@
       <c r="W468" s="2" t="inlineStr"/>
       <c r="X468" s="2" t="inlineStr"/>
       <c r="Y468" s="2" t="n">
-        <v>4.33</v>
+        <v>-7.75</v>
       </c>
       <c r="Z468" s="2" t="n">
-        <v>-10.72</v>
+        <v>-14.2</v>
       </c>
       <c r="AA468" s="2" t="n">
-        <v>-5.9</v>
+        <v>-11.41</v>
       </c>
       <c r="AB468" s="2" t="n">
-        <v>2.91</v>
+        <v>-13.07</v>
       </c>
       <c r="AC468" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>AXON US</t>
+          <t>BXP US</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C469" s="2" t="n">
-        <v>515.67</v>
+        <v>67.69</v>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>-0.25</v>
+        <v>0.8</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>6.8</v>
+        <v>10.4</v>
       </c>
       <c r="G469" s="2" t="n">
-        <v>87.58</v>
+        <v>8.73</v>
       </c>
       <c r="H469" s="2" t="inlineStr"/>
       <c r="I469" s="2" t="inlineStr"/>
@@ -32664,7 +32658,7 @@
       <c r="O469" s="2" t="inlineStr"/>
       <c r="P469" s="2" t="inlineStr"/>
       <c r="Q469" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R469" s="2" t="inlineStr"/>
       <c r="S469" s="2" t="inlineStr"/>
@@ -32674,48 +32668,48 @@
       <c r="W469" s="2" t="inlineStr"/>
       <c r="X469" s="2" t="inlineStr"/>
       <c r="Y469" s="2" t="n">
-        <v>-7.75</v>
+        <v>-1.91</v>
       </c>
       <c r="Z469" s="2" t="n">
-        <v>-14.2</v>
+        <v>-3.99</v>
       </c>
       <c r="AA469" s="2" t="n">
-        <v>-11.41</v>
+        <v>0.93</v>
       </c>
       <c r="AB469" s="2" t="n">
-        <v>-13.07</v>
+        <v>-1.97</v>
       </c>
       <c r="AC469" s="2" t="n">
-        <v>-4.75</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>BXP US</t>
+          <t>CCEP US</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Coca-Cola Europacific Partners</t>
         </is>
       </c>
       <c r="C470" s="2" t="n">
-        <v>67.69</v>
+        <v>105.76</v>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>0.8</v>
+        <v>2.68</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>10.4</v>
+        <v>6.1</v>
       </c>
       <c r="G470" s="2" t="n">
-        <v>8.73</v>
+        <v>69.25</v>
       </c>
       <c r="H470" s="2" t="inlineStr"/>
       <c r="I470" s="2" t="inlineStr"/>
@@ -32727,7 +32721,7 @@
       <c r="O470" s="2" t="inlineStr"/>
       <c r="P470" s="2" t="inlineStr"/>
       <c r="Q470" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R470" s="2" t="inlineStr"/>
       <c r="S470" s="2" t="inlineStr"/>
@@ -32737,34 +32731,34 @@
       <c r="W470" s="2" t="inlineStr"/>
       <c r="X470" s="2" t="inlineStr"/>
       <c r="Y470" s="2" t="n">
-        <v>-1.91</v>
+        <v>23.94</v>
       </c>
       <c r="Z470" s="2" t="n">
-        <v>-3.99</v>
+        <v>1.59</v>
       </c>
       <c r="AA470" s="2" t="n">
-        <v>0.93</v>
+        <v>7.13</v>
       </c>
       <c r="AB470" s="2" t="n">
-        <v>-1.97</v>
+        <v>-3.42</v>
       </c>
       <c r="AC470" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>CCEP US</t>
+          <t>CHD US</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C471" s="2" t="n">
-        <v>105.76</v>
+        <v>98.55</v>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
@@ -32772,13 +32766,13 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>2.68</v>
+        <v>1.66</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="G471" s="2" t="n">
-        <v>69.25</v>
+        <v>81.45</v>
       </c>
       <c r="H471" s="2" t="inlineStr"/>
       <c r="I471" s="2" t="inlineStr"/>
@@ -32790,7 +32784,7 @@
       <c r="O471" s="2" t="inlineStr"/>
       <c r="P471" s="2" t="inlineStr"/>
       <c r="Q471" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R471" s="2" t="inlineStr"/>
       <c r="S471" s="2" t="inlineStr"/>
@@ -32800,48 +32794,48 @@
       <c r="W471" s="2" t="inlineStr"/>
       <c r="X471" s="2" t="inlineStr"/>
       <c r="Y471" s="2" t="n">
-        <v>23.94</v>
+        <v>21.45</v>
       </c>
       <c r="Z471" s="2" t="n">
-        <v>1.59</v>
+        <v>-3.1</v>
       </c>
       <c r="AA471" s="2" t="n">
-        <v>7.13</v>
+        <v>2.26</v>
       </c>
       <c r="AB471" s="2" t="n">
-        <v>-3.42</v>
+        <v>-2.55</v>
       </c>
       <c r="AC471" s="2" t="n">
-        <v>-2.07</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CHD US</t>
+          <t>CIEN US</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C472" s="2" t="n">
-        <v>98.55</v>
+        <v>321</v>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>1.66</v>
+        <v>4.84</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>1.2</v>
+        <v>-25</v>
       </c>
       <c r="G472" s="2" t="n">
-        <v>81.45</v>
+        <v>59.47</v>
       </c>
       <c r="H472" s="2" t="inlineStr"/>
       <c r="I472" s="2" t="inlineStr"/>
@@ -32863,34 +32857,34 @@
       <c r="W472" s="2" t="inlineStr"/>
       <c r="X472" s="2" t="inlineStr"/>
       <c r="Y472" s="2" t="n">
-        <v>21.45</v>
+        <v>51.59</v>
       </c>
       <c r="Z472" s="2" t="n">
-        <v>-3.1</v>
+        <v>-10.9</v>
       </c>
       <c r="AA472" s="2" t="n">
-        <v>2.26</v>
+        <v>-18.04</v>
       </c>
       <c r="AB472" s="2" t="n">
-        <v>-2.55</v>
+        <v>-17.39</v>
       </c>
       <c r="AC472" s="2" t="n">
-        <v>-3.04</v>
+        <v>-32.22</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>CIEN US</t>
+          <t>CL US</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C473" s="2" t="n">
-        <v>321</v>
+        <v>88.77</v>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
@@ -32898,13 +32892,13 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>4.84</v>
+        <v>1.39</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>-25</v>
+        <v>-0.8</v>
       </c>
       <c r="G473" s="2" t="n">
-        <v>59.47</v>
+        <v>-5.2</v>
       </c>
       <c r="H473" s="2" t="inlineStr"/>
       <c r="I473" s="2" t="inlineStr"/>
@@ -32916,7 +32910,7 @@
       <c r="O473" s="2" t="inlineStr"/>
       <c r="P473" s="2" t="inlineStr"/>
       <c r="Q473" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R473" s="2" t="inlineStr"/>
       <c r="S473" s="2" t="inlineStr"/>
@@ -32926,48 +32920,48 @@
       <c r="W473" s="2" t="inlineStr"/>
       <c r="X473" s="2" t="inlineStr"/>
       <c r="Y473" s="2" t="n">
-        <v>51.59</v>
+        <v>18.54</v>
       </c>
       <c r="Z473" s="2" t="n">
-        <v>-10.9</v>
+        <v>-4.65</v>
       </c>
       <c r="AA473" s="2" t="n">
-        <v>-18.04</v>
+        <v>0.62</v>
       </c>
       <c r="AB473" s="2" t="n">
-        <v>-17.39</v>
+        <v>-2.05</v>
       </c>
       <c r="AC473" s="2" t="n">
-        <v>-32.22</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CL US</t>
+          <t>CMCSA US</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C474" s="2" t="n">
-        <v>88.77</v>
+        <v>26.49</v>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>1.39</v>
+        <v>-0.66</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="G474" s="2" t="n">
-        <v>-5.2</v>
+        <v>117.36</v>
       </c>
       <c r="H474" s="2" t="inlineStr"/>
       <c r="I474" s="2" t="inlineStr"/>
@@ -32979,7 +32973,7 @@
       <c r="O474" s="2" t="inlineStr"/>
       <c r="P474" s="2" t="inlineStr"/>
       <c r="Q474" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R474" s="2" t="inlineStr"/>
       <c r="S474" s="2" t="inlineStr"/>
@@ -32989,48 +32983,48 @@
       <c r="W474" s="2" t="inlineStr"/>
       <c r="X474" s="2" t="inlineStr"/>
       <c r="Y474" s="2" t="n">
-        <v>18.54</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Z474" s="2" t="n">
-        <v>-4.65</v>
+        <v>-9.41</v>
       </c>
       <c r="AA474" s="2" t="n">
-        <v>0.62</v>
+        <v>1.33</v>
       </c>
       <c r="AB474" s="2" t="n">
-        <v>-2.05</v>
+        <v>-1.44</v>
       </c>
       <c r="AC474" s="2" t="n">
-        <v>-3.66</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>CMCSA US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C475" s="2" t="n">
-        <v>26.49</v>
+        <v>39.67</v>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>-0.66</v>
+        <v>0.48</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>0.1</v>
+        <v>-5.6</v>
       </c>
       <c r="G475" s="2" t="n">
-        <v>117.36</v>
+        <v>-12.14</v>
       </c>
       <c r="H475" s="2" t="inlineStr"/>
       <c r="I475" s="2" t="inlineStr"/>
@@ -33042,7 +33036,7 @@
       <c r="O475" s="2" t="inlineStr"/>
       <c r="P475" s="2" t="inlineStr"/>
       <c r="Q475" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R475" s="2" t="inlineStr"/>
       <c r="S475" s="2" t="inlineStr"/>
@@ -33052,34 +33046,34 @@
       <c r="W475" s="2" t="inlineStr"/>
       <c r="X475" s="2" t="inlineStr"/>
       <c r="Y475" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="Z475" s="2" t="n">
-        <v>-9.41</v>
+        <v>-10.48</v>
       </c>
       <c r="AA475" s="2" t="n">
-        <v>1.33</v>
+        <v>0.45</v>
       </c>
       <c r="AB475" s="2" t="n">
-        <v>-1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AC475" s="2" t="n">
-        <v>6.41</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>COST US</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C476" s="2" t="n">
-        <v>39.67</v>
+        <v>915.74</v>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
@@ -33087,13 +33081,13 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>-5.6</v>
+        <v>-6.2</v>
       </c>
       <c r="G476" s="2" t="n">
-        <v>-12.14</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="H476" s="2" t="inlineStr"/>
       <c r="I476" s="2" t="inlineStr"/>
@@ -33105,7 +33099,7 @@
       <c r="O476" s="2" t="inlineStr"/>
       <c r="P476" s="2" t="inlineStr"/>
       <c r="Q476" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R476" s="2" t="inlineStr"/>
       <c r="S476" s="2" t="inlineStr"/>
@@ -33115,48 +33109,48 @@
       <c r="W476" s="2" t="inlineStr"/>
       <c r="X476" s="2" t="inlineStr"/>
       <c r="Y476" s="2" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="Z476" s="2" t="n">
-        <v>-10.48</v>
+        <v>-12.36</v>
       </c>
       <c r="AA476" s="2" t="n">
-        <v>0.45</v>
+        <v>-7.51</v>
       </c>
       <c r="AB476" s="2" t="n">
-        <v>1.06</v>
+        <v>-2.6</v>
       </c>
       <c r="AC476" s="2" t="n">
-        <v>-0.51</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>COST US</t>
+          <t>CVS US</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C477" s="2" t="n">
-        <v>915.74</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>0.15</v>
+        <v>2.62</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>-6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G477" s="2" t="n">
-        <v>67.48999999999999</v>
+        <v>-20.52</v>
       </c>
       <c r="H477" s="2" t="inlineStr"/>
       <c r="I477" s="2" t="inlineStr"/>
@@ -33168,9 +33162,11 @@
       <c r="O477" s="2" t="inlineStr"/>
       <c r="P477" s="2" t="inlineStr"/>
       <c r="Q477" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R477" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R477" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S477" s="2" t="inlineStr"/>
       <c r="T477" s="2" t="inlineStr"/>
       <c r="U477" s="2" t="inlineStr"/>
@@ -33178,48 +33174,48 @@
       <c r="W477" s="2" t="inlineStr"/>
       <c r="X477" s="2" t="inlineStr"/>
       <c r="Y477" s="2" t="n">
-        <v>2.31</v>
+        <v>29.35</v>
       </c>
       <c r="Z477" s="2" t="n">
-        <v>-12.36</v>
+        <v>6.16</v>
       </c>
       <c r="AA477" s="2" t="n">
-        <v>-7.51</v>
+        <v>2.61</v>
       </c>
       <c r="AB477" s="2" t="n">
-        <v>-2.6</v>
+        <v>3.68</v>
       </c>
       <c r="AC477" s="2" t="n">
-        <v>-1.24</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>CVS US</t>
+          <t>DHR US</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C478" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>207.66</v>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>2.62</v>
+        <v>-1.57</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G478" s="2" t="n">
-        <v>-20.52</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="H478" s="2" t="inlineStr"/>
       <c r="I478" s="2" t="inlineStr"/>
@@ -33233,9 +33229,7 @@
       <c r="Q478" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R478" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="R478" s="2" t="inlineStr"/>
       <c r="S478" s="2" t="inlineStr"/>
       <c r="T478" s="2" t="inlineStr"/>
       <c r="U478" s="2" t="inlineStr"/>
@@ -33243,34 +33237,34 @@
       <c r="W478" s="2" t="inlineStr"/>
       <c r="X478" s="2" t="inlineStr"/>
       <c r="Y478" s="2" t="n">
-        <v>29.35</v>
+        <v>-5.5</v>
       </c>
       <c r="Z478" s="2" t="n">
-        <v>6.16</v>
+        <v>-6.83</v>
       </c>
       <c r="AA478" s="2" t="n">
-        <v>2.61</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="AB478" s="2" t="n">
-        <v>3.68</v>
+        <v>-3.6</v>
       </c>
       <c r="AC478" s="2" t="n">
-        <v>0.4</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>DHR US</t>
+          <t>DIS US</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C479" s="2" t="n">
-        <v>207.66</v>
+        <v>105.31</v>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
@@ -33278,13 +33272,13 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>-1.57</v>
+        <v>-0.67</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="G479" s="2" t="n">
-        <v>98.26000000000001</v>
+        <v>116.03</v>
       </c>
       <c r="H479" s="2" t="inlineStr"/>
       <c r="I479" s="2" t="inlineStr"/>
@@ -33296,7 +33290,7 @@
       <c r="O479" s="2" t="inlineStr"/>
       <c r="P479" s="2" t="inlineStr"/>
       <c r="Q479" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R479" s="2" t="inlineStr"/>
       <c r="S479" s="2" t="inlineStr"/>
@@ -33306,34 +33300,34 @@
       <c r="W479" s="2" t="inlineStr"/>
       <c r="X479" s="2" t="inlineStr"/>
       <c r="Y479" s="2" t="n">
-        <v>-5.5</v>
+        <v>-2.14</v>
       </c>
       <c r="Z479" s="2" t="n">
-        <v>-6.83</v>
+        <v>-8.66</v>
       </c>
       <c r="AA479" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>1.96</v>
       </c>
       <c r="AB479" s="2" t="n">
-        <v>-3.6</v>
+        <v>-1.99</v>
       </c>
       <c r="AC479" s="2" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>DIS US</t>
+          <t>DLTR US</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C480" s="2" t="n">
-        <v>105.31</v>
+        <v>131.42</v>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
@@ -33341,13 +33335,13 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>-0.67</v>
+        <v>0.01</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="G480" s="2" t="n">
-        <v>116.03</v>
+        <v>64.8</v>
       </c>
       <c r="H480" s="2" t="inlineStr"/>
       <c r="I480" s="2" t="inlineStr"/>
@@ -33359,7 +33353,7 @@
       <c r="O480" s="2" t="inlineStr"/>
       <c r="P480" s="2" t="inlineStr"/>
       <c r="Q480" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R480" s="2" t="inlineStr"/>
       <c r="S480" s="2" t="inlineStr"/>
@@ -33369,48 +33363,48 @@
       <c r="W480" s="2" t="inlineStr"/>
       <c r="X480" s="2" t="inlineStr"/>
       <c r="Y480" s="2" t="n">
-        <v>-2.14</v>
+        <v>28.78</v>
       </c>
       <c r="Z480" s="2" t="n">
-        <v>-8.66</v>
+        <v>6.13</v>
       </c>
       <c r="AA480" s="2" t="n">
-        <v>1.96</v>
+        <v>11.9</v>
       </c>
       <c r="AB480" s="2" t="n">
-        <v>-1.99</v>
+        <v>2.41</v>
       </c>
       <c r="AC480" s="2" t="n">
-        <v>2.69</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>DLTR US</t>
+          <t>DOC US</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Healthpeak Properties</t>
         </is>
       </c>
       <c r="C481" s="2" t="n">
-        <v>131.42</v>
+        <v>20.65</v>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E481" s="2" t="n">
-        <v>0.01</v>
+        <v>3.21</v>
       </c>
       <c r="F481" s="2" t="n">
-        <v>14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G481" s="2" t="n">
-        <v>64.8</v>
+        <v>-0.5</v>
       </c>
       <c r="H481" s="2" t="inlineStr"/>
       <c r="I481" s="2" t="inlineStr"/>
@@ -33422,7 +33416,7 @@
       <c r="O481" s="2" t="inlineStr"/>
       <c r="P481" s="2" t="inlineStr"/>
       <c r="Q481" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R481" s="2" t="inlineStr"/>
       <c r="S481" s="2" t="inlineStr"/>
@@ -33432,34 +33426,34 @@
       <c r="W481" s="2" t="inlineStr"/>
       <c r="X481" s="2" t="inlineStr"/>
       <c r="Y481" s="2" t="n">
-        <v>28.78</v>
+        <v>30.5</v>
       </c>
       <c r="Z481" s="2" t="n">
-        <v>6.13</v>
+        <v>4.99</v>
       </c>
       <c r="AA481" s="2" t="n">
-        <v>11.9</v>
+        <v>10.42</v>
       </c>
       <c r="AB481" s="2" t="n">
-        <v>2.41</v>
+        <v>-1.77</v>
       </c>
       <c r="AC481" s="2" t="n">
-        <v>1.21</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>DOC US</t>
+          <t>DVA US</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>Healthpeak Properties</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C482" s="2" t="n">
-        <v>20.65</v>
+        <v>183.99</v>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
@@ -33467,13 +33461,13 @@
         </is>
       </c>
       <c r="E482" s="2" t="n">
-        <v>3.21</v>
+        <v>5.46</v>
       </c>
       <c r="F482" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="G482" s="2" t="n">
-        <v>-0.5</v>
+        <v>-23.7</v>
       </c>
       <c r="H482" s="2" t="inlineStr"/>
       <c r="I482" s="2" t="inlineStr"/>
@@ -33495,48 +33489,48 @@
       <c r="W482" s="2" t="inlineStr"/>
       <c r="X482" s="2" t="inlineStr"/>
       <c r="Y482" s="2" t="n">
-        <v>30.5</v>
+        <v>46.27</v>
       </c>
       <c r="Z482" s="2" t="n">
-        <v>4.99</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AA482" s="2" t="n">
-        <v>10.42</v>
+        <v>4.24</v>
       </c>
       <c r="AB482" s="2" t="n">
-        <v>-1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AC482" s="2" t="n">
-        <v>-3.43</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>DVA US</t>
+          <t>ECHO US</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C483" s="2" t="n">
-        <v>183.99</v>
+        <v>89.8</v>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>5.46</v>
+        <v>-3.8</v>
       </c>
       <c r="F483" s="2" t="n">
-        <v>1.7</v>
+        <v>-17.9</v>
       </c>
       <c r="G483" s="2" t="n">
-        <v>-23.7</v>
+        <v>17.06</v>
       </c>
       <c r="H483" s="2" t="inlineStr"/>
       <c r="I483" s="2" t="inlineStr"/>
@@ -33548,7 +33542,7 @@
       <c r="O483" s="2" t="inlineStr"/>
       <c r="P483" s="2" t="inlineStr"/>
       <c r="Q483" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R483" s="2" t="inlineStr"/>
       <c r="S483" s="2" t="inlineStr"/>
@@ -33558,48 +33552,48 @@
       <c r="W483" s="2" t="inlineStr"/>
       <c r="X483" s="2" t="inlineStr"/>
       <c r="Y483" s="2" t="n">
-        <v>46.27</v>
+        <v>22.69</v>
       </c>
       <c r="Z483" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>-18.58</v>
       </c>
       <c r="AA483" s="2" t="n">
-        <v>4.24</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AB483" s="2" t="n">
-        <v>1.64</v>
+        <v>2.43</v>
       </c>
       <c r="AC483" s="2" t="n">
-        <v>-0.18</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>ECHO US</t>
+          <t>ECL US</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>89.8</v>
+        <v>279.28</v>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E484" s="2" t="n">
-        <v>-3.8</v>
+        <v>0.39</v>
       </c>
       <c r="F484" s="2" t="n">
-        <v>-17.9</v>
+        <v>2.1</v>
       </c>
       <c r="G484" s="2" t="n">
-        <v>17.06</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="H484" s="2" t="inlineStr"/>
       <c r="I484" s="2" t="inlineStr"/>
@@ -33611,7 +33605,7 @@
       <c r="O484" s="2" t="inlineStr"/>
       <c r="P484" s="2" t="inlineStr"/>
       <c r="Q484" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R484" s="2" t="inlineStr"/>
       <c r="S484" s="2" t="inlineStr"/>
@@ -33621,48 +33615,48 @@
       <c r="W484" s="2" t="inlineStr"/>
       <c r="X484" s="2" t="inlineStr"/>
       <c r="Y484" s="2" t="n">
-        <v>22.69</v>
+        <v>10.83</v>
       </c>
       <c r="Z484" s="2" t="n">
-        <v>-18.58</v>
+        <v>-6.04</v>
       </c>
       <c r="AA484" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>-4.89</v>
       </c>
       <c r="AB484" s="2" t="n">
-        <v>2.43</v>
+        <v>-2.31</v>
       </c>
       <c r="AC484" s="2" t="n">
-        <v>-2.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>ECL US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C485" s="2" t="n">
-        <v>279.28</v>
+        <v>56.77</v>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E485" s="2" t="n">
-        <v>0.39</v>
+        <v>1.66</v>
       </c>
       <c r="F485" s="2" t="n">
-        <v>2.1</v>
+        <v>-19.6</v>
       </c>
       <c r="G485" s="2" t="n">
-        <v>74.76000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="H485" s="2" t="inlineStr"/>
       <c r="I485" s="2" t="inlineStr"/>
@@ -33684,48 +33678,48 @@
       <c r="W485" s="2" t="inlineStr"/>
       <c r="X485" s="2" t="inlineStr"/>
       <c r="Y485" s="2" t="n">
-        <v>10.83</v>
+        <v>-0.05</v>
       </c>
       <c r="Z485" s="2" t="n">
-        <v>-6.04</v>
+        <v>-19.49</v>
       </c>
       <c r="AA485" s="2" t="n">
-        <v>-4.89</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AB485" s="2" t="n">
-        <v>-2.31</v>
+        <v>-18.92</v>
       </c>
       <c r="AC485" s="2" t="n">
-        <v>-0.3</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ESS US</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C486" s="2" t="n">
-        <v>56.77</v>
+        <v>278.61</v>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E486" s="2" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="F486" s="2" t="n">
-        <v>-19.6</v>
+        <v>3.9</v>
       </c>
       <c r="G486" s="2" t="n">
-        <v>2.13</v>
+        <v>3.29</v>
       </c>
       <c r="H486" s="2" t="inlineStr"/>
       <c r="I486" s="2" t="inlineStr"/>
@@ -33737,7 +33731,7 @@
       <c r="O486" s="2" t="inlineStr"/>
       <c r="P486" s="2" t="inlineStr"/>
       <c r="Q486" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R486" s="2" t="inlineStr"/>
       <c r="S486" s="2" t="inlineStr"/>
@@ -33747,48 +33741,48 @@
       <c r="W486" s="2" t="inlineStr"/>
       <c r="X486" s="2" t="inlineStr"/>
       <c r="Y486" s="2" t="n">
-        <v>-0.05</v>
+        <v>15.46</v>
       </c>
       <c r="Z486" s="2" t="n">
-        <v>-19.49</v>
+        <v>-2.67</v>
       </c>
       <c r="AA486" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="AB486" s="2" t="n">
-        <v>-18.92</v>
+        <v>-1.82</v>
       </c>
       <c r="AC486" s="2" t="n">
-        <v>-16.9</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>ESS US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C487" s="2" t="n">
-        <v>278.61</v>
+        <v>107.27</v>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E487" s="2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="F487" s="2" t="n">
-        <v>3.9</v>
+        <v>-1.2</v>
       </c>
       <c r="G487" s="2" t="n">
-        <v>3.29</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H487" s="2" t="inlineStr"/>
       <c r="I487" s="2" t="inlineStr"/>
@@ -33800,7 +33794,7 @@
       <c r="O487" s="2" t="inlineStr"/>
       <c r="P487" s="2" t="inlineStr"/>
       <c r="Q487" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R487" s="2" t="inlineStr"/>
       <c r="S487" s="2" t="inlineStr"/>
@@ -33810,48 +33804,48 @@
       <c r="W487" s="2" t="inlineStr"/>
       <c r="X487" s="2" t="inlineStr"/>
       <c r="Y487" s="2" t="n">
-        <v>15.46</v>
+        <v>16.6</v>
       </c>
       <c r="Z487" s="2" t="n">
-        <v>-2.67</v>
+        <v>-3.72</v>
       </c>
       <c r="AA487" s="2" t="n">
-        <v>2.37</v>
+        <v>7.91</v>
       </c>
       <c r="AB487" s="2" t="n">
-        <v>-1.82</v>
+        <v>1.19</v>
       </c>
       <c r="AC487" s="2" t="n">
-        <v>-2.35</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>EXPE US</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C488" s="2" t="n">
-        <v>107.27</v>
+        <v>298.04</v>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E488" s="2" t="n">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="F488" s="2" t="n">
-        <v>-1.2</v>
+        <v>18</v>
       </c>
       <c r="G488" s="2" t="n">
-        <v>-8.550000000000001</v>
+        <v>101.92</v>
       </c>
       <c r="H488" s="2" t="inlineStr"/>
       <c r="I488" s="2" t="inlineStr"/>
@@ -33873,48 +33867,48 @@
       <c r="W488" s="2" t="inlineStr"/>
       <c r="X488" s="2" t="inlineStr"/>
       <c r="Y488" s="2" t="n">
-        <v>16.6</v>
+        <v>22.81</v>
       </c>
       <c r="Z488" s="2" t="n">
-        <v>-3.72</v>
+        <v>8.69</v>
       </c>
       <c r="AA488" s="2" t="n">
-        <v>7.91</v>
+        <v>20.99</v>
       </c>
       <c r="AB488" s="2" t="n">
-        <v>1.19</v>
+        <v>-12.03</v>
       </c>
       <c r="AC488" s="2" t="n">
-        <v>0.95</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>EXPE US</t>
+          <t>FTV US</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C489" s="2" t="n">
-        <v>298.04</v>
+        <v>56.94</v>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E489" s="2" t="n">
-        <v>2.13</v>
+        <v>1.22</v>
       </c>
       <c r="F489" s="2" t="n">
-        <v>18</v>
+        <v>-3.9</v>
       </c>
       <c r="G489" s="2" t="n">
-        <v>101.92</v>
+        <v>6.83</v>
       </c>
       <c r="H489" s="2" t="inlineStr"/>
       <c r="I489" s="2" t="inlineStr"/>
@@ -33936,34 +33930,34 @@
       <c r="W489" s="2" t="inlineStr"/>
       <c r="X489" s="2" t="inlineStr"/>
       <c r="Y489" s="2" t="n">
-        <v>22.81</v>
+        <v>13.33</v>
       </c>
       <c r="Z489" s="2" t="n">
-        <v>8.69</v>
+        <v>-7.3</v>
       </c>
       <c r="AA489" s="2" t="n">
-        <v>20.99</v>
+        <v>-3.69</v>
       </c>
       <c r="AB489" s="2" t="n">
-        <v>-12.03</v>
+        <v>-4.48</v>
       </c>
       <c r="AC489" s="2" t="n">
-        <v>-6.36</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>FTV US</t>
+          <t>HLT US</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C490" s="2" t="n">
-        <v>56.94</v>
+        <v>311.18</v>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
@@ -33971,13 +33965,13 @@
         </is>
       </c>
       <c r="E490" s="2" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="F490" s="2" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G490" s="2" t="n">
-        <v>6.83</v>
+        <v>11.37</v>
       </c>
       <c r="H490" s="2" t="inlineStr"/>
       <c r="I490" s="2" t="inlineStr"/>
@@ -33999,52 +33993,56 @@
       <c r="W490" s="2" t="inlineStr"/>
       <c r="X490" s="2" t="inlineStr"/>
       <c r="Y490" s="2" t="n">
-        <v>13.33</v>
+        <v>17.86</v>
       </c>
       <c r="Z490" s="2" t="n">
-        <v>-7.3</v>
+        <v>-6.07</v>
       </c>
       <c r="AA490" s="2" t="n">
-        <v>-3.69</v>
+        <v>4.46</v>
       </c>
       <c r="AB490" s="2" t="n">
-        <v>-4.48</v>
+        <v>-3.22</v>
       </c>
       <c r="AC490" s="2" t="n">
-        <v>-7.48</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>HLT US</t>
+          <t>HWM US</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C491" s="2" t="n">
-        <v>311.18</v>
+        <v>259.27</v>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E491" s="2" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="F491" s="2" t="n">
-        <v>-3.1</v>
+        <v>0.4</v>
       </c>
       <c r="G491" s="2" t="n">
-        <v>11.37</v>
+        <v>4.33</v>
       </c>
       <c r="H491" s="2" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr"/>
-      <c r="J491" s="2" t="inlineStr"/>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K491" s="2" t="inlineStr"/>
       <c r="L491" s="2" t="inlineStr"/>
       <c r="M491" s="2" t="inlineStr"/>
@@ -34062,56 +34060,52 @@
       <c r="W491" s="2" t="inlineStr"/>
       <c r="X491" s="2" t="inlineStr"/>
       <c r="Y491" s="2" t="n">
-        <v>17.86</v>
+        <v>27.19</v>
       </c>
       <c r="Z491" s="2" t="n">
-        <v>-6.07</v>
+        <v>1.19</v>
       </c>
       <c r="AA491" s="2" t="n">
-        <v>4.46</v>
+        <v>5.3</v>
       </c>
       <c r="AB491" s="2" t="n">
-        <v>-3.22</v>
+        <v>-2.64</v>
       </c>
       <c r="AC491" s="2" t="n">
-        <v>-1.37</v>
+        <v>-10.41</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>HWM US</t>
+          <t>ICE US</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>259.27</v>
+        <v>161.26</v>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E492" s="2" t="n">
-        <v>2.96</v>
+        <v>-0.9</v>
       </c>
       <c r="F492" s="2" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="G492" s="2" t="n">
-        <v>4.33</v>
+        <v>115.88</v>
       </c>
       <c r="H492" s="2" t="inlineStr"/>
       <c r="I492" s="2" t="inlineStr"/>
-      <c r="J492" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J492" s="2" t="inlineStr"/>
       <c r="K492" s="2" t="inlineStr"/>
       <c r="L492" s="2" t="inlineStr"/>
       <c r="M492" s="2" t="inlineStr"/>
@@ -34129,48 +34123,48 @@
       <c r="W492" s="2" t="inlineStr"/>
       <c r="X492" s="2" t="inlineStr"/>
       <c r="Y492" s="2" t="n">
-        <v>27.19</v>
+        <v>8.49</v>
       </c>
       <c r="Z492" s="2" t="n">
-        <v>1.19</v>
+        <v>-5.65</v>
       </c>
       <c r="AA492" s="2" t="n">
-        <v>5.3</v>
+        <v>-5.45</v>
       </c>
       <c r="AB492" s="2" t="n">
-        <v>-2.64</v>
+        <v>-0.21</v>
       </c>
       <c r="AC492" s="2" t="n">
-        <v>-10.41</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>ICE US</t>
+          <t>INTU US</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>161.26</v>
+        <v>332.7</v>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E493" s="2" t="n">
-        <v>-0.9</v>
+        <v>-7.71</v>
       </c>
       <c r="F493" s="2" t="n">
-        <v>6</v>
+        <v>-7.3</v>
       </c>
       <c r="G493" s="2" t="n">
-        <v>115.88</v>
+        <v>115.64</v>
       </c>
       <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr"/>
@@ -34192,48 +34186,48 @@
       <c r="W493" s="2" t="inlineStr"/>
       <c r="X493" s="2" t="inlineStr"/>
       <c r="Y493" s="2" t="n">
-        <v>8.49</v>
+        <v>-91.27</v>
       </c>
       <c r="Z493" s="2" t="n">
-        <v>-5.65</v>
+        <v>-36.75</v>
       </c>
       <c r="AA493" s="2" t="n">
-        <v>-5.45</v>
+        <v>-43.71</v>
       </c>
       <c r="AB493" s="2" t="n">
-        <v>-0.21</v>
+        <v>-3.77</v>
       </c>
       <c r="AC493" s="2" t="n">
-        <v>9.02</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>INTU US</t>
+          <t>INVH US</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C494" s="2" t="n">
-        <v>332.7</v>
+        <v>28.39</v>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E494" s="2" t="n">
-        <v>-7.71</v>
+        <v>1.6</v>
       </c>
       <c r="F494" s="2" t="n">
-        <v>-7.3</v>
+        <v>2</v>
       </c>
       <c r="G494" s="2" t="n">
-        <v>115.64</v>
+        <v>-6.18</v>
       </c>
       <c r="H494" s="2" t="inlineStr"/>
       <c r="I494" s="2" t="inlineStr"/>
@@ -34255,48 +34249,48 @@
       <c r="W494" s="2" t="inlineStr"/>
       <c r="X494" s="2" t="inlineStr"/>
       <c r="Y494" s="2" t="n">
-        <v>-91.27</v>
+        <v>6.03</v>
       </c>
       <c r="Z494" s="2" t="n">
-        <v>-36.75</v>
+        <v>-5.98</v>
       </c>
       <c r="AA494" s="2" t="n">
-        <v>-43.71</v>
+        <v>-1.11</v>
       </c>
       <c r="AB494" s="2" t="n">
-        <v>-3.77</v>
+        <v>-2.51</v>
       </c>
       <c r="AC494" s="2" t="n">
-        <v>5.82</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>INVH US</t>
+          <t>IT US</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C495" s="2" t="n">
-        <v>28.39</v>
+        <v>186.42</v>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E495" s="2" t="n">
-        <v>1.6</v>
+        <v>-3.54</v>
       </c>
       <c r="F495" s="2" t="n">
-        <v>2</v>
+        <v>18.1</v>
       </c>
       <c r="G495" s="2" t="n">
-        <v>-6.18</v>
+        <v>115.12</v>
       </c>
       <c r="H495" s="2" t="inlineStr"/>
       <c r="I495" s="2" t="inlineStr"/>
@@ -34318,48 +34312,48 @@
       <c r="W495" s="2" t="inlineStr"/>
       <c r="X495" s="2" t="inlineStr"/>
       <c r="Y495" s="2" t="n">
-        <v>6.03</v>
+        <v>-28.12</v>
       </c>
       <c r="Z495" s="2" t="n">
-        <v>-5.98</v>
+        <v>-11.99</v>
       </c>
       <c r="AA495" s="2" t="n">
-        <v>-1.11</v>
+        <v>-21.13</v>
       </c>
       <c r="AB495" s="2" t="n">
-        <v>-2.51</v>
+        <v>-4.84</v>
       </c>
       <c r="AC495" s="2" t="n">
-        <v>-4.67</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>IT US</t>
+          <t>J US</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C496" s="2" t="n">
-        <v>186.42</v>
+        <v>146.23</v>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E496" s="2" t="n">
-        <v>-3.54</v>
+        <v>1.09</v>
       </c>
       <c r="F496" s="2" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="G496" s="2" t="n">
-        <v>115.12</v>
+        <v>101.58</v>
       </c>
       <c r="H496" s="2" t="inlineStr"/>
       <c r="I496" s="2" t="inlineStr"/>
@@ -34381,34 +34375,34 @@
       <c r="W496" s="2" t="inlineStr"/>
       <c r="X496" s="2" t="inlineStr"/>
       <c r="Y496" s="2" t="n">
-        <v>-28.12</v>
+        <v>-4.56</v>
       </c>
       <c r="Z496" s="2" t="n">
-        <v>-11.99</v>
+        <v>-2.22</v>
       </c>
       <c r="AA496" s="2" t="n">
-        <v>-21.13</v>
+        <v>1.26</v>
       </c>
       <c r="AB496" s="2" t="n">
-        <v>-4.84</v>
+        <v>-3.62</v>
       </c>
       <c r="AC496" s="2" t="n">
-        <v>3.93</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>J US</t>
+          <t>KMB US</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C497" s="2" t="n">
-        <v>146.23</v>
+        <v>104.96</v>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
@@ -34416,13 +34410,13 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="F497" s="2" t="n">
-        <v>11.8</v>
+        <v>3.4</v>
       </c>
       <c r="G497" s="2" t="n">
-        <v>101.58</v>
+        <v>0.93</v>
       </c>
       <c r="H497" s="2" t="inlineStr"/>
       <c r="I497" s="2" t="inlineStr"/>
@@ -34444,34 +34438,34 @@
       <c r="W497" s="2" t="inlineStr"/>
       <c r="X497" s="2" t="inlineStr"/>
       <c r="Y497" s="2" t="n">
-        <v>-4.56</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Z497" s="2" t="n">
-        <v>-2.22</v>
+        <v>-7.28</v>
       </c>
       <c r="AA497" s="2" t="n">
-        <v>1.26</v>
+        <v>-2.27</v>
       </c>
       <c r="AB497" s="2" t="n">
-        <v>-3.62</v>
+        <v>-2.36</v>
       </c>
       <c r="AC497" s="2" t="n">
-        <v>2.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>KMB US</t>
+          <t>KVUE US</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C498" s="2" t="n">
-        <v>104.96</v>
+        <v>18.74</v>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
@@ -34479,13 +34473,13 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="F498" s="2" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="G498" s="2" t="n">
-        <v>0.93</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H498" s="2" t="inlineStr"/>
       <c r="I498" s="2" t="inlineStr"/>
@@ -34507,48 +34501,48 @@
       <c r="W498" s="2" t="inlineStr"/>
       <c r="X498" s="2" t="inlineStr"/>
       <c r="Y498" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>21.37</v>
       </c>
       <c r="Z498" s="2" t="n">
-        <v>-7.28</v>
+        <v>-0.55</v>
       </c>
       <c r="AA498" s="2" t="n">
-        <v>-2.27</v>
+        <v>4.87</v>
       </c>
       <c r="AB498" s="2" t="n">
-        <v>-2.36</v>
+        <v>-1.89</v>
       </c>
       <c r="AC498" s="2" t="n">
-        <v>0.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>KVUE US</t>
+          <t>LEN US</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C499" s="2" t="n">
-        <v>18.74</v>
+        <v>83.58</v>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E499" s="2" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="F499" s="2" t="n">
-        <v>4.4</v>
+        <v>-9.1</v>
       </c>
       <c r="G499" s="2" t="n">
-        <v>65.04000000000001</v>
+        <v>51.77</v>
       </c>
       <c r="H499" s="2" t="inlineStr"/>
       <c r="I499" s="2" t="inlineStr"/>
@@ -34560,7 +34554,7 @@
       <c r="O499" s="2" t="inlineStr"/>
       <c r="P499" s="2" t="inlineStr"/>
       <c r="Q499" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R499" s="2" t="inlineStr"/>
       <c r="S499" s="2" t="inlineStr"/>
@@ -34570,48 +34564,48 @@
       <c r="W499" s="2" t="inlineStr"/>
       <c r="X499" s="2" t="inlineStr"/>
       <c r="Y499" s="2" t="n">
-        <v>21.37</v>
+        <v>-47.09</v>
       </c>
       <c r="Z499" s="2" t="n">
-        <v>-0.55</v>
+        <v>-26.5</v>
       </c>
       <c r="AA499" s="2" t="n">
-        <v>4.87</v>
+        <v>-17.34</v>
       </c>
       <c r="AB499" s="2" t="n">
-        <v>-1.89</v>
+        <v>-1.53</v>
       </c>
       <c r="AC499" s="2" t="n">
-        <v>1.15</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>LEN US</t>
+          <t>LMT US</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C500" s="2" t="n">
-        <v>83.58</v>
+        <v>525.28</v>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>-3.6</v>
+        <v>0.34</v>
       </c>
       <c r="F500" s="2" t="n">
-        <v>-9.1</v>
+        <v>-7.4</v>
       </c>
       <c r="G500" s="2" t="n">
-        <v>51.77</v>
+        <v>115.8</v>
       </c>
       <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr"/>
@@ -34623,7 +34617,7 @@
       <c r="O500" s="2" t="inlineStr"/>
       <c r="P500" s="2" t="inlineStr"/>
       <c r="Q500" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R500" s="2" t="inlineStr"/>
       <c r="S500" s="2" t="inlineStr"/>
@@ -34633,48 +34627,48 @@
       <c r="W500" s="2" t="inlineStr"/>
       <c r="X500" s="2" t="inlineStr"/>
       <c r="Y500" s="2" t="n">
-        <v>-47.09</v>
+        <v>21.06</v>
       </c>
       <c r="Z500" s="2" t="n">
-        <v>-26.5</v>
+        <v>-10.3</v>
       </c>
       <c r="AA500" s="2" t="n">
-        <v>-17.34</v>
+        <v>-6.6</v>
       </c>
       <c r="AB500" s="2" t="n">
-        <v>-1.53</v>
+        <v>-6.12</v>
       </c>
       <c r="AC500" s="2" t="n">
-        <v>-0.18</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>LMT US</t>
+          <t>LVS US</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C501" s="2" t="n">
-        <v>525.28</v>
+        <v>44.37</v>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E501" s="2" t="n">
-        <v>0.34</v>
+        <v>-3.44</v>
       </c>
       <c r="F501" s="2" t="n">
-        <v>-7.4</v>
+        <v>-12.3</v>
       </c>
       <c r="G501" s="2" t="n">
-        <v>115.8</v>
+        <v>53.43</v>
       </c>
       <c r="H501" s="2" t="inlineStr"/>
       <c r="I501" s="2" t="inlineStr"/>
@@ -34696,48 +34690,48 @@
       <c r="W501" s="2" t="inlineStr"/>
       <c r="X501" s="2" t="inlineStr"/>
       <c r="Y501" s="2" t="n">
-        <v>21.06</v>
+        <v>-49.35</v>
       </c>
       <c r="Z501" s="2" t="n">
-        <v>-10.3</v>
+        <v>-25.16</v>
       </c>
       <c r="AA501" s="2" t="n">
-        <v>-6.6</v>
+        <v>-16.09</v>
       </c>
       <c r="AB501" s="2" t="n">
-        <v>-6.12</v>
+        <v>-0.65</v>
       </c>
       <c r="AC501" s="2" t="n">
-        <v>-10.32</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>LVS US</t>
+          <t>LYV US</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C502" s="2" t="n">
-        <v>44.37</v>
+        <v>173.5</v>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E502" s="2" t="n">
-        <v>-3.44</v>
+        <v>3.03</v>
       </c>
       <c r="F502" s="2" t="n">
-        <v>-12.3</v>
+        <v>3.8</v>
       </c>
       <c r="G502" s="2" t="n">
-        <v>53.43</v>
+        <v>86.94</v>
       </c>
       <c r="H502" s="2" t="inlineStr"/>
       <c r="I502" s="2" t="inlineStr"/>
@@ -34759,48 +34753,48 @@
       <c r="W502" s="2" t="inlineStr"/>
       <c r="X502" s="2" t="inlineStr"/>
       <c r="Y502" s="2" t="n">
-        <v>-49.35</v>
+        <v>32.65</v>
       </c>
       <c r="Z502" s="2" t="n">
-        <v>-25.16</v>
+        <v>-0.52</v>
       </c>
       <c r="AA502" s="2" t="n">
-        <v>-16.09</v>
+        <v>10.36</v>
       </c>
       <c r="AB502" s="2" t="n">
-        <v>-0.65</v>
+        <v>-4.55</v>
       </c>
       <c r="AC502" s="2" t="n">
-        <v>-0.1</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>LYV US</t>
+          <t>MAA US</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C503" s="2" t="n">
-        <v>173.5</v>
+        <v>128.32</v>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>3.03</v>
+        <v>-0.08</v>
       </c>
       <c r="F503" s="2" t="n">
-        <v>3.8</v>
+        <v>-1.1</v>
       </c>
       <c r="G503" s="2" t="n">
-        <v>86.94</v>
+        <v>-10.82</v>
       </c>
       <c r="H503" s="2" t="inlineStr"/>
       <c r="I503" s="2" t="inlineStr"/>
@@ -34822,48 +34816,48 @@
       <c r="W503" s="2" t="inlineStr"/>
       <c r="X503" s="2" t="inlineStr"/>
       <c r="Y503" s="2" t="n">
-        <v>32.65</v>
+        <v>2.28</v>
       </c>
       <c r="Z503" s="2" t="n">
-        <v>-0.52</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AA503" s="2" t="n">
-        <v>10.36</v>
+        <v>-5.27</v>
       </c>
       <c r="AB503" s="2" t="n">
-        <v>-4.55</v>
+        <v>-0.55</v>
       </c>
       <c r="AC503" s="2" t="n">
-        <v>-3.05</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>MAA US</t>
+          <t>MDLZ US</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C504" s="2" t="n">
-        <v>128.32</v>
+        <v>61.28</v>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>-0.08</v>
+        <v>1.68</v>
       </c>
       <c r="F504" s="2" t="n">
-        <v>-1.1</v>
+        <v>2.5</v>
       </c>
       <c r="G504" s="2" t="n">
-        <v>-10.82</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H504" s="2" t="inlineStr"/>
       <c r="I504" s="2" t="inlineStr"/>
@@ -34885,34 +34879,34 @@
       <c r="W504" s="2" t="inlineStr"/>
       <c r="X504" s="2" t="inlineStr"/>
       <c r="Y504" s="2" t="n">
-        <v>2.28</v>
+        <v>14.56</v>
       </c>
       <c r="Z504" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-4.55</v>
       </c>
       <c r="AA504" s="2" t="n">
-        <v>-5.27</v>
+        <v>0.62</v>
       </c>
       <c r="AB504" s="2" t="n">
-        <v>-0.55</v>
+        <v>-1.51</v>
       </c>
       <c r="AC504" s="2" t="n">
-        <v>-2.57</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>MDLZ US</t>
+          <t>MNST US</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C505" s="2" t="n">
-        <v>61.28</v>
+        <v>43.82</v>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
@@ -34920,13 +34914,13 @@
         </is>
       </c>
       <c r="E505" s="2" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="F505" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G505" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="H505" s="2" t="inlineStr"/>
       <c r="I505" s="2" t="inlineStr"/>
@@ -34938,7 +34932,7 @@
       <c r="O505" s="2" t="inlineStr"/>
       <c r="P505" s="2" t="inlineStr"/>
       <c r="Q505" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R505" s="2" t="inlineStr"/>
       <c r="S505" s="2" t="inlineStr"/>
@@ -34948,48 +34942,48 @@
       <c r="W505" s="2" t="inlineStr"/>
       <c r="X505" s="2" t="inlineStr"/>
       <c r="Y505" s="2" t="n">
-        <v>14.56</v>
+        <v>28.1</v>
       </c>
       <c r="Z505" s="2" t="n">
-        <v>-4.55</v>
+        <v>0.08</v>
       </c>
       <c r="AA505" s="2" t="n">
-        <v>0.62</v>
+        <v>5.38</v>
       </c>
       <c r="AB505" s="2" t="n">
-        <v>-1.51</v>
+        <v>-7.39</v>
       </c>
       <c r="AC505" s="2" t="n">
-        <v>-0.51</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>MNST US</t>
+          <t>MOS US</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Mosaic Company (The)</t>
         </is>
       </c>
       <c r="C506" s="2" t="n">
-        <v>43.82</v>
+        <v>25.85</v>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E506" s="2" t="n">
-        <v>2.22</v>
+        <v>-1.57</v>
       </c>
       <c r="F506" s="2" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="G506" s="2" t="n">
-        <v>1.29</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="H506" s="2" t="inlineStr"/>
       <c r="I506" s="2" t="inlineStr"/>
@@ -35001,7 +34995,7 @@
       <c r="O506" s="2" t="inlineStr"/>
       <c r="P506" s="2" t="inlineStr"/>
       <c r="Q506" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R506" s="2" t="inlineStr"/>
       <c r="S506" s="2" t="inlineStr"/>
@@ -35011,48 +35005,48 @@
       <c r="W506" s="2" t="inlineStr"/>
       <c r="X506" s="2" t="inlineStr"/>
       <c r="Y506" s="2" t="n">
-        <v>28.1</v>
+        <v>2.36</v>
       </c>
       <c r="Z506" s="2" t="n">
-        <v>0.08</v>
+        <v>-7.95</v>
       </c>
       <c r="AA506" s="2" t="n">
-        <v>5.38</v>
+        <v>-6.92</v>
       </c>
       <c r="AB506" s="2" t="n">
-        <v>-7.39</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AC506" s="2" t="n">
-        <v>-4.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>MOS US</t>
+          <t>MTD US</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>Mosaic Company (The)</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C507" s="2" t="n">
-        <v>25.85</v>
+        <v>1345.26</v>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E507" s="2" t="n">
-        <v>-1.57</v>
+        <v>-0.44</v>
       </c>
       <c r="F507" s="2" t="n">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="G507" s="2" t="n">
-        <v>95.63</v>
+        <v>94.53</v>
       </c>
       <c r="H507" s="2" t="inlineStr"/>
       <c r="I507" s="2" t="inlineStr"/>
@@ -35074,48 +35068,48 @@
       <c r="W507" s="2" t="inlineStr"/>
       <c r="X507" s="2" t="inlineStr"/>
       <c r="Y507" s="2" t="n">
-        <v>2.36</v>
+        <v>-4.86</v>
       </c>
       <c r="Z507" s="2" t="n">
-        <v>-7.95</v>
+        <v>-7.42</v>
       </c>
       <c r="AA507" s="2" t="n">
-        <v>-6.92</v>
+        <v>-10.17</v>
       </c>
       <c r="AB507" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>-3.55</v>
       </c>
       <c r="AC507" s="2" t="n">
-        <v>13.5</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>MTD US</t>
+          <t>NDAQ US</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C508" s="2" t="n">
-        <v>1345.26</v>
+        <v>96.88</v>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E508" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="F508" s="2" t="n">
-        <v>4.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G508" s="2" t="n">
-        <v>94.53</v>
+        <v>107.47</v>
       </c>
       <c r="H508" s="2" t="inlineStr"/>
       <c r="I508" s="2" t="inlineStr"/>
@@ -35137,48 +35131,48 @@
       <c r="W508" s="2" t="inlineStr"/>
       <c r="X508" s="2" t="inlineStr"/>
       <c r="Y508" s="2" t="n">
-        <v>-4.86</v>
+        <v>15.9</v>
       </c>
       <c r="Z508" s="2" t="n">
-        <v>-7.42</v>
+        <v>-1.46</v>
       </c>
       <c r="AA508" s="2" t="n">
-        <v>-10.17</v>
+        <v>-1.34</v>
       </c>
       <c r="AB508" s="2" t="n">
-        <v>-3.55</v>
+        <v>-2.29</v>
       </c>
       <c r="AC508" s="2" t="n">
-        <v>-4.54</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>NDAQ US</t>
+          <t>NDSN US</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C509" s="2" t="n">
-        <v>96.88</v>
+        <v>318.36</v>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E509" s="2" t="n">
-        <v>-0.11</v>
+        <v>2.66</v>
       </c>
       <c r="F509" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G509" s="2" t="n">
-        <v>107.47</v>
+        <v>92.69</v>
       </c>
       <c r="H509" s="2" t="inlineStr"/>
       <c r="I509" s="2" t="inlineStr"/>
@@ -35190,7 +35184,7 @@
       <c r="O509" s="2" t="inlineStr"/>
       <c r="P509" s="2" t="inlineStr"/>
       <c r="Q509" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R509" s="2" t="inlineStr"/>
       <c r="S509" s="2" t="inlineStr"/>
@@ -35200,48 +35194,48 @@
       <c r="W509" s="2" t="inlineStr"/>
       <c r="X509" s="2" t="inlineStr"/>
       <c r="Y509" s="2" t="n">
-        <v>15.9</v>
+        <v>41.03</v>
       </c>
       <c r="Z509" s="2" t="n">
-        <v>-1.46</v>
+        <v>8.76</v>
       </c>
       <c r="AA509" s="2" t="n">
-        <v>-1.34</v>
+        <v>13.1</v>
       </c>
       <c r="AB509" s="2" t="n">
-        <v>-2.29</v>
+        <v>-2.64</v>
       </c>
       <c r="AC509" s="2" t="n">
-        <v>3.95</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>NDSN US</t>
+          <t>PEP US</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C510" s="2" t="n">
-        <v>318.36</v>
+        <v>137.63</v>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E510" s="2" t="n">
-        <v>2.66</v>
+        <v>-0.1</v>
       </c>
       <c r="F510" s="2" t="n">
-        <v>10.2</v>
+        <v>-6.4</v>
       </c>
       <c r="G510" s="2" t="n">
-        <v>92.69</v>
+        <v>66.03</v>
       </c>
       <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr"/>
@@ -35263,34 +35257,34 @@
       <c r="W510" s="2" t="inlineStr"/>
       <c r="X510" s="2" t="inlineStr"/>
       <c r="Y510" s="2" t="n">
-        <v>41.03</v>
+        <v>-1.33</v>
       </c>
       <c r="Z510" s="2" t="n">
-        <v>8.76</v>
+        <v>-13.19</v>
       </c>
       <c r="AA510" s="2" t="n">
-        <v>13.1</v>
+        <v>-8.32</v>
       </c>
       <c r="AB510" s="2" t="n">
-        <v>-2.64</v>
+        <v>-0.98</v>
       </c>
       <c r="AC510" s="2" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>PEP US</t>
+          <t>PLD US</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C511" s="2" t="n">
-        <v>137.63</v>
+        <v>137.34</v>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
@@ -35298,13 +35292,13 @@
         </is>
       </c>
       <c r="E511" s="2" t="n">
-        <v>-0.1</v>
+        <v>1.26</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>-6.4</v>
+        <v>-1.5</v>
       </c>
       <c r="G511" s="2" t="n">
-        <v>66.03</v>
+        <v>4.24</v>
       </c>
       <c r="H511" s="2" t="inlineStr"/>
       <c r="I511" s="2" t="inlineStr"/>
@@ -35316,7 +35310,7 @@
       <c r="O511" s="2" t="inlineStr"/>
       <c r="P511" s="2" t="inlineStr"/>
       <c r="Q511" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R511" s="2" t="inlineStr"/>
       <c r="S511" s="2" t="inlineStr"/>
@@ -35326,48 +35320,48 @@
       <c r="W511" s="2" t="inlineStr"/>
       <c r="X511" s="2" t="inlineStr"/>
       <c r="Y511" s="2" t="n">
-        <v>-1.33</v>
+        <v>16.2</v>
       </c>
       <c r="Z511" s="2" t="n">
-        <v>-13.19</v>
+        <v>-4.93</v>
       </c>
       <c r="AA511" s="2" t="n">
-        <v>-8.32</v>
+        <v>0.03</v>
       </c>
       <c r="AB511" s="2" t="n">
-        <v>-0.98</v>
+        <v>-2.53</v>
       </c>
       <c r="AC511" s="2" t="n">
-        <v>1.76</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>PLD US</t>
+          <t>SLB US</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C512" s="2" t="n">
-        <v>137.34</v>
+        <v>57.51</v>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E512" s="2" t="n">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="F512" s="2" t="n">
-        <v>-1.5</v>
+        <v>12.2</v>
       </c>
       <c r="G512" s="2" t="n">
-        <v>4.24</v>
+        <v>114.42</v>
       </c>
       <c r="H512" s="2" t="inlineStr"/>
       <c r="I512" s="2" t="inlineStr"/>
@@ -35389,48 +35383,48 @@
       <c r="W512" s="2" t="inlineStr"/>
       <c r="X512" s="2" t="inlineStr"/>
       <c r="Y512" s="2" t="n">
-        <v>16.2</v>
+        <v>60.3</v>
       </c>
       <c r="Z512" s="2" t="n">
-        <v>-4.93</v>
+        <v>15.59</v>
       </c>
       <c r="AA512" s="2" t="n">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="AB512" s="2" t="n">
-        <v>-2.53</v>
+        <v>0.1</v>
       </c>
       <c r="AC512" s="2" t="n">
-        <v>-2.2</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>SLB US</t>
+          <t>SPGI US</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C513" s="2" t="n">
-        <v>57.51</v>
+        <v>443.51</v>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E513" s="2" t="n">
-        <v>2.35</v>
+        <v>-2.37</v>
       </c>
       <c r="F513" s="2" t="n">
-        <v>12.2</v>
+        <v>8.4</v>
       </c>
       <c r="G513" s="2" t="n">
-        <v>114.42</v>
+        <v>47.27</v>
       </c>
       <c r="H513" s="2" t="inlineStr"/>
       <c r="I513" s="2" t="inlineStr"/>
@@ -35452,48 +35446,48 @@
       <c r="W513" s="2" t="inlineStr"/>
       <c r="X513" s="2" t="inlineStr"/>
       <c r="Y513" s="2" t="n">
-        <v>60.3</v>
+        <v>-7.47</v>
       </c>
       <c r="Z513" s="2" t="n">
-        <v>15.59</v>
+        <v>-7.56</v>
       </c>
       <c r="AA513" s="2" t="n">
-        <v>2.94</v>
+        <v>-7.23</v>
       </c>
       <c r="AB513" s="2" t="n">
-        <v>0.1</v>
+        <v>0.68</v>
       </c>
       <c r="AC513" s="2" t="n">
-        <v>12.64</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>SPGI US</t>
+          <t>SRE US</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C514" s="2" t="n">
-        <v>443.51</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E514" s="2" t="n">
-        <v>-2.37</v>
+        <v>-0.29</v>
       </c>
       <c r="F514" s="2" t="n">
-        <v>8.4</v>
+        <v>-7.7</v>
       </c>
       <c r="G514" s="2" t="n">
-        <v>47.27</v>
+        <v>-8.98</v>
       </c>
       <c r="H514" s="2" t="inlineStr"/>
       <c r="I514" s="2" t="inlineStr"/>
@@ -35505,7 +35499,7 @@
       <c r="O514" s="2" t="inlineStr"/>
       <c r="P514" s="2" t="inlineStr"/>
       <c r="Q514" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R514" s="2" t="inlineStr"/>
       <c r="S514" s="2" t="inlineStr"/>
@@ -35515,48 +35509,48 @@
       <c r="W514" s="2" t="inlineStr"/>
       <c r="X514" s="2" t="inlineStr"/>
       <c r="Y514" s="2" t="n">
-        <v>-7.47</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="Z514" s="2" t="n">
-        <v>-7.56</v>
+        <v>-14.58</v>
       </c>
       <c r="AA514" s="2" t="n">
-        <v>-7.23</v>
+        <v>-4.06</v>
       </c>
       <c r="AB514" s="2" t="n">
-        <v>0.68</v>
+        <v>-0.15</v>
       </c>
       <c r="AC514" s="2" t="n">
-        <v>10.58</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>SRE US</t>
+          <t>STE US</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C515" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>224.59</v>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>-0.29</v>
+        <v>-1.49</v>
       </c>
       <c r="F515" s="2" t="n">
-        <v>-7.7</v>
+        <v>0.7</v>
       </c>
       <c r="G515" s="2" t="n">
-        <v>-8.98</v>
+        <v>97.2</v>
       </c>
       <c r="H515" s="2" t="inlineStr"/>
       <c r="I515" s="2" t="inlineStr"/>
@@ -35568,7 +35562,7 @@
       <c r="O515" s="2" t="inlineStr"/>
       <c r="P515" s="2" t="inlineStr"/>
       <c r="Q515" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R515" s="2" t="inlineStr"/>
       <c r="S515" s="2" t="inlineStr"/>
@@ -35578,48 +35572,48 @@
       <c r="W515" s="2" t="inlineStr"/>
       <c r="X515" s="2" t="inlineStr"/>
       <c r="Y515" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-17.34</v>
       </c>
       <c r="Z515" s="2" t="n">
-        <v>-14.58</v>
+        <v>-12.74</v>
       </c>
       <c r="AA515" s="2" t="n">
-        <v>-4.06</v>
+        <v>-15.37</v>
       </c>
       <c r="AB515" s="2" t="n">
-        <v>-0.15</v>
+        <v>-2.97</v>
       </c>
       <c r="AC515" s="2" t="n">
-        <v>1.3</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>STE US</t>
+          <t>STX US</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="C516" s="2" t="n">
-        <v>224.59</v>
+        <v>849.28</v>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>-1.49</v>
+        <v>11.03</v>
       </c>
       <c r="F516" s="2" t="n">
-        <v>0.7</v>
+        <v>23</v>
       </c>
       <c r="G516" s="2" t="n">
-        <v>97.2</v>
+        <v>36.09</v>
       </c>
       <c r="H516" s="2" t="inlineStr"/>
       <c r="I516" s="2" t="inlineStr"/>
@@ -35631,7 +35625,7 @@
       <c r="O516" s="2" t="inlineStr"/>
       <c r="P516" s="2" t="inlineStr"/>
       <c r="Q516" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R516" s="2" t="inlineStr"/>
       <c r="S516" s="2" t="inlineStr"/>
@@ -35641,48 +35635,48 @@
       <c r="W516" s="2" t="inlineStr"/>
       <c r="X516" s="2" t="inlineStr"/>
       <c r="Y516" s="2" t="n">
-        <v>-17.34</v>
+        <v>123.7</v>
       </c>
       <c r="Z516" s="2" t="n">
-        <v>-12.74</v>
+        <v>53.05</v>
       </c>
       <c r="AA516" s="2" t="n">
-        <v>-15.37</v>
+        <v>42.94</v>
       </c>
       <c r="AB516" s="2" t="n">
-        <v>-2.97</v>
+        <v>0.01</v>
       </c>
       <c r="AC516" s="2" t="n">
-        <v>-2.69</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>STX US</t>
+          <t>STZ US</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C517" s="2" t="n">
-        <v>849.28</v>
+        <v>128.18</v>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E517" s="2" t="n">
-        <v>11.03</v>
+        <v>-1.63</v>
       </c>
       <c r="F517" s="2" t="n">
-        <v>23</v>
+        <v>-10.9</v>
       </c>
       <c r="G517" s="2" t="n">
-        <v>36.09</v>
+        <v>13.78</v>
       </c>
       <c r="H517" s="2" t="inlineStr"/>
       <c r="I517" s="2" t="inlineStr"/>
@@ -35694,7 +35688,7 @@
       <c r="O517" s="2" t="inlineStr"/>
       <c r="P517" s="2" t="inlineStr"/>
       <c r="Q517" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R517" s="2" t="inlineStr"/>
       <c r="S517" s="2" t="inlineStr"/>
@@ -35704,34 +35698,34 @@
       <c r="W517" s="2" t="inlineStr"/>
       <c r="X517" s="2" t="inlineStr"/>
       <c r="Y517" s="2" t="n">
-        <v>123.7</v>
+        <v>1.71</v>
       </c>
       <c r="Z517" s="2" t="n">
-        <v>53.05</v>
+        <v>-17.37</v>
       </c>
       <c r="AA517" s="2" t="n">
-        <v>42.94</v>
+        <v>-12.71</v>
       </c>
       <c r="AB517" s="2" t="n">
-        <v>0.01</v>
+        <v>-1.19</v>
       </c>
       <c r="AC517" s="2" t="n">
-        <v>-7.93</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>STZ US</t>
+          <t>SYK US</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C518" s="2" t="n">
-        <v>128.18</v>
+        <v>303.13</v>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
@@ -35739,13 +35733,13 @@
         </is>
       </c>
       <c r="E518" s="2" t="n">
-        <v>-1.63</v>
+        <v>-1.14</v>
       </c>
       <c r="F518" s="2" t="n">
-        <v>-10.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G518" s="2" t="n">
-        <v>13.78</v>
+        <v>8.09</v>
       </c>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr"/>
@@ -35767,48 +35761,48 @@
       <c r="W518" s="2" t="inlineStr"/>
       <c r="X518" s="2" t="inlineStr"/>
       <c r="Y518" s="2" t="n">
-        <v>1.71</v>
+        <v>-19.05</v>
       </c>
       <c r="Z518" s="2" t="n">
-        <v>-17.37</v>
+        <v>-19.89</v>
       </c>
       <c r="AA518" s="2" t="n">
-        <v>-12.71</v>
+        <v>-22.34</v>
       </c>
       <c r="AB518" s="2" t="n">
-        <v>-1.19</v>
+        <v>-6.69</v>
       </c>
       <c r="AC518" s="2" t="n">
-        <v>-1.96</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>SYK US</t>
+          <t>SYY US</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C519" s="2" t="n">
-        <v>303.13</v>
+        <v>80.05</v>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E519" s="2" t="n">
-        <v>-1.14</v>
+        <v>1.12</v>
       </c>
       <c r="F519" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="G519" s="2" t="n">
-        <v>8.09</v>
+        <v>-1.92</v>
       </c>
       <c r="H519" s="2" t="inlineStr"/>
       <c r="I519" s="2" t="inlineStr"/>
@@ -35830,34 +35824,34 @@
       <c r="W519" s="2" t="inlineStr"/>
       <c r="X519" s="2" t="inlineStr"/>
       <c r="Y519" s="2" t="n">
-        <v>-19.05</v>
+        <v>12.67</v>
       </c>
       <c r="Z519" s="2" t="n">
-        <v>-19.89</v>
+        <v>-6.81</v>
       </c>
       <c r="AA519" s="2" t="n">
-        <v>-22.34</v>
+        <v>-1.63</v>
       </c>
       <c r="AB519" s="2" t="n">
-        <v>-6.69</v>
+        <v>-2.01</v>
       </c>
       <c r="AC519" s="2" t="n">
-        <v>-6.7</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>SYY US</t>
+          <t>TPR US</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C520" s="2" t="n">
-        <v>80.05</v>
+        <v>122.14</v>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
@@ -35865,13 +35859,13 @@
         </is>
       </c>
       <c r="E520" s="2" t="n">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
       <c r="F520" s="2" t="n">
-        <v>-0.1</v>
+        <v>-14.4</v>
       </c>
       <c r="G520" s="2" t="n">
-        <v>-1.92</v>
+        <v>-10.63</v>
       </c>
       <c r="H520" s="2" t="inlineStr"/>
       <c r="I520" s="2" t="inlineStr"/>
@@ -35883,7 +35877,7 @@
       <c r="O520" s="2" t="inlineStr"/>
       <c r="P520" s="2" t="inlineStr"/>
       <c r="Q520" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R520" s="2" t="inlineStr"/>
       <c r="S520" s="2" t="inlineStr"/>
@@ -35893,19 +35887,19 @@
       <c r="W520" s="2" t="inlineStr"/>
       <c r="X520" s="2" t="inlineStr"/>
       <c r="Y520" s="2" t="n">
-        <v>12.67</v>
+        <v>20.89</v>
       </c>
       <c r="Z520" s="2" t="n">
-        <v>-6.81</v>
+        <v>-15.2</v>
       </c>
       <c r="AA520" s="2" t="n">
-        <v>-1.63</v>
+        <v>-5.71</v>
       </c>
       <c r="AB520" s="2" t="n">
-        <v>-2.01</v>
+        <v>-2.09</v>
       </c>
       <c r="AC520" s="2" t="n">
-        <v>-3.47</v>
+        <v>-27.59</v>
       </c>
     </row>
     <row r="521">
@@ -36314,7 +36308,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-09-05 | 525 只</t>
+          <t>截至: 2026-09-06 | 525 只</t>
         </is>
       </c>
     </row>

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -1774,9 +1774,7 @@
         <v>1</v>
       </c>
       <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="n">
         <v>1</v>
@@ -8759,9 +8757,7 @@
       </c>
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="2" t="inlineStr"/>
-      <c r="T120" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="T120" s="2" t="inlineStr"/>
       <c r="U120" s="2" t="inlineStr">
         <is>
           <t>预-1</t>
@@ -32282,9 +32278,7 @@
       </c>
       <c r="R463" s="2" t="inlineStr"/>
       <c r="S463" s="2" t="inlineStr"/>
-      <c r="T463" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="T463" s="2" t="inlineStr"/>
       <c r="U463" s="2" t="inlineStr"/>
       <c r="V463" s="2" t="inlineStr"/>
       <c r="W463" s="2" t="inlineStr"/>
@@ -36308,7 +36302,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-09-06 | 525 只</t>
+          <t>截至: 2026-09-07 | 525 只</t>
         </is>
       </c>
     </row>
@@ -36432,14 +36426,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5%。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
+          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5% 且距250日收盘高点回落≥5%(创新高处的平台突破归新高, 不算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=1.8x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
+          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
         </is>
       </c>
     </row>

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>-4.1</v>
@@ -14310,16 +14310,16 @@
       <c r="W201" s="2" t="inlineStr"/>
       <c r="X201" s="2" t="inlineStr"/>
       <c r="Y201" s="2" t="n">
-        <v>-13.64</v>
+        <v>-14.18</v>
       </c>
       <c r="Z201" s="2" t="n">
-        <v>-16.06</v>
+        <v>-16.05</v>
       </c>
       <c r="AA201" s="2" t="n">
-        <v>-6.03</v>
+        <v>-6.02</v>
       </c>
       <c r="AB201" s="2" t="n">
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
       <c r="AC201" s="2" t="n">
         <v>-5.42</v>
@@ -28064,47 +28064,37 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>TRGP US</t>
+          <t>TPR US</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>290.05</v>
+        <v>122.14</v>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>5.68</v>
+        <v>0.23</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>13.6</v>
+        <v>-14.4</v>
       </c>
       <c r="G402" s="2" t="n">
-        <v>38.96</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="H402" s="2" t="inlineStr"/>
-      <c r="I402" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
-      <c r="J402" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I402" s="2" t="inlineStr"/>
+      <c r="J402" s="2" t="inlineStr"/>
       <c r="K402" s="2" t="inlineStr"/>
       <c r="L402" s="2" t="inlineStr"/>
-      <c r="M402" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M402" s="2" t="inlineStr"/>
       <c r="N402" s="2" t="inlineStr"/>
       <c r="O402" s="2" t="inlineStr"/>
       <c r="P402" s="2" t="inlineStr"/>
@@ -28114,73 +28104,83 @@
       <c r="R402" s="2" t="inlineStr"/>
       <c r="S402" s="2" t="inlineStr"/>
       <c r="T402" s="2" t="inlineStr"/>
-      <c r="U402" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V402" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W402" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="U402" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="V402" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="W402" s="2" t="inlineStr"/>
       <c r="X402" s="2" t="inlineStr"/>
       <c r="Y402" s="2" t="n">
-        <v>69.63</v>
+        <v>20.54</v>
       </c>
       <c r="Z402" s="2" t="n">
-        <v>21.01</v>
+        <v>-15.2</v>
       </c>
       <c r="AA402" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="AB402" s="2" t="n">
-        <v>-0.18</v>
+        <v>-2.09</v>
       </c>
       <c r="AC402" s="2" t="n">
-        <v>10.96</v>
+        <v>-27.58</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>TRI US</t>
+          <t>TRGP US</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>105.68</v>
+        <v>290.05</v>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>-2.07</v>
+        <v>5.68</v>
       </c>
       <c r="F403" s="2" t="n">
-        <v>15.8</v>
+        <v>13.6</v>
       </c>
       <c r="G403" s="2" t="n">
-        <v>89.18000000000001</v>
+        <v>38.96</v>
       </c>
       <c r="H403" s="2" t="inlineStr"/>
-      <c r="I403" s="2" t="inlineStr"/>
-      <c r="J403" s="2" t="inlineStr"/>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K403" s="2" t="inlineStr"/>
       <c r="L403" s="2" t="inlineStr"/>
-      <c r="M403" s="2" t="inlineStr"/>
+      <c r="M403" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N403" s="2" t="inlineStr"/>
-      <c r="O403" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O403" s="2" t="inlineStr"/>
       <c r="P403" s="2" t="inlineStr"/>
       <c r="Q403" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R403" s="2" t="inlineStr"/>
       <c r="S403" s="2" t="inlineStr"/>
@@ -28191,49 +28191,53 @@
       <c r="V403" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="W403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X403" s="2" t="inlineStr"/>
       <c r="Y403" s="2" t="n">
-        <v>-33.69</v>
+        <v>69.63</v>
       </c>
       <c r="Z403" s="2" t="n">
-        <v>-13.05</v>
-      </c>
-      <c r="AA403" s="2" t="n"/>
+        <v>21.01</v>
+      </c>
+      <c r="AA403" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
       <c r="AB403" s="2" t="n">
-        <v>0.82</v>
+        <v>-0.18</v>
       </c>
       <c r="AC403" s="2" t="n">
-        <v>9.06</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>TRMB US</t>
+          <t>TRI US</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>59.47</v>
+        <v>105.68</v>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>-3.45</v>
+        <v>-2.07</v>
       </c>
       <c r="F404" s="2" t="n">
-        <v>-1.4</v>
+        <v>15.8</v>
       </c>
       <c r="G404" s="2" t="n">
-        <v>106.71</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="H404" s="2" t="inlineStr"/>
       <c r="I404" s="2" t="inlineStr"/>
@@ -28242,67 +28246,65 @@
       <c r="L404" s="2" t="inlineStr"/>
       <c r="M404" s="2" t="inlineStr"/>
       <c r="N404" s="2" t="inlineStr"/>
-      <c r="O404" s="2" t="inlineStr"/>
-      <c r="P404" s="2" t="inlineStr">
-        <is>
-          <t>+13/-13</t>
-        </is>
-      </c>
+      <c r="O404" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P404" s="2" t="inlineStr"/>
       <c r="Q404" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R404" s="2" t="inlineStr"/>
       <c r="S404" s="2" t="inlineStr"/>
       <c r="T404" s="2" t="inlineStr"/>
-      <c r="U404" s="2" t="inlineStr"/>
-      <c r="V404" s="2" t="inlineStr"/>
-      <c r="W404" s="2" t="n">
+      <c r="U404" s="2" t="n">
         <v>-1</v>
       </c>
+      <c r="V404" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W404" s="2" t="inlineStr"/>
       <c r="X404" s="2" t="inlineStr"/>
       <c r="Y404" s="2" t="n">
-        <v>-37.57</v>
+        <v>-33.69</v>
       </c>
       <c r="Z404" s="2" t="n">
-        <v>-20.74</v>
-      </c>
-      <c r="AA404" s="2" t="n">
-        <v>-29.04</v>
-      </c>
+        <v>-13.05</v>
+      </c>
+      <c r="AA404" s="2" t="n"/>
       <c r="AB404" s="2" t="n">
-        <v>-1.36</v>
+        <v>0.82</v>
       </c>
       <c r="AC404" s="2" t="n">
-        <v>3.47</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>TRV US</t>
+          <t>TRMB US</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>369.35</v>
+        <v>59.47</v>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>3.96</v>
+        <v>-3.45</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>15.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G405" s="2" t="n">
-        <v>75.8</v>
+        <v>106.71</v>
       </c>
       <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="2" t="inlineStr"/>
@@ -28312,64 +28314,66 @@
       <c r="M405" s="2" t="inlineStr"/>
       <c r="N405" s="2" t="inlineStr"/>
       <c r="O405" s="2" t="inlineStr"/>
-      <c r="P405" s="2" t="inlineStr"/>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>+13/-13</t>
+        </is>
+      </c>
       <c r="Q405" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R405" s="2" t="inlineStr"/>
       <c r="S405" s="2" t="inlineStr"/>
       <c r="T405" s="2" t="inlineStr"/>
-      <c r="U405" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U405" s="2" t="inlineStr"/>
       <c r="V405" s="2" t="inlineStr"/>
-      <c r="W405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X405" s="2" t="inlineStr"/>
       <c r="Y405" s="2" t="n">
-        <v>35.77</v>
+        <v>-37.57</v>
       </c>
       <c r="Z405" s="2" t="n">
-        <v>11.5</v>
+        <v>-20.74</v>
       </c>
       <c r="AA405" s="2" t="n">
-        <v>11.43</v>
+        <v>-29.04</v>
       </c>
       <c r="AB405" s="2" t="n">
-        <v>-0.58</v>
+        <v>-1.36</v>
       </c>
       <c r="AC405" s="2" t="n">
-        <v>-5.33</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>TSCO US</t>
+          <t>TRV US</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>34.99</v>
+        <v>369.35</v>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-5.31</v>
+        <v>3.96</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>-7.7</v>
+        <v>15.2</v>
       </c>
       <c r="G406" s="2" t="n">
-        <v>104.9</v>
+        <v>75.8</v>
       </c>
       <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="2" t="inlineStr"/>
@@ -28381,46 +28385,48 @@
       <c r="O406" s="2" t="inlineStr"/>
       <c r="P406" s="2" t="inlineStr"/>
       <c r="Q406" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R406" s="2" t="inlineStr"/>
       <c r="S406" s="2" t="inlineStr"/>
       <c r="T406" s="2" t="inlineStr"/>
-      <c r="U406" s="2" t="n">
-        <v>1</v>
+      <c r="U406" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="V406" s="2" t="inlineStr"/>
       <c r="W406" s="2" t="inlineStr"/>
       <c r="X406" s="2" t="inlineStr"/>
       <c r="Y406" s="2" t="n">
-        <v>-60.15</v>
+        <v>35.77</v>
       </c>
       <c r="Z406" s="2" t="n">
-        <v>-28.45</v>
+        <v>11.5</v>
       </c>
       <c r="AA406" s="2" t="n">
-        <v>-19.22</v>
+        <v>11.43</v>
       </c>
       <c r="AB406" s="2" t="n">
-        <v>1.53</v>
+        <v>-0.58</v>
       </c>
       <c r="AC406" s="2" t="n">
-        <v>5.58</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>TSLA US</t>
+          <t>TSCO US</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>354.08</v>
+        <v>34.99</v>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
@@ -28428,13 +28434,13 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>-2.98</v>
+        <v>-5.31</v>
       </c>
       <c r="F407" s="2" t="n">
-        <v>-8</v>
+        <v>-7.7</v>
       </c>
       <c r="G407" s="2" t="n">
-        <v>21.62</v>
+        <v>104.9</v>
       </c>
       <c r="H407" s="2" t="inlineStr"/>
       <c r="I407" s="2" t="inlineStr"/>
@@ -28452,67 +28458,61 @@
       <c r="S407" s="2" t="inlineStr"/>
       <c r="T407" s="2" t="inlineStr"/>
       <c r="U407" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V407" s="2" t="inlineStr"/>
       <c r="W407" s="2" t="inlineStr"/>
       <c r="X407" s="2" t="inlineStr"/>
       <c r="Y407" s="2" t="n">
-        <v>-17.77</v>
+        <v>-60.15</v>
       </c>
       <c r="Z407" s="2" t="n">
-        <v>-20.6</v>
+        <v>-28.45</v>
       </c>
       <c r="AA407" s="2" t="n">
-        <v>-11.05</v>
+        <v>-19.22</v>
       </c>
       <c r="AB407" s="2" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AC407" s="2" t="n">
-        <v>6.78</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>TSN US</t>
+          <t>TSLA US</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>51.42</v>
+        <v>354.08</v>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>-0.68</v>
+        <v>-2.98</v>
       </c>
       <c r="F408" s="2" t="n">
-        <v>-14.6</v>
+        <v>-8</v>
       </c>
       <c r="G408" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>21.62</v>
+      </c>
+      <c r="H408" s="2" t="inlineStr"/>
       <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr"/>
       <c r="K408" s="2" t="inlineStr"/>
       <c r="L408" s="2" t="inlineStr"/>
-      <c r="M408" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M408" s="2" t="inlineStr"/>
       <c r="N408" s="2" t="inlineStr"/>
       <c r="O408" s="2" t="inlineStr"/>
       <c r="P408" s="2" t="inlineStr"/>
@@ -28522,39 +28522,41 @@
       <c r="R408" s="2" t="inlineStr"/>
       <c r="S408" s="2" t="inlineStr"/>
       <c r="T408" s="2" t="inlineStr"/>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="V408" s="2" t="inlineStr"/>
       <c r="W408" s="2" t="inlineStr"/>
       <c r="X408" s="2" t="inlineStr"/>
       <c r="Y408" s="2" t="n">
-        <v>3.03</v>
+        <v>-17.77</v>
       </c>
       <c r="Z408" s="2" t="n">
-        <v>-18.88</v>
+        <v>-20.6</v>
       </c>
       <c r="AA408" s="2" t="n">
-        <v>-14.36</v>
+        <v>-11.05</v>
       </c>
       <c r="AB408" s="2" t="n">
-        <v>-5.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC408" s="2" t="n">
-        <v>-8.109999999999999</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>TT US</t>
+          <t>TSN US</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>447.9</v>
+        <v>51.42</v>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
@@ -28562,20 +28564,26 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>2.06</v>
+        <v>-0.68</v>
       </c>
       <c r="F409" s="2" t="n">
-        <v>-2.3</v>
+        <v>-14.6</v>
       </c>
       <c r="G409" s="2" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="H409" s="2" t="inlineStr"/>
+        <v>7.15</v>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="I409" s="2" t="inlineStr"/>
       <c r="J409" s="2" t="inlineStr"/>
       <c r="K409" s="2" t="inlineStr"/>
       <c r="L409" s="2" t="inlineStr"/>
-      <c r="M409" s="2" t="inlineStr"/>
+      <c r="M409" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N409" s="2" t="inlineStr"/>
       <c r="O409" s="2" t="inlineStr"/>
       <c r="P409" s="2" t="inlineStr"/>
@@ -28585,76 +28593,60 @@
       <c r="R409" s="2" t="inlineStr"/>
       <c r="S409" s="2" t="inlineStr"/>
       <c r="T409" s="2" t="inlineStr"/>
-      <c r="U409" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V409" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
       <c r="W409" s="2" t="inlineStr"/>
       <c r="X409" s="2" t="inlineStr"/>
       <c r="Y409" s="2" t="n">
-        <v>8.35</v>
+        <v>3.03</v>
       </c>
       <c r="Z409" s="2" t="n">
-        <v>-6.33</v>
+        <v>-18.88</v>
       </c>
       <c r="AA409" s="2" t="n">
-        <v>-2.72</v>
+        <v>-14.36</v>
       </c>
       <c r="AB409" s="2" t="n">
-        <v>0.09</v>
+        <v>-5.25</v>
       </c>
       <c r="AC409" s="2" t="n">
-        <v>-5.73</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>TTD US</t>
+          <t>TT US</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>14.43</v>
+        <v>447.9</v>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>-12.35</v>
+        <v>2.06</v>
       </c>
       <c r="F410" s="2" t="n">
-        <v>-31</v>
+        <v>-2.3</v>
       </c>
       <c r="G410" s="2" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
-      <c r="I410" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>13.22</v>
+      </c>
+      <c r="H410" s="2" t="inlineStr"/>
+      <c r="I410" s="2" t="inlineStr"/>
       <c r="J410" s="2" t="inlineStr"/>
       <c r="K410" s="2" t="inlineStr"/>
       <c r="L410" s="2" t="inlineStr"/>
-      <c r="M410" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M410" s="2" t="inlineStr"/>
       <c r="N410" s="2" t="inlineStr"/>
       <c r="O410" s="2" t="inlineStr"/>
       <c r="P410" s="2" t="inlineStr"/>
@@ -28664,126 +28656,136 @@
       <c r="R410" s="2" t="inlineStr"/>
       <c r="S410" s="2" t="inlineStr"/>
       <c r="T410" s="2" t="inlineStr"/>
-      <c r="U410" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="V410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V410" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="W410" s="2" t="inlineStr"/>
       <c r="X410" s="2" t="inlineStr"/>
       <c r="Y410" s="2" t="n">
-        <v>-142.86</v>
+        <v>8.35</v>
       </c>
       <c r="Z410" s="2" t="n">
-        <v>-56.73</v>
+        <v>-6.33</v>
       </c>
       <c r="AA410" s="2" t="n">
-        <v>-50.84</v>
+        <v>-2.72</v>
       </c>
       <c r="AB410" s="2" t="n">
-        <v>3.72</v>
+        <v>0.09</v>
       </c>
       <c r="AC410" s="2" t="n">
-        <v>6.65</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TTWO US</t>
+          <t>TTD US</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Trade Desk (The)</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>214.69</v>
+        <v>14.43</v>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-0.66</v>
+        <v>-12.35</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>-3.3</v>
+        <v>-31</v>
       </c>
       <c r="G411" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H411" s="2" t="inlineStr"/>
-      <c r="I411" s="2" t="inlineStr"/>
+        <v>4.73</v>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="J411" s="2" t="inlineStr"/>
       <c r="K411" s="2" t="inlineStr"/>
       <c r="L411" s="2" t="inlineStr"/>
-      <c r="M411" s="2" t="inlineStr"/>
+      <c r="M411" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N411" s="2" t="inlineStr"/>
       <c r="O411" s="2" t="inlineStr"/>
-      <c r="P411" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P411" s="2" t="inlineStr"/>
       <c r="Q411" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R411" s="2" t="inlineStr"/>
       <c r="S411" s="2" t="inlineStr"/>
       <c r="T411" s="2" t="inlineStr"/>
       <c r="U411" s="2" t="inlineStr">
         <is>
-          <t>预1</t>
+          <t>预-1</t>
         </is>
       </c>
       <c r="V411" s="2" t="inlineStr"/>
       <c r="W411" s="2" t="inlineStr"/>
       <c r="X411" s="2" t="inlineStr"/>
       <c r="Y411" s="2" t="n">
-        <v>-12.05</v>
+        <v>-142.86</v>
       </c>
       <c r="Z411" s="2" t="n">
-        <v>-15.95</v>
+        <v>-56.73</v>
       </c>
       <c r="AA411" s="2" t="n">
-        <v>-6.35</v>
+        <v>-50.84</v>
       </c>
       <c r="AB411" s="2" t="n">
-        <v>-7.71</v>
+        <v>3.72</v>
       </c>
       <c r="AC411" s="2" t="n">
-        <v>-10.7</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TXN US</t>
+          <t>TTWO US</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>258.44</v>
+        <v>214.69</v>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>4.09</v>
+        <v>-0.66</v>
       </c>
       <c r="F412" s="2" t="n">
-        <v>0.5</v>
+        <v>-3.3</v>
       </c>
       <c r="G412" s="2" t="n">
-        <v>-4.38</v>
+        <v>0.37</v>
       </c>
       <c r="H412" s="2" t="inlineStr"/>
       <c r="I412" s="2" t="inlineStr"/>
@@ -28793,66 +28795,66 @@
       <c r="M412" s="2" t="inlineStr"/>
       <c r="N412" s="2" t="inlineStr"/>
       <c r="O412" s="2" t="inlineStr"/>
-      <c r="P412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q412" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R412" s="2" t="inlineStr"/>
       <c r="S412" s="2" t="inlineStr"/>
       <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V412" s="2" t="inlineStr">
+      <c r="U412" s="2" t="inlineStr">
         <is>
           <t>预1</t>
         </is>
       </c>
+      <c r="V412" s="2" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
       <c r="X412" s="2" t="inlineStr"/>
       <c r="Y412" s="2" t="n">
-        <v>54.79</v>
+        <v>-12.05</v>
       </c>
       <c r="Z412" s="2" t="n">
-        <v>6.46</v>
+        <v>-15.95</v>
       </c>
       <c r="AA412" s="2" t="n">
-        <v>-2.52</v>
+        <v>-6.35</v>
       </c>
       <c r="AB412" s="2" t="n">
-        <v>-0.41</v>
+        <v>-7.71</v>
       </c>
       <c r="AC412" s="2" t="n">
-        <v>-12.22</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TXT US</t>
+          <t>TXN US</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>79.06999999999999</v>
+        <v>258.44</v>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>-1.15</v>
+        <v>4.09</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>-12.8</v>
+        <v>0.5</v>
       </c>
       <c r="G413" s="2" t="n">
-        <v>-9.73</v>
+        <v>-4.38</v>
       </c>
       <c r="H413" s="2" t="inlineStr"/>
       <c r="I413" s="2" t="inlineStr"/>
@@ -28862,9 +28864,7 @@
       <c r="M413" s="2" t="inlineStr"/>
       <c r="N413" s="2" t="inlineStr"/>
       <c r="O413" s="2" t="inlineStr"/>
-      <c r="P413" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P413" s="2" t="inlineStr"/>
       <c r="Q413" s="2" t="n">
         <v>0</v>
       </c>
@@ -28874,52 +28874,56 @@
       <c r="U413" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="W413" s="2" t="inlineStr"/>
       <c r="X413" s="2" t="inlineStr"/>
       <c r="Y413" s="2" t="n">
-        <v>-2.58</v>
+        <v>54.79</v>
       </c>
       <c r="Z413" s="2" t="n">
-        <v>-18.51</v>
+        <v>6.46</v>
       </c>
       <c r="AA413" s="2" t="n">
-        <v>-15.34</v>
+        <v>-2.52</v>
       </c>
       <c r="AB413" s="2" t="n">
-        <v>-3.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AC413" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>-12.22</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TYL US</t>
+          <t>TXT US</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>364.03</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-3.32</v>
+        <v>-1.15</v>
       </c>
       <c r="F414" s="2" t="n">
-        <v>11.4</v>
+        <v>-12.8</v>
       </c>
       <c r="G414" s="2" t="n">
-        <v>108.82</v>
+        <v>-9.73</v>
       </c>
       <c r="H414" s="2" t="inlineStr"/>
       <c r="I414" s="2" t="inlineStr"/>
@@ -28930,7 +28934,7 @@
       <c r="N414" s="2" t="inlineStr"/>
       <c r="O414" s="2" t="inlineStr"/>
       <c r="P414" s="2" t="n">
-        <v>-9</v>
+        <v>9</v>
       </c>
       <c r="Q414" s="2" t="n">
         <v>0</v>
@@ -28939,58 +28943,54 @@
       <c r="S414" s="2" t="inlineStr"/>
       <c r="T414" s="2" t="inlineStr"/>
       <c r="U414" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V414" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V414" s="2" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
       <c r="X414" s="2" t="inlineStr"/>
       <c r="Y414" s="2" t="n">
-        <v>-33.73</v>
+        <v>-2.58</v>
       </c>
       <c r="Z414" s="2" t="n">
-        <v>-15.25</v>
+        <v>-18.51</v>
       </c>
       <c r="AA414" s="2" t="n">
-        <v>-24.11</v>
+        <v>-15.34</v>
       </c>
       <c r="AB414" s="2" t="n">
-        <v>-2.16</v>
+        <v>-3.89</v>
       </c>
       <c r="AC414" s="2" t="n">
-        <v>16.54</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>UAL US</t>
+          <t>TYL US</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>111.38</v>
+        <v>364.03</v>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.57</v>
+        <v>-3.32</v>
       </c>
       <c r="F415" s="2" t="n">
-        <v>2.7</v>
+        <v>11.4</v>
       </c>
       <c r="G415" s="2" t="n">
-        <v>-8.82</v>
+        <v>108.82</v>
       </c>
       <c r="H415" s="2" t="inlineStr"/>
       <c r="I415" s="2" t="inlineStr"/>
@@ -29001,7 +29001,7 @@
       <c r="N415" s="2" t="inlineStr"/>
       <c r="O415" s="2" t="inlineStr"/>
       <c r="P415" s="2" t="n">
-        <v>13</v>
+        <v>-9</v>
       </c>
       <c r="Q415" s="2" t="n">
         <v>0</v>
@@ -29010,58 +29010,58 @@
       <c r="S415" s="2" t="inlineStr"/>
       <c r="T415" s="2" t="inlineStr"/>
       <c r="U415" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V415" s="2" t="inlineStr">
         <is>
-          <t>预1</t>
+          <t>预-1</t>
         </is>
       </c>
       <c r="W415" s="2" t="inlineStr"/>
       <c r="X415" s="2" t="inlineStr"/>
       <c r="Y415" s="2" t="n">
-        <v>15.4</v>
+        <v>-33.73</v>
       </c>
       <c r="Z415" s="2" t="n">
-        <v>-4.36</v>
+        <v>-15.25</v>
       </c>
       <c r="AA415" s="2" t="n">
-        <v>-0.76</v>
+        <v>-24.11</v>
       </c>
       <c r="AB415" s="2" t="n">
-        <v>0.86</v>
+        <v>-2.16</v>
       </c>
       <c r="AC415" s="2" t="n">
-        <v>-14.73</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>UHS US</t>
+          <t>UAL US</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>169.65</v>
+        <v>111.38</v>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>-2.52</v>
+        <v>0.57</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>-2.7</v>
+        <v>2.7</v>
       </c>
       <c r="G416" s="2" t="n">
-        <v>111.95</v>
+        <v>-8.82</v>
       </c>
       <c r="H416" s="2" t="inlineStr"/>
       <c r="I416" s="2" t="inlineStr"/>
@@ -29070,67 +29070,69 @@
       <c r="L416" s="2" t="inlineStr"/>
       <c r="M416" s="2" t="inlineStr"/>
       <c r="N416" s="2" t="inlineStr"/>
-      <c r="O416" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P416" s="2" t="inlineStr"/>
+      <c r="O416" s="2" t="inlineStr"/>
+      <c r="P416" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="Q416" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R416" s="2" t="inlineStr"/>
       <c r="S416" s="2" t="inlineStr"/>
       <c r="T416" s="2" t="inlineStr"/>
-      <c r="U416" s="2" t="inlineStr">
+      <c r="U416" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V416" s="2" t="inlineStr">
         <is>
           <t>预1</t>
         </is>
       </c>
-      <c r="V416" s="2" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>
       <c r="X416" s="2" t="inlineStr"/>
       <c r="Y416" s="2" t="n">
-        <v>-38.91</v>
+        <v>15.4</v>
       </c>
       <c r="Z416" s="2" t="n">
-        <v>-18.96</v>
+        <v>-4.36</v>
       </c>
       <c r="AA416" s="2" t="n">
-        <v>-21.27</v>
+        <v>-0.76</v>
       </c>
       <c r="AB416" s="2" t="n">
-        <v>-0.58</v>
+        <v>0.86</v>
       </c>
       <c r="AC416" s="2" t="n">
-        <v>-0.04</v>
+        <v>-14.73</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>ULTA US</t>
+          <t>UHS US</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>564.12</v>
+        <v>169.65</v>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>-2.99</v>
+        <v>-2.52</v>
       </c>
       <c r="F417" s="2" t="n">
-        <v>4.5</v>
+        <v>-2.7</v>
       </c>
       <c r="G417" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>111.95</v>
       </c>
       <c r="H417" s="2" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr"/>
@@ -29139,65 +29141,67 @@
       <c r="L417" s="2" t="inlineStr"/>
       <c r="M417" s="2" t="inlineStr"/>
       <c r="N417" s="2" t="inlineStr"/>
-      <c r="O417" s="2" t="inlineStr"/>
-      <c r="P417" s="2" t="n">
-        <v>-13</v>
-      </c>
+      <c r="O417" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P417" s="2" t="inlineStr"/>
       <c r="Q417" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R417" s="2" t="inlineStr"/>
       <c r="S417" s="2" t="inlineStr"/>
       <c r="T417" s="2" t="inlineStr"/>
-      <c r="U417" s="2" t="inlineStr"/>
-      <c r="V417" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U417" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="V417" s="2" t="inlineStr"/>
       <c r="W417" s="2" t="inlineStr"/>
       <c r="X417" s="2" t="inlineStr"/>
       <c r="Y417" s="2" t="n">
-        <v>5.84</v>
+        <v>-38.91</v>
       </c>
       <c r="Z417" s="2" t="n">
-        <v>-6.95</v>
+        <v>-18.96</v>
       </c>
       <c r="AA417" s="2" t="n">
-        <v>4.21</v>
+        <v>-21.27</v>
       </c>
       <c r="AB417" s="2" t="n">
-        <v>7.81</v>
+        <v>-0.58</v>
       </c>
       <c r="AC417" s="2" t="n">
-        <v>1.38</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>UNH US</t>
+          <t>ULTA US</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>397.14</v>
+        <v>564.12</v>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>2.65</v>
+        <v>-2.99</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>11.1</v>
+        <v>4.5</v>
       </c>
       <c r="G418" s="2" t="n">
-        <v>-13.85</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H418" s="2" t="inlineStr"/>
       <c r="I418" s="2" t="inlineStr"/>
@@ -29207,52 +29211,50 @@
       <c r="M418" s="2" t="inlineStr"/>
       <c r="N418" s="2" t="inlineStr"/>
       <c r="O418" s="2" t="inlineStr"/>
-      <c r="P418" s="2" t="inlineStr"/>
+      <c r="P418" s="2" t="n">
+        <v>-13</v>
+      </c>
       <c r="Q418" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R418" s="2" t="inlineStr"/>
       <c r="S418" s="2" t="inlineStr"/>
       <c r="T418" s="2" t="inlineStr"/>
-      <c r="U418" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="V418" s="2" t="inlineStr"/>
-      <c r="W418" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W418" s="2" t="inlineStr"/>
       <c r="X418" s="2" t="inlineStr"/>
       <c r="Y418" s="2" t="n">
-        <v>28.06</v>
+        <v>5.84</v>
       </c>
       <c r="Z418" s="2" t="n">
-        <v>4.82</v>
+        <v>-6.95</v>
       </c>
       <c r="AA418" s="2" t="n">
-        <v>1.17</v>
+        <v>4.21</v>
       </c>
       <c r="AB418" s="2" t="n">
-        <v>0.79</v>
+        <v>7.81</v>
       </c>
       <c r="AC418" s="2" t="n">
-        <v>-3.38</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>UNP US</t>
+          <t>UNH US</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>289.62</v>
+        <v>397.14</v>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
@@ -29260,153 +29262,153 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>3.71</v>
+        <v>2.65</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="G419" s="2" t="n">
-        <v>81.27</v>
+        <v>-13.85</v>
       </c>
       <c r="H419" s="2" t="inlineStr"/>
       <c r="I419" s="2" t="inlineStr"/>
-      <c r="J419" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J419" s="2" t="inlineStr"/>
       <c r="K419" s="2" t="inlineStr"/>
       <c r="L419" s="2" t="inlineStr"/>
-      <c r="M419" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M419" s="2" t="inlineStr"/>
       <c r="N419" s="2" t="inlineStr"/>
       <c r="O419" s="2" t="inlineStr"/>
-      <c r="P419" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P419" s="2" t="inlineStr"/>
       <c r="Q419" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R419" s="2" t="inlineStr"/>
       <c r="S419" s="2" t="inlineStr"/>
       <c r="T419" s="2" t="inlineStr"/>
-      <c r="U419" s="2" t="inlineStr"/>
+      <c r="U419" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="V419" s="2" t="inlineStr"/>
-      <c r="W419" s="2" t="inlineStr"/>
+      <c r="W419" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X419" s="2" t="inlineStr"/>
       <c r="Y419" s="2" t="n">
-        <v>37.48</v>
+        <v>28.06</v>
       </c>
       <c r="Z419" s="2" t="n">
-        <v>6.1</v>
+        <v>4.82</v>
       </c>
       <c r="AA419" s="2" t="n">
-        <v>10.24</v>
+        <v>1.17</v>
       </c>
       <c r="AB419" s="2" t="n">
-        <v>-6.37</v>
+        <v>0.79</v>
       </c>
       <c r="AC419" s="2" t="n">
-        <v>-1.46</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>UPS US</t>
+          <t>UNP US</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>102.29</v>
+        <v>289.62</v>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.22</v>
+        <v>3.71</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>-1.4</v>
+        <v>8.1</v>
       </c>
       <c r="G420" s="2" t="n">
-        <v>-14.23</v>
+        <v>81.27</v>
       </c>
       <c r="H420" s="2" t="inlineStr"/>
       <c r="I420" s="2" t="inlineStr"/>
-      <c r="J420" s="2" t="inlineStr"/>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K420" s="2" t="inlineStr"/>
       <c r="L420" s="2" t="inlineStr"/>
-      <c r="M420" s="2" t="inlineStr"/>
+      <c r="M420" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N420" s="2" t="inlineStr"/>
       <c r="O420" s="2" t="inlineStr"/>
-      <c r="P420" s="2" t="inlineStr"/>
+      <c r="P420" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q420" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R420" s="2" t="inlineStr"/>
       <c r="S420" s="2" t="inlineStr"/>
       <c r="T420" s="2" t="inlineStr"/>
       <c r="U420" s="2" t="inlineStr"/>
-      <c r="V420" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="W420" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr"/>
       <c r="X420" s="2" t="inlineStr"/>
       <c r="Y420" s="2" t="n">
-        <v>16.95</v>
+        <v>37.48</v>
       </c>
       <c r="Z420" s="2" t="n">
-        <v>-4.52</v>
+        <v>6.1</v>
       </c>
       <c r="AA420" s="2" t="n">
-        <v>-0.73</v>
+        <v>10.24</v>
       </c>
       <c r="AB420" s="2" t="n">
-        <v>-3.06</v>
+        <v>-6.37</v>
       </c>
       <c r="AC420" s="2" t="n">
-        <v>-0.49</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>URI US</t>
+          <t>UPS US</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>United Rentals</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>1009.86</v>
+        <v>102.29</v>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>2.6</v>
+        <v>0.22</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>6</v>
+        <v>-1.4</v>
       </c>
       <c r="G421" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>-14.23</v>
       </c>
       <c r="H421" s="2" t="inlineStr"/>
       <c r="I421" s="2" t="inlineStr"/>
@@ -29416,50 +29418,52 @@
       <c r="M421" s="2" t="inlineStr"/>
       <c r="N421" s="2" t="inlineStr"/>
       <c r="O421" s="2" t="inlineStr"/>
-      <c r="P421" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P421" s="2" t="inlineStr"/>
       <c r="Q421" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R421" s="2" t="inlineStr"/>
       <c r="S421" s="2" t="inlineStr"/>
       <c r="T421" s="2" t="inlineStr"/>
-      <c r="U421" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V421" s="2" t="inlineStr"/>
-      <c r="W421" s="2" t="inlineStr"/>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="W421" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X421" s="2" t="inlineStr"/>
       <c r="Y421" s="2" t="n">
-        <v>23.71</v>
+        <v>16.95</v>
       </c>
       <c r="Z421" s="2" t="n">
-        <v>0.06</v>
+        <v>-4.52</v>
       </c>
       <c r="AA421" s="2" t="n">
-        <v>3.75</v>
+        <v>-0.73</v>
       </c>
       <c r="AB421" s="2" t="n">
-        <v>-1.86</v>
+        <v>-3.06</v>
       </c>
       <c r="AC421" s="2" t="n">
-        <v>-14.23</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>USB US</t>
+          <t>URI US</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>United Rentals</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>63.37</v>
+        <v>1009.86</v>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
@@ -29467,13 +29471,13 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="G422" s="2" t="n">
-        <v>98.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H422" s="2" t="inlineStr"/>
       <c r="I422" s="2" t="inlineStr"/>
@@ -29483,7 +29487,9 @@
       <c r="M422" s="2" t="inlineStr"/>
       <c r="N422" s="2" t="inlineStr"/>
       <c r="O422" s="2" t="inlineStr"/>
-      <c r="P422" s="2" t="inlineStr"/>
+      <c r="P422" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q422" s="2" t="n">
         <v>0</v>
       </c>
@@ -29497,34 +29503,34 @@
       <c r="W422" s="2" t="inlineStr"/>
       <c r="X422" s="2" t="inlineStr"/>
       <c r="Y422" s="2" t="n">
-        <v>39.1</v>
+        <v>23.71</v>
       </c>
       <c r="Z422" s="2" t="n">
-        <v>7.31</v>
+        <v>0.06</v>
       </c>
       <c r="AA422" s="2" t="n">
-        <v>7.21</v>
+        <v>3.75</v>
       </c>
       <c r="AB422" s="2" t="n">
-        <v>1.19</v>
+        <v>-1.86</v>
       </c>
       <c r="AC422" s="2" t="n">
-        <v>-1.75</v>
+        <v>-14.23</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>V US</t>
+          <t>USB US</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>375.07</v>
+        <v>63.37</v>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
@@ -29532,74 +29538,64 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>12.9</v>
+        <v>10.2</v>
       </c>
       <c r="G423" s="2" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="H423" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+        <v>98.41</v>
+      </c>
+      <c r="H423" s="2" t="inlineStr"/>
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr"/>
       <c r="K423" s="2" t="inlineStr"/>
       <c r="L423" s="2" t="inlineStr"/>
-      <c r="M423" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M423" s="2" t="inlineStr"/>
       <c r="N423" s="2" t="inlineStr"/>
-      <c r="O423" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O423" s="2" t="inlineStr"/>
       <c r="P423" s="2" t="inlineStr"/>
       <c r="Q423" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R423" s="2" t="inlineStr"/>
       <c r="S423" s="2" t="inlineStr"/>
       <c r="T423" s="2" t="inlineStr"/>
-      <c r="U423" s="2" t="inlineStr"/>
-      <c r="V423" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W423" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr"/>
       <c r="X423" s="2" t="inlineStr"/>
       <c r="Y423" s="2" t="n">
-        <v>17.65</v>
+        <v>39.1</v>
       </c>
       <c r="Z423" s="2" t="n">
-        <v>2.37</v>
+        <v>7.31</v>
       </c>
       <c r="AA423" s="2" t="n">
-        <v>2.52</v>
+        <v>7.21</v>
       </c>
       <c r="AB423" s="2" t="n">
-        <v>-1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AC423" s="2" t="n">
-        <v>4.92</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>VEEV US</t>
+          <t>V US</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>275.09</v>
+        <v>375.07</v>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
@@ -29607,20 +29603,26 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>2.42</v>
+        <v>1.56</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>46.3</v>
+        <v>12.9</v>
       </c>
       <c r="G424" s="2" t="n">
-        <v>104.52</v>
-      </c>
-      <c r="H424" s="2" t="inlineStr"/>
+        <v>95.8</v>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr"/>
       <c r="K424" s="2" t="inlineStr"/>
       <c r="L424" s="2" t="inlineStr"/>
-      <c r="M424" s="2" t="inlineStr"/>
+      <c r="M424" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N424" s="2" t="inlineStr"/>
       <c r="O424" s="2" t="n">
         <v>-9</v>
@@ -29632,59 +29634,57 @@
       <c r="R424" s="2" t="inlineStr"/>
       <c r="S424" s="2" t="inlineStr"/>
       <c r="T424" s="2" t="inlineStr"/>
-      <c r="U424" s="2" t="n">
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V424" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="W424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X424" s="2" t="inlineStr"/>
       <c r="Y424" s="2" t="n">
-        <v>-6.93</v>
+        <v>17.65</v>
       </c>
       <c r="Z424" s="2" t="n">
-        <v>14.96</v>
+        <v>2.37</v>
       </c>
       <c r="AA424" s="2" t="n">
-        <v>11.42</v>
+        <v>2.52</v>
       </c>
       <c r="AB424" s="2" t="n">
-        <v>-0.38</v>
+        <v>-1.67</v>
       </c>
       <c r="AC424" s="2" t="n">
-        <v>21.54</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>VICI US</t>
+          <t>VEEV US</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>25.42</v>
+        <v>275.09</v>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>-0.6</v>
+        <v>2.42</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>-7</v>
+        <v>46.3</v>
       </c>
       <c r="G425" s="2" t="n">
-        <v>0.63</v>
+        <v>104.52</v>
       </c>
       <c r="H425" s="2" t="inlineStr"/>
       <c r="I425" s="2" t="inlineStr"/>
@@ -29693,81 +29693,81 @@
       <c r="L425" s="2" t="inlineStr"/>
       <c r="M425" s="2" t="inlineStr"/>
       <c r="N425" s="2" t="inlineStr"/>
-      <c r="O425" s="2" t="inlineStr"/>
-      <c r="P425" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="O425" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P425" s="2" t="inlineStr"/>
       <c r="Q425" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R425" s="2" t="inlineStr"/>
       <c r="S425" s="2" t="inlineStr"/>
       <c r="T425" s="2" t="inlineStr"/>
-      <c r="U425" s="2" t="inlineStr"/>
-      <c r="V425" s="2" t="inlineStr"/>
+      <c r="U425" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V425" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W425" s="2" t="inlineStr"/>
       <c r="X425" s="2" t="inlineStr"/>
       <c r="Y425" s="2" t="n">
-        <v>-16.17</v>
+        <v>-6.93</v>
       </c>
       <c r="Z425" s="2" t="n">
-        <v>-16.93</v>
+        <v>14.96</v>
       </c>
       <c r="AA425" s="2" t="n">
-        <v>-12.52</v>
+        <v>11.42</v>
       </c>
       <c r="AB425" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.38</v>
       </c>
       <c r="AC425" s="2" t="n">
-        <v>-1.42</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>VLO US</t>
+          <t>VICI US</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>370.72</v>
+        <v>25.42</v>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>42.8</v>
+        <v>-7</v>
       </c>
       <c r="G426" s="2" t="n">
-        <v>103.03</v>
+        <v>0.63</v>
       </c>
       <c r="H426" s="2" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr"/>
-      <c r="J426" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J426" s="2" t="inlineStr"/>
       <c r="K426" s="2" t="inlineStr"/>
       <c r="L426" s="2" t="inlineStr"/>
-      <c r="M426" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M426" s="2" t="inlineStr"/>
       <c r="N426" s="2" t="inlineStr"/>
-      <c r="O426" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="P426" s="2" t="inlineStr"/>
+      <c r="O426" s="2" t="inlineStr"/>
+      <c r="P426" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q426" s="2" t="n">
         <v>0</v>
       </c>
@@ -29779,62 +29779,66 @@
       <c r="W426" s="2" t="inlineStr"/>
       <c r="X426" s="2" t="inlineStr"/>
       <c r="Y426" s="2" t="n">
-        <v>106.19</v>
+        <v>-16.17</v>
       </c>
       <c r="Z426" s="2" t="n">
-        <v>53.38</v>
+        <v>-16.93</v>
       </c>
       <c r="AA426" s="2" t="n">
-        <v>37.18</v>
+        <v>-12.52</v>
       </c>
       <c r="AB426" s="2" t="n">
-        <v>5.19</v>
+        <v>-0.9</v>
       </c>
       <c r="AC426" s="2" t="n">
-        <v>22.85</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>VLTO US</t>
+          <t>VLO US</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>96.31</v>
+        <v>370.72</v>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>-0.39</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>5.9</v>
+        <v>42.8</v>
       </c>
       <c r="G427" s="2" t="n">
-        <v>86.87</v>
+        <v>103.03</v>
       </c>
       <c r="H427" s="2" t="inlineStr"/>
       <c r="I427" s="2" t="inlineStr"/>
-      <c r="J427" s="2" t="inlineStr"/>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K427" s="2" t="inlineStr"/>
       <c r="L427" s="2" t="inlineStr"/>
-      <c r="M427" s="2" t="inlineStr"/>
+      <c r="M427" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N427" s="2" t="inlineStr"/>
       <c r="O427" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P427" s="2" t="n">
-        <v>9</v>
-      </c>
+        <v>-13</v>
+      </c>
+      <c r="P427" s="2" t="inlineStr"/>
       <c r="Q427" s="2" t="n">
         <v>0</v>
       </c>
@@ -29846,48 +29850,48 @@
       <c r="W427" s="2" t="inlineStr"/>
       <c r="X427" s="2" t="inlineStr"/>
       <c r="Y427" s="2" t="n">
-        <v>-0.53</v>
+        <v>106.19</v>
       </c>
       <c r="Z427" s="2" t="n">
-        <v>-8.029999999999999</v>
+        <v>53.38</v>
       </c>
       <c r="AA427" s="2" t="n">
-        <v>-4.77</v>
+        <v>37.18</v>
       </c>
       <c r="AB427" s="2" t="n">
-        <v>-1.73</v>
+        <v>5.19</v>
       </c>
       <c r="AC427" s="2" t="n">
-        <v>0.62</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>VMC US</t>
+          <t>VLTO US</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>262.63</v>
+        <v>96.31</v>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>-1.18</v>
+        <v>-0.39</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>-7.9</v>
+        <v>5.9</v>
       </c>
       <c r="G428" s="2" t="n">
-        <v>3.12</v>
+        <v>86.87</v>
       </c>
       <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr"/>
@@ -29896,65 +29900,65 @@
       <c r="L428" s="2" t="inlineStr"/>
       <c r="M428" s="2" t="inlineStr"/>
       <c r="N428" s="2" t="inlineStr"/>
-      <c r="O428" s="2" t="inlineStr"/>
-      <c r="P428" s="2" t="inlineStr"/>
+      <c r="O428" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q428" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R428" s="2" t="inlineStr"/>
       <c r="S428" s="2" t="inlineStr"/>
       <c r="T428" s="2" t="inlineStr"/>
-      <c r="U428" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U428" s="2" t="inlineStr"/>
       <c r="V428" s="2" t="inlineStr"/>
       <c r="W428" s="2" t="inlineStr"/>
       <c r="X428" s="2" t="inlineStr"/>
       <c r="Y428" s="2" t="n">
-        <v>-10</v>
+        <v>-0.53</v>
       </c>
       <c r="Z428" s="2" t="n">
-        <v>-17.15</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AA428" s="2" t="n">
-        <v>-16.24</v>
+        <v>-4.77</v>
       </c>
       <c r="AB428" s="2" t="n">
-        <v>-3.39</v>
+        <v>-1.73</v>
       </c>
       <c r="AC428" s="2" t="n">
-        <v>-4.78</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>VRSK US</t>
+          <t>VMC US</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>185.79</v>
+        <v>262.63</v>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>-2.3</v>
+        <v>-1.18</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>0.2</v>
+        <v>-7.9</v>
       </c>
       <c r="G429" s="2" t="n">
-        <v>12.2</v>
+        <v>3.12</v>
       </c>
       <c r="H429" s="2" t="inlineStr"/>
       <c r="I429" s="2" t="inlineStr"/>
@@ -29964,68 +29968,64 @@
       <c r="M429" s="2" t="inlineStr"/>
       <c r="N429" s="2" t="inlineStr"/>
       <c r="O429" s="2" t="inlineStr"/>
-      <c r="P429" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P429" s="2" t="inlineStr"/>
       <c r="Q429" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R429" s="2" t="inlineStr"/>
       <c r="S429" s="2" t="inlineStr"/>
       <c r="T429" s="2" t="inlineStr"/>
-      <c r="U429" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V429" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U429" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
+      <c r="V429" s="2" t="inlineStr"/>
       <c r="W429" s="2" t="inlineStr"/>
       <c r="X429" s="2" t="inlineStr"/>
       <c r="Y429" s="2" t="n">
-        <v>-16.07</v>
+        <v>-10</v>
       </c>
       <c r="Z429" s="2" t="n">
-        <v>-16.85</v>
+        <v>-17.15</v>
       </c>
       <c r="AA429" s="2" t="n">
-        <v>-14.01</v>
+        <v>-16.24</v>
       </c>
       <c r="AB429" s="2" t="n">
-        <v>-1.81</v>
+        <v>-3.39</v>
       </c>
       <c r="AC429" s="2" t="n">
-        <v>1.53</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>VRSN US</t>
+          <t>VRSK US</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>292.08</v>
+        <v>185.79</v>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="G430" s="2" t="n">
-        <v>76.79000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H430" s="2" t="inlineStr"/>
       <c r="I430" s="2" t="inlineStr"/>
@@ -30035,62 +30035,68 @@
       <c r="M430" s="2" t="inlineStr"/>
       <c r="N430" s="2" t="inlineStr"/>
       <c r="O430" s="2" t="inlineStr"/>
-      <c r="P430" s="2" t="inlineStr"/>
+      <c r="P430" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q430" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R430" s="2" t="inlineStr"/>
       <c r="S430" s="2" t="inlineStr"/>
       <c r="T430" s="2" t="inlineStr"/>
-      <c r="U430" s="2" t="inlineStr"/>
-      <c r="V430" s="2" t="inlineStr"/>
-      <c r="W430" s="2" t="n">
+      <c r="U430" s="2" t="n">
         <v>-1</v>
       </c>
+      <c r="V430" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="W430" s="2" t="inlineStr"/>
       <c r="X430" s="2" t="inlineStr"/>
       <c r="Y430" s="2" t="n">
-        <v>21.43</v>
+        <v>-16.07</v>
       </c>
       <c r="Z430" s="2" t="n">
-        <v>2.32</v>
+        <v>-16.85</v>
       </c>
       <c r="AA430" s="2" t="n">
-        <v>-7.29</v>
+        <v>-14.01</v>
       </c>
       <c r="AB430" s="2" t="n">
-        <v>0.19</v>
+        <v>-1.81</v>
       </c>
       <c r="AC430" s="2" t="n">
-        <v>0.89</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>VRSN US</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>280.53</v>
+        <v>292.08</v>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>4.51</v>
+        <v>2.1</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>-1.8</v>
+        <v>10</v>
       </c>
       <c r="G431" s="2" t="n">
-        <v>32.75</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="H431" s="2" t="inlineStr"/>
       <c r="I431" s="2" t="inlineStr"/>
@@ -30102,75 +30108,67 @@
       <c r="O431" s="2" t="inlineStr"/>
       <c r="P431" s="2" t="inlineStr"/>
       <c r="Q431" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R431" s="2" t="inlineStr"/>
       <c r="S431" s="2" t="inlineStr"/>
       <c r="T431" s="2" t="inlineStr"/>
       <c r="U431" s="2" t="inlineStr"/>
-      <c r="V431" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="V431" s="2" t="inlineStr"/>
       <c r="W431" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X431" s="2" t="inlineStr"/>
       <c r="Y431" s="2" t="n">
-        <v>47.69</v>
+        <v>21.43</v>
       </c>
       <c r="Z431" s="2" t="n">
-        <v>8.48</v>
+        <v>2.32</v>
       </c>
       <c r="AA431" s="2" t="n">
-        <v>13.17</v>
+        <v>-7.29</v>
       </c>
       <c r="AB431" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="AC431" s="2" t="n">
-        <v>-0.08</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>VRTX US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>546.12</v>
+        <v>280.53</v>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>2.21</v>
+        <v>4.51</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>16</v>
+        <v>-1.8</v>
       </c>
       <c r="G432" s="2" t="n">
-        <v>57.73</v>
+        <v>32.75</v>
       </c>
       <c r="H432" s="2" t="inlineStr"/>
       <c r="I432" s="2" t="inlineStr"/>
-      <c r="J432" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J432" s="2" t="inlineStr"/>
       <c r="K432" s="2" t="inlineStr"/>
       <c r="L432" s="2" t="inlineStr"/>
-      <c r="M432" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M432" s="2" t="inlineStr"/>
       <c r="N432" s="2" t="inlineStr"/>
       <c r="O432" s="2" t="inlineStr"/>
       <c r="P432" s="2" t="inlineStr"/>
@@ -30180,73 +30178,69 @@
       <c r="R432" s="2" t="inlineStr"/>
       <c r="S432" s="2" t="inlineStr"/>
       <c r="T432" s="2" t="inlineStr"/>
-      <c r="U432" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U432" s="2" t="inlineStr"/>
       <c r="V432" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W432" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W432" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="X432" s="2" t="inlineStr"/>
       <c r="Y432" s="2" t="n">
-        <v>32.77</v>
+        <v>47.69</v>
       </c>
       <c r="Z432" s="2" t="n">
-        <v>9.82</v>
+        <v>8.48</v>
       </c>
       <c r="AA432" s="2" t="n">
-        <v>6.49</v>
+        <v>13.17</v>
       </c>
       <c r="AB432" s="2" t="n">
-        <v>0.44</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AC432" s="2" t="n">
-        <v>9.41</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>VRTX US</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>149.3</v>
+        <v>546.12</v>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>-1.82</v>
+        <v>2.21</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>-3.4</v>
+        <v>16</v>
       </c>
       <c r="G433" s="2" t="n">
-        <v>-6.77</v>
+        <v>57.73</v>
       </c>
       <c r="H433" s="2" t="inlineStr"/>
-      <c r="I433" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+      <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>底背离</t>
+          <t>顶背离</t>
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr"/>
       <c r="L433" s="2" t="inlineStr"/>
       <c r="M433" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N433" s="2" t="inlineStr"/>
       <c r="O433" s="2" t="inlineStr"/>
@@ -30257,60 +30251,74 @@
       <c r="R433" s="2" t="inlineStr"/>
       <c r="S433" s="2" t="inlineStr"/>
       <c r="T433" s="2" t="inlineStr"/>
-      <c r="U433" s="2" t="inlineStr"/>
-      <c r="V433" s="2" t="inlineStr"/>
+      <c r="U433" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="W433" s="2" t="inlineStr"/>
       <c r="X433" s="2" t="inlineStr"/>
       <c r="Y433" s="2" t="n">
-        <v>-26.71</v>
+        <v>32.77</v>
       </c>
       <c r="Z433" s="2" t="n">
-        <v>-18.17</v>
+        <v>9.82</v>
       </c>
       <c r="AA433" s="2" t="n">
-        <v>-7.95</v>
+        <v>6.49</v>
       </c>
       <c r="AB433" s="2" t="n">
-        <v>7.29</v>
+        <v>0.44</v>
       </c>
       <c r="AC433" s="2" t="n">
-        <v>8.1</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>VTRS US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>16.88</v>
+        <v>149.3</v>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>3.42</v>
+        <v>-1.82</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>-3.4</v>
       </c>
       <c r="G434" s="2" t="n">
-        <v>18.9</v>
+        <v>-6.77</v>
       </c>
       <c r="H434" s="2" t="inlineStr"/>
-      <c r="I434" s="2" t="inlineStr"/>
-      <c r="J434" s="2" t="inlineStr"/>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="K434" s="2" t="inlineStr"/>
       <c r="L434" s="2" t="inlineStr"/>
-      <c r="M434" s="2" t="inlineStr"/>
+      <c r="M434" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N434" s="2" t="inlineStr"/>
       <c r="O434" s="2" t="inlineStr"/>
       <c r="P434" s="2" t="inlineStr"/>
@@ -30320,45 +30328,39 @@
       <c r="R434" s="2" t="inlineStr"/>
       <c r="S434" s="2" t="inlineStr"/>
       <c r="T434" s="2" t="inlineStr"/>
-      <c r="U434" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U434" s="2" t="inlineStr"/>
       <c r="V434" s="2" t="inlineStr"/>
       <c r="W434" s="2" t="inlineStr"/>
-      <c r="X434" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="X434" s="2" t="inlineStr"/>
       <c r="Y434" s="2" t="n">
-        <v>56.9</v>
+        <v>-26.71</v>
       </c>
       <c r="Z434" s="2" t="n">
-        <v>14.49</v>
+        <v>-18.17</v>
       </c>
       <c r="AA434" s="2" t="n">
-        <v>10.72</v>
+        <v>-7.95</v>
       </c>
       <c r="AB434" s="2" t="n">
-        <v>2.84</v>
+        <v>7.29</v>
       </c>
       <c r="AC434" s="2" t="n">
-        <v>1.72</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>VZ US</t>
+          <t>VTRS US</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>50.14</v>
+        <v>16.88</v>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
@@ -30366,78 +30368,68 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G435" s="2" t="n">
-        <v>110.73</v>
+        <v>18.9</v>
       </c>
       <c r="H435" s="2" t="inlineStr"/>
-      <c r="I435" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I435" s="2" t="inlineStr"/>
       <c r="J435" s="2" t="inlineStr"/>
       <c r="K435" s="2" t="inlineStr"/>
-      <c r="L435" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
-      <c r="M435" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N435" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="L435" s="2" t="inlineStr"/>
+      <c r="M435" s="2" t="inlineStr"/>
+      <c r="N435" s="2" t="inlineStr"/>
       <c r="O435" s="2" t="inlineStr"/>
-      <c r="P435" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P435" s="2" t="inlineStr"/>
       <c r="Q435" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R435" s="2" t="inlineStr"/>
       <c r="S435" s="2" t="inlineStr"/>
       <c r="T435" s="2" t="inlineStr"/>
-      <c r="U435" s="2" t="inlineStr"/>
-      <c r="V435" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="U435" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="V435" s="2" t="inlineStr"/>
       <c r="W435" s="2" t="inlineStr"/>
-      <c r="X435" s="2" t="inlineStr"/>
+      <c r="X435" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y435" s="2" t="n">
-        <v>33.02</v>
+        <v>56.9</v>
       </c>
       <c r="Z435" s="2" t="n">
-        <v>5.09</v>
+        <v>14.49</v>
       </c>
       <c r="AA435" s="2" t="n">
-        <v>16.78</v>
+        <v>10.72</v>
       </c>
       <c r="AB435" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="AC435" s="2" t="n">
-        <v>6.97</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>WAB US</t>
+          <t>VZ US</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>282.86</v>
+        <v>50.14</v>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
@@ -30445,82 +30437,92 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="G436" s="2" t="n">
-        <v>92.55</v>
+        <v>110.73</v>
       </c>
       <c r="H436" s="2" t="inlineStr"/>
-      <c r="I436" s="2" t="inlineStr"/>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J436" s="2" t="inlineStr"/>
       <c r="K436" s="2" t="inlineStr"/>
-      <c r="L436" s="2" t="inlineStr"/>
-      <c r="M436" s="2" t="inlineStr"/>
-      <c r="N436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="O436" s="2" t="inlineStr"/>
       <c r="P436" s="2" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="Q436" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R436" s="2" t="inlineStr"/>
       <c r="S436" s="2" t="inlineStr"/>
       <c r="T436" s="2" t="inlineStr"/>
-      <c r="U436" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="V436" s="2" t="inlineStr"/>
+      <c r="U436" s="2" t="inlineStr"/>
+      <c r="V436" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="W436" s="2" t="inlineStr"/>
       <c r="X436" s="2" t="inlineStr"/>
       <c r="Y436" s="2" t="n">
-        <v>40.03</v>
+        <v>33.02</v>
       </c>
       <c r="Z436" s="2" t="n">
-        <v>7.12</v>
+        <v>5.09</v>
       </c>
       <c r="AA436" s="2" t="n">
-        <v>11.46</v>
+        <v>16.78</v>
       </c>
       <c r="AB436" s="2" t="n">
-        <v>-4.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC436" s="2" t="n">
-        <v>-4.85</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>WAT US</t>
+          <t>WAB US</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C437" s="2" t="n">
-        <v>409.38</v>
+        <v>282.86</v>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>16.6</v>
+        <v>6.3</v>
       </c>
       <c r="G437" s="2" t="n">
-        <v>92.18000000000001</v>
+        <v>92.55</v>
       </c>
       <c r="H437" s="2" t="inlineStr"/>
       <c r="I437" s="2" t="inlineStr"/>
@@ -30530,48 +30532,52 @@
       <c r="M437" s="2" t="inlineStr"/>
       <c r="N437" s="2" t="inlineStr"/>
       <c r="O437" s="2" t="inlineStr"/>
-      <c r="P437" s="2" t="inlineStr"/>
+      <c r="P437" s="2" t="n">
+        <v>-13</v>
+      </c>
       <c r="Q437" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R437" s="2" t="inlineStr"/>
       <c r="S437" s="2" t="inlineStr"/>
       <c r="T437" s="2" t="inlineStr"/>
-      <c r="U437" s="2" t="inlineStr"/>
+      <c r="U437" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="V437" s="2" t="inlineStr"/>
-      <c r="W437" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="W437" s="2" t="inlineStr"/>
       <c r="X437" s="2" t="inlineStr"/>
       <c r="Y437" s="2" t="n">
-        <v>10.5</v>
+        <v>40.03</v>
       </c>
       <c r="Z437" s="2" t="n">
-        <v>5.4</v>
+        <v>7.12</v>
       </c>
       <c r="AA437" s="2" t="n">
-        <v>2.18</v>
+        <v>11.46</v>
       </c>
       <c r="AB437" s="2" t="n">
-        <v>-1.78</v>
+        <v>-4.09</v>
       </c>
       <c r="AC437" s="2" t="n">
-        <v>-0.15</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>WBD US</t>
+          <t>WAT US</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C438" s="2" t="n">
-        <v>28.25</v>
+        <v>409.38</v>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
@@ -30579,26 +30585,20 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>3.6</v>
+        <v>16.6</v>
       </c>
       <c r="G438" s="2" t="n">
-        <v>112.43</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="H438" s="2" t="inlineStr"/>
-      <c r="I438" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr"/>
       <c r="K438" s="2" t="inlineStr"/>
       <c r="L438" s="2" t="inlineStr"/>
-      <c r="M438" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M438" s="2" t="inlineStr"/>
       <c r="N438" s="2" t="inlineStr"/>
       <c r="O438" s="2" t="inlineStr"/>
       <c r="P438" s="2" t="inlineStr"/>
@@ -30609,40 +30609,40 @@
       <c r="S438" s="2" t="inlineStr"/>
       <c r="T438" s="2" t="inlineStr"/>
       <c r="U438" s="2" t="inlineStr"/>
-      <c r="V438" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W438" s="2" t="inlineStr"/>
+      <c r="V438" s="2" t="inlineStr"/>
+      <c r="W438" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X438" s="2" t="inlineStr"/>
       <c r="Y438" s="2" t="n">
-        <v>27.49</v>
+        <v>10.5</v>
       </c>
       <c r="Z438" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AA438" s="2" t="n">
-        <v>11.67</v>
+        <v>2.18</v>
       </c>
       <c r="AB438" s="2" t="n">
-        <v>-2.99</v>
+        <v>-1.78</v>
       </c>
       <c r="AC438" s="2" t="n">
-        <v>1.73</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>WDAY US</t>
+          <t>WBD US</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C439" s="2" t="n">
-        <v>195.79</v>
+        <v>28.25</v>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
@@ -30650,95 +30650,95 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>36.2</v>
+        <v>3.6</v>
       </c>
       <c r="G439" s="2" t="n">
-        <v>92.42</v>
+        <v>112.43</v>
       </c>
       <c r="H439" s="2" t="inlineStr"/>
-      <c r="I439" s="2" t="inlineStr"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J439" s="2" t="inlineStr"/>
       <c r="K439" s="2" t="inlineStr"/>
       <c r="L439" s="2" t="inlineStr"/>
-      <c r="M439" s="2" t="inlineStr"/>
+      <c r="M439" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N439" s="2" t="inlineStr"/>
-      <c r="O439" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O439" s="2" t="inlineStr"/>
       <c r="P439" s="2" t="inlineStr"/>
       <c r="Q439" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R439" s="2" t="inlineStr"/>
       <c r="S439" s="2" t="inlineStr"/>
       <c r="T439" s="2" t="inlineStr"/>
-      <c r="U439" s="2" t="n">
+      <c r="U439" s="2" t="inlineStr"/>
+      <c r="V439" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V439" s="2" t="inlineStr"/>
       <c r="W439" s="2" t="inlineStr"/>
       <c r="X439" s="2" t="inlineStr"/>
       <c r="Y439" s="2" t="n">
-        <v>-21.46</v>
+        <v>27.49</v>
       </c>
       <c r="Z439" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA439" s="2" t="n">
-        <v>-9.279999999999999</v>
+        <v>11.67</v>
       </c>
       <c r="AB439" s="2" t="n">
-        <v>-3.9</v>
+        <v>-2.99</v>
       </c>
       <c r="AC439" s="2" t="n">
-        <v>11.55</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>WDAY US</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="C440" s="2" t="n">
-        <v>105.94</v>
+        <v>195.79</v>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>-5.3</v>
+        <v>36.2</v>
       </c>
       <c r="G440" s="2" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="H440" s="2" t="inlineStr">
-        <is>
-          <t>底背离</t>
-        </is>
-      </c>
+        <v>92.42</v>
+      </c>
+      <c r="H440" s="2" t="inlineStr"/>
       <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr"/>
       <c r="K440" s="2" t="inlineStr"/>
       <c r="L440" s="2" t="inlineStr"/>
-      <c r="M440" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M440" s="2" t="inlineStr"/>
       <c r="N440" s="2" t="inlineStr"/>
-      <c r="O440" s="2" t="inlineStr"/>
+      <c r="O440" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P440" s="2" t="inlineStr"/>
       <c r="Q440" s="2" t="n">
         <v>0</v>
@@ -30747,66 +30747,70 @@
       <c r="S440" s="2" t="inlineStr"/>
       <c r="T440" s="2" t="inlineStr"/>
       <c r="U440" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V440" s="2" t="inlineStr"/>
       <c r="W440" s="2" t="inlineStr"/>
       <c r="X440" s="2" t="inlineStr"/>
       <c r="Y440" s="2" t="n">
-        <v>-2.77</v>
+        <v>-21.46</v>
       </c>
       <c r="Z440" s="2" t="n">
-        <v>-12.11</v>
+        <v>1.1</v>
       </c>
       <c r="AA440" s="2" t="n">
-        <v>-1.33</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AB440" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.9</v>
       </c>
       <c r="AC440" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>WELL US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Welltower</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>236.17</v>
+        <v>105.94</v>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>3.35</v>
+        <v>0.29</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>-5.3</v>
       </c>
       <c r="G441" s="2" t="n">
-        <v>63.35</v>
-      </c>
-      <c r="H441" s="2" t="inlineStr"/>
+        <v>-1.62</v>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>底背离</t>
+        </is>
+      </c>
       <c r="I441" s="2" t="inlineStr"/>
       <c r="J441" s="2" t="inlineStr"/>
       <c r="K441" s="2" t="inlineStr"/>
       <c r="L441" s="2" t="inlineStr"/>
-      <c r="M441" s="2" t="inlineStr"/>
+      <c r="M441" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N441" s="2" t="inlineStr"/>
       <c r="O441" s="2" t="inlineStr"/>
-      <c r="P441" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="P441" s="2" t="inlineStr"/>
       <c r="Q441" s="2" t="n">
         <v>0</v>
       </c>
@@ -30814,56 +30818,54 @@
       <c r="S441" s="2" t="inlineStr"/>
       <c r="T441" s="2" t="inlineStr"/>
       <c r="U441" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V441" s="2" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V441" s="2" t="inlineStr"/>
       <c r="W441" s="2" t="inlineStr"/>
       <c r="X441" s="2" t="inlineStr"/>
       <c r="Y441" s="2" t="n">
-        <v>29.54</v>
+        <v>-2.77</v>
       </c>
       <c r="Z441" s="2" t="n">
-        <v>6.9</v>
+        <v>-12.11</v>
       </c>
       <c r="AA441" s="2" t="n">
-        <v>12.46</v>
+        <v>-1.33</v>
       </c>
       <c r="AB441" s="2" t="n">
-        <v>-1.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC441" s="2" t="n">
-        <v>-0.99</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>WFC US</t>
+          <t>WELL US</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Welltower</t>
         </is>
       </c>
       <c r="C442" s="2" t="n">
-        <v>89.97</v>
+        <v>236.17</v>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>-0.45</v>
+        <v>3.35</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G442" s="2" t="n">
-        <v>41.04</v>
+        <v>63.35</v>
       </c>
       <c r="H442" s="2" t="inlineStr"/>
       <c r="I442" s="2" t="inlineStr"/>
@@ -30873,64 +30875,66 @@
       <c r="M442" s="2" t="inlineStr"/>
       <c r="N442" s="2" t="inlineStr"/>
       <c r="O442" s="2" t="inlineStr"/>
-      <c r="P442" s="2" t="inlineStr"/>
+      <c r="P442" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="Q442" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R442" s="2" t="inlineStr"/>
       <c r="S442" s="2" t="inlineStr"/>
       <c r="T442" s="2" t="inlineStr"/>
-      <c r="U442" s="2" t="inlineStr"/>
+      <c r="U442" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="V442" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W442" s="2" t="inlineStr"/>
-      <c r="X442" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="X442" s="2" t="inlineStr"/>
       <c r="Y442" s="2" t="n">
-        <v>7.16</v>
+        <v>29.54</v>
       </c>
       <c r="Z442" s="2" t="n">
-        <v>-2.04</v>
+        <v>6.9</v>
       </c>
       <c r="AA442" s="2" t="n">
-        <v>-1.85</v>
+        <v>12.46</v>
       </c>
       <c r="AB442" s="2" t="n">
-        <v>3.62</v>
+        <v>-1.36</v>
       </c>
       <c r="AC442" s="2" t="n">
-        <v>3.94</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>WM US</t>
+          <t>WFC US</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C443" s="2" t="n">
-        <v>218.99</v>
+        <v>89.97</v>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>0.12</v>
+        <v>-0.45</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>-3.4</v>
+        <v>8.9</v>
       </c>
       <c r="G443" s="2" t="n">
-        <v>-4.75</v>
+        <v>41.04</v>
       </c>
       <c r="H443" s="2" t="inlineStr"/>
       <c r="I443" s="2" t="inlineStr"/>
@@ -30942,62 +30946,62 @@
       <c r="O443" s="2" t="inlineStr"/>
       <c r="P443" s="2" t="inlineStr"/>
       <c r="Q443" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R443" s="2" t="inlineStr"/>
       <c r="S443" s="2" t="inlineStr"/>
       <c r="T443" s="2" t="inlineStr"/>
-      <c r="U443" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="V443" s="2" t="inlineStr"/>
+      <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W443" s="2" t="inlineStr"/>
-      <c r="X443" s="2" t="inlineStr"/>
+      <c r="X443" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y443" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="Z443" s="2" t="n">
-        <v>-9.82</v>
+        <v>-2.04</v>
       </c>
       <c r="AA443" s="2" t="n">
-        <v>-6.35</v>
+        <v>-1.85</v>
       </c>
       <c r="AB443" s="2" t="n">
-        <v>-0.03</v>
+        <v>3.62</v>
       </c>
       <c r="AC443" s="2" t="n">
-        <v>-1.72</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>WMB US</t>
+          <t>WM US</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C444" s="2" t="n">
-        <v>74.15000000000001</v>
+        <v>218.99</v>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>2.21</v>
+        <v>0.12</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G444" s="2" t="n">
-        <v>25.75</v>
+        <v>-4.75</v>
       </c>
       <c r="H444" s="2" t="inlineStr"/>
       <c r="I444" s="2" t="inlineStr"/>
@@ -31014,57 +31018,57 @@
       <c r="R444" s="2" t="inlineStr"/>
       <c r="S444" s="2" t="inlineStr"/>
       <c r="T444" s="2" t="inlineStr"/>
-      <c r="U444" s="2" t="n">
-        <v>-1</v>
+      <c r="U444" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="V444" s="2" t="inlineStr"/>
       <c r="W444" s="2" t="inlineStr"/>
-      <c r="X444" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="X444" s="2" t="inlineStr"/>
       <c r="Y444" s="2" t="n">
-        <v>29.66</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z444" s="2" t="n">
-        <v>0.5</v>
+        <v>-9.82</v>
       </c>
       <c r="AA444" s="2" t="n">
-        <v>-11.06</v>
+        <v>-6.35</v>
       </c>
       <c r="AB444" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="AC444" s="2" t="n">
-        <v>4.87</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>WMT US</t>
+          <t>WMB US</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="C445" s="2" t="n">
-        <v>107.14</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>-10.6</v>
+        <v>1.9</v>
       </c>
       <c r="G445" s="2" t="n">
-        <v>8.68</v>
+        <v>25.75</v>
       </c>
       <c r="H445" s="2" t="inlineStr"/>
       <c r="I445" s="2" t="inlineStr"/>
@@ -31081,57 +31085,57 @@
       <c r="R445" s="2" t="inlineStr"/>
       <c r="S445" s="2" t="inlineStr"/>
       <c r="T445" s="2" t="inlineStr"/>
-      <c r="U445" s="2" t="inlineStr"/>
-      <c r="V445" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W445" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X445" s="2" t="inlineStr"/>
+      <c r="U445" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V445" s="2" t="inlineStr"/>
+      <c r="W445" s="2" t="inlineStr"/>
+      <c r="X445" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y445" s="2" t="n">
-        <v>4.82</v>
+        <v>29.66</v>
       </c>
       <c r="Z445" s="2" t="n">
-        <v>-15.02</v>
+        <v>0.5</v>
       </c>
       <c r="AA445" s="2" t="n">
-        <v>-10.26</v>
+        <v>-11.06</v>
       </c>
       <c r="AB445" s="2" t="n">
-        <v>3.26</v>
+        <v>0.26</v>
       </c>
       <c r="AC445" s="2" t="n">
-        <v>-2.55</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>WRB US</t>
+          <t>WMT US</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C446" s="2" t="n">
-        <v>69.14</v>
+        <v>107.14</v>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>1</v>
+        <v>-10.6</v>
       </c>
       <c r="G446" s="2" t="n">
-        <v>-5.79</v>
+        <v>8.68</v>
       </c>
       <c r="H446" s="2" t="inlineStr"/>
       <c r="I446" s="2" t="inlineStr"/>
@@ -31141,66 +31145,64 @@
       <c r="M446" s="2" t="inlineStr"/>
       <c r="N446" s="2" t="inlineStr"/>
       <c r="O446" s="2" t="inlineStr"/>
-      <c r="P446" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="P446" s="2" t="inlineStr"/>
       <c r="Q446" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R446" s="2" t="inlineStr"/>
       <c r="S446" s="2" t="inlineStr"/>
       <c r="T446" s="2" t="inlineStr"/>
-      <c r="U446" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U446" s="2" t="inlineStr"/>
       <c r="V446" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W446" s="2" t="inlineStr"/>
+      <c r="W446" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="X446" s="2" t="inlineStr"/>
       <c r="Y446" s="2" t="n">
-        <v>-12.14</v>
+        <v>4.82</v>
       </c>
       <c r="Z446" s="2" t="n">
-        <v>-9.460000000000001</v>
+        <v>-15.02</v>
       </c>
       <c r="AA446" s="2" t="n">
-        <v>-9.31</v>
+        <v>-10.26</v>
       </c>
       <c r="AB446" s="2" t="n">
-        <v>1.19</v>
+        <v>3.26</v>
       </c>
       <c r="AC446" s="2" t="n">
-        <v>-1.41</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>WSM US</t>
+          <t>WRB US</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C447" s="2" t="n">
-        <v>227.42</v>
+        <v>69.14</v>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>2.28</v>
+        <v>0.3</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="G447" s="2" t="n">
-        <v>75.94</v>
+        <v>-5.79</v>
       </c>
       <c r="H447" s="2" t="inlineStr"/>
       <c r="I447" s="2" t="inlineStr"/>
@@ -31210,50 +31212,52 @@
       <c r="M447" s="2" t="inlineStr"/>
       <c r="N447" s="2" t="inlineStr"/>
       <c r="O447" s="2" t="inlineStr"/>
-      <c r="P447" s="2" t="inlineStr"/>
+      <c r="P447" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="Q447" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R447" s="2" t="inlineStr"/>
       <c r="S447" s="2" t="inlineStr"/>
       <c r="T447" s="2" t="inlineStr"/>
-      <c r="U447" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="V447" s="2" t="inlineStr"/>
+      <c r="U447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V447" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W447" s="2" t="inlineStr"/>
       <c r="X447" s="2" t="inlineStr"/>
       <c r="Y447" s="2" t="n">
-        <v>25.52</v>
+        <v>-12.14</v>
       </c>
       <c r="Z447" s="2" t="n">
-        <v>3.47</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="AA447" s="2" t="n">
-        <v>15.1</v>
+        <v>-9.31</v>
       </c>
       <c r="AB447" s="2" t="n">
-        <v>-3.57</v>
+        <v>1.19</v>
       </c>
       <c r="AC447" s="2" t="n">
-        <v>-10.57</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>WST US</t>
+          <t>WSM US</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C448" s="2" t="n">
-        <v>339.97</v>
+        <v>227.42</v>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
@@ -31261,13 +31265,13 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>4.04</v>
+        <v>2.28</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>12.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G448" s="2" t="n">
-        <v>11.88</v>
+        <v>75.94</v>
       </c>
       <c r="H448" s="2" t="inlineStr"/>
       <c r="I448" s="2" t="inlineStr"/>
@@ -31284,55 +31288,57 @@
       <c r="R448" s="2" t="inlineStr"/>
       <c r="S448" s="2" t="inlineStr"/>
       <c r="T448" s="2" t="inlineStr"/>
-      <c r="U448" s="2" t="n">
-        <v>-1</v>
+      <c r="U448" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
       </c>
       <c r="V448" s="2" t="inlineStr"/>
       <c r="W448" s="2" t="inlineStr"/>
       <c r="X448" s="2" t="inlineStr"/>
       <c r="Y448" s="2" t="n">
-        <v>32.7</v>
+        <v>25.52</v>
       </c>
       <c r="Z448" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>3.47</v>
       </c>
       <c r="AA448" s="2" t="n">
-        <v>4.53</v>
+        <v>15.1</v>
       </c>
       <c r="AB448" s="2" t="n">
-        <v>0.37</v>
+        <v>-3.57</v>
       </c>
       <c r="AC448" s="2" t="n">
-        <v>-5.5</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>WTW US</t>
+          <t>WST US</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C449" s="2" t="n">
-        <v>334.74</v>
+        <v>339.97</v>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>0.73</v>
+        <v>4.04</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="G449" s="2" t="n">
-        <v>104.55</v>
+        <v>11.88</v>
       </c>
       <c r="H449" s="2" t="inlineStr"/>
       <c r="I449" s="2" t="inlineStr"/>
@@ -31341,9 +31347,7 @@
       <c r="L449" s="2" t="inlineStr"/>
       <c r="M449" s="2" t="inlineStr"/>
       <c r="N449" s="2" t="inlineStr"/>
-      <c r="O449" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="O449" s="2" t="inlineStr"/>
       <c r="P449" s="2" t="inlineStr"/>
       <c r="Q449" s="2" t="n">
         <v>1</v>
@@ -31351,53 +31355,55 @@
       <c r="R449" s="2" t="inlineStr"/>
       <c r="S449" s="2" t="inlineStr"/>
       <c r="T449" s="2" t="inlineStr"/>
-      <c r="U449" s="2" t="inlineStr"/>
+      <c r="U449" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="V449" s="2" t="inlineStr"/>
       <c r="W449" s="2" t="inlineStr"/>
       <c r="X449" s="2" t="inlineStr"/>
       <c r="Y449" s="2" t="n">
-        <v>8.35</v>
+        <v>32.7</v>
       </c>
       <c r="Z449" s="2" t="n">
-        <v>-0.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA449" s="2" t="n">
-        <v>0.23</v>
+        <v>4.53</v>
       </c>
       <c r="AB449" s="2" t="n">
-        <v>-2.49</v>
+        <v>0.37</v>
       </c>
       <c r="AC449" s="2" t="n">
-        <v>-1.22</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>WY US</t>
+          <t>WTW US</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C450" s="2" t="n">
-        <v>23.02</v>
+        <v>334.74</v>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>-0.65</v>
+        <v>0.73</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>-4.1</v>
+        <v>15</v>
       </c>
       <c r="G450" s="2" t="n">
-        <v>73.33</v>
+        <v>104.55</v>
       </c>
       <c r="H450" s="2" t="inlineStr"/>
       <c r="I450" s="2" t="inlineStr"/>
@@ -31406,67 +31412,63 @@
       <c r="L450" s="2" t="inlineStr"/>
       <c r="M450" s="2" t="inlineStr"/>
       <c r="N450" s="2" t="inlineStr"/>
-      <c r="O450" s="2" t="inlineStr"/>
-      <c r="P450" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="O450" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P450" s="2" t="inlineStr"/>
       <c r="Q450" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R450" s="2" t="inlineStr"/>
       <c r="S450" s="2" t="inlineStr"/>
       <c r="T450" s="2" t="inlineStr"/>
-      <c r="U450" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U450" s="2" t="inlineStr"/>
       <c r="V450" s="2" t="inlineStr"/>
       <c r="W450" s="2" t="inlineStr"/>
       <c r="X450" s="2" t="inlineStr"/>
       <c r="Y450" s="2" t="n">
-        <v>8.52</v>
+        <v>8.35</v>
       </c>
       <c r="Z450" s="2" t="n">
-        <v>-11.42</v>
+        <v>-0.17</v>
       </c>
       <c r="AA450" s="2" t="n">
-        <v>-6.76</v>
+        <v>0.23</v>
       </c>
       <c r="AB450" s="2" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="AC450" s="2" t="n">
         <v>-1.22</v>
-      </c>
-      <c r="AC450" s="2" t="n">
-        <v>-6.77</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>WYNN US</t>
+          <t>WY US</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C451" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>23.02</v>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>-2.13</v>
+        <v>-0.65</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>-10.3</v>
+        <v>-4.1</v>
       </c>
       <c r="G451" s="2" t="n">
-        <v>12.26</v>
+        <v>73.33</v>
       </c>
       <c r="H451" s="2" t="inlineStr"/>
       <c r="I451" s="2" t="inlineStr"/>
@@ -31480,60 +31482,62 @@
         <v>9</v>
       </c>
       <c r="Q451" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R451" s="2" t="inlineStr"/>
       <c r="S451" s="2" t="inlineStr"/>
       <c r="T451" s="2" t="inlineStr"/>
-      <c r="U451" s="2" t="n">
-        <v>1</v>
+      <c r="U451" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
       </c>
       <c r="V451" s="2" t="inlineStr"/>
       <c r="W451" s="2" t="inlineStr"/>
       <c r="X451" s="2" t="inlineStr"/>
       <c r="Y451" s="2" t="n">
-        <v>-36.57</v>
+        <v>8.52</v>
       </c>
       <c r="Z451" s="2" t="n">
-        <v>-24.35</v>
+        <v>-11.42</v>
       </c>
       <c r="AA451" s="2" t="n">
-        <v>-15.17</v>
+        <v>-6.76</v>
       </c>
       <c r="AB451" s="2" t="n">
-        <v>-2.42</v>
+        <v>-1.22</v>
       </c>
       <c r="AC451" s="2" t="n">
-        <v>-6.35</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>WYNN US</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C452" s="2" t="n">
-        <v>75.72</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>-4.2</v>
+        <v>-10.3</v>
       </c>
       <c r="G452" s="2" t="n">
-        <v>-4.88</v>
+        <v>12.26</v>
       </c>
       <c r="H452" s="2" t="inlineStr"/>
       <c r="I452" s="2" t="inlineStr"/>
@@ -31543,9 +31547,11 @@
       <c r="M452" s="2" t="inlineStr"/>
       <c r="N452" s="2" t="inlineStr"/>
       <c r="O452" s="2" t="inlineStr"/>
-      <c r="P452" s="2" t="inlineStr"/>
+      <c r="P452" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q452" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R452" s="2" t="inlineStr"/>
       <c r="S452" s="2" t="inlineStr"/>
@@ -31557,190 +31563,188 @@
       <c r="W452" s="2" t="inlineStr"/>
       <c r="X452" s="2" t="inlineStr"/>
       <c r="Y452" s="2" t="n">
-        <v>-5.25</v>
+        <v>-36.57</v>
       </c>
       <c r="Z452" s="2" t="n">
-        <v>-11.16</v>
+        <v>-24.35</v>
       </c>
       <c r="AA452" s="2" t="n">
-        <v>-0.28</v>
+        <v>-15.17</v>
       </c>
       <c r="AB452" s="2" t="n">
-        <v>-0.78</v>
+        <v>-2.42</v>
       </c>
       <c r="AC452" s="2" t="n">
-        <v>-1.7</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>XOM US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C453" s="2" t="n">
-        <v>159.47</v>
+        <v>75.72</v>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>3.08</v>
+        <v>0.57</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>5.8</v>
+        <v>-4.2</v>
       </c>
       <c r="G453" s="2" t="n">
-        <v>110.23</v>
+        <v>-4.88</v>
       </c>
       <c r="H453" s="2" t="inlineStr"/>
-      <c r="I453" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr"/>
       <c r="K453" s="2" t="inlineStr"/>
       <c r="L453" s="2" t="inlineStr"/>
-      <c r="M453" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M453" s="2" t="inlineStr"/>
       <c r="N453" s="2" t="inlineStr"/>
       <c r="O453" s="2" t="inlineStr"/>
       <c r="P453" s="2" t="inlineStr"/>
       <c r="Q453" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R453" s="2" t="inlineStr"/>
       <c r="S453" s="2" t="inlineStr"/>
       <c r="T453" s="2" t="inlineStr"/>
-      <c r="U453" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="U453" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V453" s="2" t="inlineStr"/>
-      <c r="W453" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="W453" s="2" t="inlineStr"/>
       <c r="X453" s="2" t="inlineStr"/>
       <c r="Y453" s="2" t="n">
-        <v>42.57</v>
+        <v>-5.25</v>
       </c>
       <c r="Z453" s="2" t="n">
-        <v>6.89</v>
+        <v>-11.16</v>
       </c>
       <c r="AA453" s="2" t="n">
-        <v>-4.93</v>
+        <v>-0.28</v>
       </c>
       <c r="AB453" s="2" t="n">
-        <v>1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="AC453" s="2" t="n">
-        <v>3.61</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>XYL US</t>
+          <t>XOM US</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C454" s="2" t="n">
-        <v>105.69</v>
+        <v>159.47</v>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>-2.74</v>
+        <v>3.08</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>-10.8</v>
+        <v>5.8</v>
       </c>
       <c r="G454" s="2" t="n">
-        <v>-11.99</v>
+        <v>110.23</v>
       </c>
       <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="inlineStr"/>
       <c r="K454" s="2" t="inlineStr"/>
       <c r="L454" s="2" t="inlineStr"/>
-      <c r="M454" s="2" t="inlineStr"/>
+      <c r="M454" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="N454" s="2" t="inlineStr"/>
       <c r="O454" s="2" t="inlineStr"/>
-      <c r="P454" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="P454" s="2" t="inlineStr"/>
       <c r="Q454" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R454" s="2" t="inlineStr"/>
       <c r="S454" s="2" t="inlineStr"/>
       <c r="T454" s="2" t="inlineStr"/>
-      <c r="U454" s="2" t="n">
-        <v>-1</v>
+      <c r="U454" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="V454" s="2" t="inlineStr"/>
-      <c r="W454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="X454" s="2" t="inlineStr"/>
       <c r="Y454" s="2" t="n">
-        <v>-38.35</v>
+        <v>42.57</v>
       </c>
       <c r="Z454" s="2" t="n">
-        <v>-24.81</v>
+        <v>6.89</v>
       </c>
       <c r="AA454" s="2" t="n">
-        <v>-22.17</v>
+        <v>-4.93</v>
       </c>
       <c r="AB454" s="2" t="n">
-        <v>-3.42</v>
+        <v>1.32</v>
       </c>
       <c r="AC454" s="2" t="n">
-        <v>-7.15</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>XYZ US</t>
+          <t>XYL US</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C455" s="2" t="n">
-        <v>82.76000000000001</v>
+        <v>105.69</v>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>2.98</v>
+        <v>-2.74</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>17.9</v>
+        <v>-10.8</v>
       </c>
       <c r="G455" s="2" t="n">
-        <v>70.94</v>
+        <v>-11.99</v>
       </c>
       <c r="H455" s="2" t="inlineStr"/>
       <c r="I455" s="2" t="inlineStr"/>
@@ -31750,64 +31754,64 @@
       <c r="M455" s="2" t="inlineStr"/>
       <c r="N455" s="2" t="inlineStr"/>
       <c r="O455" s="2" t="inlineStr"/>
-      <c r="P455" s="2" t="inlineStr"/>
+      <c r="P455" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q455" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R455" s="2" t="inlineStr"/>
       <c r="S455" s="2" t="inlineStr"/>
       <c r="T455" s="2" t="inlineStr"/>
       <c r="U455" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V455" s="2" t="inlineStr"/>
-      <c r="W455" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="W455" s="2" t="inlineStr"/>
       <c r="X455" s="2" t="inlineStr"/>
       <c r="Y455" s="2" t="n">
-        <v>36.21</v>
+        <v>-38.35</v>
       </c>
       <c r="Z455" s="2" t="n">
-        <v>8.18</v>
+        <v>-24.81</v>
       </c>
       <c r="AA455" s="2" t="n">
-        <v>8.24</v>
+        <v>-22.17</v>
       </c>
       <c r="AB455" s="2" t="n">
-        <v>-0.85</v>
+        <v>-3.42</v>
       </c>
       <c r="AC455" s="2" t="n">
-        <v>6.51</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>YUM US</t>
+          <t>XYZ US</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C456" s="2" t="n">
-        <v>150.71</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>-0.2</v>
+        <v>2.98</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>-2.9</v>
+        <v>17.9</v>
       </c>
       <c r="G456" s="2" t="n">
-        <v>12.54</v>
+        <v>70.94</v>
       </c>
       <c r="H456" s="2" t="inlineStr"/>
       <c r="I456" s="2" t="inlineStr"/>
@@ -31817,66 +31821,64 @@
       <c r="M456" s="2" t="inlineStr"/>
       <c r="N456" s="2" t="inlineStr"/>
       <c r="O456" s="2" t="inlineStr"/>
-      <c r="P456" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="P456" s="2" t="inlineStr"/>
       <c r="Q456" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R456" s="2" t="inlineStr"/>
       <c r="S456" s="2" t="inlineStr"/>
       <c r="T456" s="2" t="inlineStr"/>
-      <c r="U456" s="2" t="inlineStr"/>
-      <c r="V456" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="W456" s="2" t="inlineStr"/>
+      <c r="U456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V456" s="2" t="inlineStr"/>
+      <c r="W456" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="X456" s="2" t="inlineStr"/>
       <c r="Y456" s="2" t="n">
-        <v>3.97</v>
+        <v>36.21</v>
       </c>
       <c r="Z456" s="2" t="n">
-        <v>-9.77</v>
+        <v>8.18</v>
       </c>
       <c r="AA456" s="2" t="n">
-        <v>0.67</v>
+        <v>8.24</v>
       </c>
       <c r="AB456" s="2" t="n">
-        <v>-1.77</v>
+        <v>-0.85</v>
       </c>
       <c r="AC456" s="2" t="n">
-        <v>1.31</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>ZBRA US</t>
+          <t>YUM US</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C457" s="2" t="n">
-        <v>362.74</v>
+        <v>150.71</v>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>6.31</v>
+        <v>-0.2</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>39.9</v>
+        <v>-2.9</v>
       </c>
       <c r="G457" s="2" t="n">
-        <v>102.22</v>
+        <v>12.54</v>
       </c>
       <c r="H457" s="2" t="inlineStr"/>
       <c r="I457" s="2" t="inlineStr"/>
@@ -31885,65 +31887,67 @@
       <c r="L457" s="2" t="inlineStr"/>
       <c r="M457" s="2" t="inlineStr"/>
       <c r="N457" s="2" t="inlineStr"/>
-      <c r="O457" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P457" s="2" t="inlineStr"/>
+      <c r="O457" s="2" t="inlineStr"/>
+      <c r="P457" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="Q457" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R457" s="2" t="inlineStr"/>
       <c r="S457" s="2" t="inlineStr"/>
       <c r="T457" s="2" t="inlineStr"/>
-      <c r="U457" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V457" s="2" t="inlineStr"/>
+      <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W457" s="2" t="inlineStr"/>
       <c r="X457" s="2" t="inlineStr"/>
       <c r="Y457" s="2" t="n">
-        <v>55.46</v>
+        <v>3.97</v>
       </c>
       <c r="Z457" s="2" t="n">
-        <v>25.4</v>
+        <v>-9.77</v>
       </c>
       <c r="AA457" s="2" t="n">
-        <v>13.57</v>
+        <v>0.67</v>
       </c>
       <c r="AB457" s="2" t="n">
-        <v>2.22</v>
+        <v>-1.77</v>
       </c>
       <c r="AC457" s="2" t="n">
-        <v>-3.54</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>ZTS US</t>
+          <t>ZBRA US</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C458" s="2" t="n">
-        <v>75.81</v>
+        <v>362.74</v>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>-6.24</v>
+        <v>6.31</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>-20.6</v>
+        <v>39.9</v>
       </c>
       <c r="G458" s="2" t="n">
-        <v>76.98</v>
+        <v>102.22</v>
       </c>
       <c r="H458" s="2" t="inlineStr"/>
       <c r="I458" s="2" t="inlineStr"/>
@@ -31952,7 +31956,9 @@
       <c r="L458" s="2" t="inlineStr"/>
       <c r="M458" s="2" t="inlineStr"/>
       <c r="N458" s="2" t="inlineStr"/>
-      <c r="O458" s="2" t="inlineStr"/>
+      <c r="O458" s="2" t="n">
+        <v>-9</v>
+      </c>
       <c r="P458" s="2" t="inlineStr"/>
       <c r="Q458" s="2" t="n">
         <v>0</v>
@@ -31960,57 +31966,55 @@
       <c r="R458" s="2" t="inlineStr"/>
       <c r="S458" s="2" t="inlineStr"/>
       <c r="T458" s="2" t="inlineStr"/>
-      <c r="U458" s="2" t="inlineStr"/>
-      <c r="V458" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V458" s="2" t="inlineStr"/>
       <c r="W458" s="2" t="inlineStr"/>
       <c r="X458" s="2" t="inlineStr"/>
       <c r="Y458" s="2" t="n">
-        <v>-53.02</v>
+        <v>55.46</v>
       </c>
       <c r="Z458" s="2" t="n">
-        <v>-37.6</v>
+        <v>25.4</v>
       </c>
       <c r="AA458" s="2" t="n">
-        <v>-39.49</v>
+        <v>13.57</v>
       </c>
       <c r="AB458" s="2" t="n">
-        <v>-0.26</v>
+        <v>2.22</v>
       </c>
       <c r="AC458" s="2" t="n">
-        <v>6.69</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>ABBV US</t>
+          <t>ZTS US</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C459" s="2" t="n">
-        <v>256.46</v>
+        <v>75.81</v>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>2.45</v>
+        <v>-6.24</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>12.6</v>
+        <v>-20.6</v>
       </c>
       <c r="G459" s="2" t="n">
-        <v>81.87</v>
+        <v>76.98</v>
       </c>
       <c r="H459" s="2" t="inlineStr"/>
       <c r="I459" s="2" t="inlineStr"/>
@@ -32028,38 +32032,42 @@
       <c r="S459" s="2" t="inlineStr"/>
       <c r="T459" s="2" t="inlineStr"/>
       <c r="U459" s="2" t="inlineStr"/>
-      <c r="V459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W459" s="2" t="inlineStr"/>
       <c r="X459" s="2" t="inlineStr"/>
       <c r="Y459" s="2" t="n">
-        <v>19.01</v>
+        <v>-53.02</v>
       </c>
       <c r="Z459" s="2" t="n">
-        <v>4.37</v>
+        <v>-37.6</v>
       </c>
       <c r="AA459" s="2" t="n">
-        <v>1.14</v>
+        <v>-39.49</v>
       </c>
       <c r="AB459" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.26</v>
       </c>
       <c r="AC459" s="2" t="n">
-        <v>4.17</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>ABNB US</t>
+          <t>ABBV US</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C460" s="2" t="n">
-        <v>181.94</v>
+        <v>256.46</v>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
@@ -32067,13 +32075,13 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>4.97</v>
+        <v>2.45</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>27.4</v>
+        <v>12.6</v>
       </c>
       <c r="G460" s="2" t="n">
-        <v>103.21</v>
+        <v>81.87</v>
       </c>
       <c r="H460" s="2" t="inlineStr"/>
       <c r="I460" s="2" t="inlineStr"/>
@@ -32085,7 +32093,7 @@
       <c r="O460" s="2" t="inlineStr"/>
       <c r="P460" s="2" t="inlineStr"/>
       <c r="Q460" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R460" s="2" t="inlineStr"/>
       <c r="S460" s="2" t="inlineStr"/>
@@ -32095,48 +32103,48 @@
       <c r="W460" s="2" t="inlineStr"/>
       <c r="X460" s="2" t="inlineStr"/>
       <c r="Y460" s="2" t="n">
-        <v>58.69</v>
+        <v>19.01</v>
       </c>
       <c r="Z460" s="2" t="n">
-        <v>22.4</v>
+        <v>4.37</v>
       </c>
       <c r="AA460" s="2" t="n">
-        <v>35.97</v>
+        <v>1.14</v>
       </c>
       <c r="AB460" s="2" t="n">
-        <v>-5.69</v>
+        <v>0.18</v>
       </c>
       <c r="AC460" s="2" t="n">
-        <v>0.96</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>ACGL US</t>
+          <t>ABNB US</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Arch Capital Group</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C461" s="2" t="n">
-        <v>98.09999999999999</v>
+        <v>181.94</v>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>0.75</v>
+        <v>4.97</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>1.3</v>
+        <v>27.4</v>
       </c>
       <c r="G461" s="2" t="n">
-        <v>3.36</v>
+        <v>103.21</v>
       </c>
       <c r="H461" s="2" t="inlineStr"/>
       <c r="I461" s="2" t="inlineStr"/>
@@ -32148,7 +32156,7 @@
       <c r="O461" s="2" t="inlineStr"/>
       <c r="P461" s="2" t="inlineStr"/>
       <c r="Q461" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R461" s="2" t="inlineStr"/>
       <c r="S461" s="2" t="inlineStr"/>
@@ -32158,48 +32166,48 @@
       <c r="W461" s="2" t="inlineStr"/>
       <c r="X461" s="2" t="inlineStr"/>
       <c r="Y461" s="2" t="n">
-        <v>9.02</v>
+        <v>58.69</v>
       </c>
       <c r="Z461" s="2" t="n">
-        <v>-5.57</v>
+        <v>22.4</v>
       </c>
       <c r="AA461" s="2" t="n">
-        <v>-5.53</v>
+        <v>35.97</v>
       </c>
       <c r="AB461" s="2" t="n">
-        <v>-0.6</v>
+        <v>-5.69</v>
       </c>
       <c r="AC461" s="2" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>ADM US</t>
+          <t>ACGL US</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Archer Daniels Midland</t>
+          <t>Arch Capital Group</t>
         </is>
       </c>
       <c r="C462" s="2" t="n">
-        <v>84.61</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>3.3</v>
+        <v>0.75</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>12.7</v>
+        <v>1.3</v>
       </c>
       <c r="G462" s="2" t="n">
-        <v>40.7</v>
+        <v>3.36</v>
       </c>
       <c r="H462" s="2" t="inlineStr"/>
       <c r="I462" s="2" t="inlineStr"/>
@@ -32221,48 +32229,48 @@
       <c r="W462" s="2" t="inlineStr"/>
       <c r="X462" s="2" t="inlineStr"/>
       <c r="Y462" s="2" t="n">
-        <v>50.43</v>
+        <v>9.02</v>
       </c>
       <c r="Z462" s="2" t="n">
-        <v>12.73</v>
+        <v>-5.57</v>
       </c>
       <c r="AA462" s="2" t="n">
-        <v>18.76</v>
+        <v>-5.53</v>
       </c>
       <c r="AB462" s="2" t="n">
-        <v>3.64</v>
+        <v>-0.6</v>
       </c>
       <c r="AC462" s="2" t="n">
-        <v>10.69</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>ALNY US</t>
+          <t>ADM US</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals</t>
+          <t>Archer Daniels Midland</t>
         </is>
       </c>
       <c r="C463" s="2" t="n">
-        <v>266.11</v>
+        <v>84.61</v>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>-5.77</v>
+        <v>3.3</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>-9.4</v>
+        <v>12.7</v>
       </c>
       <c r="G463" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>40.7</v>
       </c>
       <c r="H463" s="2" t="inlineStr"/>
       <c r="I463" s="2" t="inlineStr"/>
@@ -32284,48 +32292,48 @@
       <c r="W463" s="2" t="inlineStr"/>
       <c r="X463" s="2" t="inlineStr"/>
       <c r="Y463" s="2" t="n">
-        <v>-78.43000000000001</v>
+        <v>50.43</v>
       </c>
       <c r="Z463" s="2" t="n">
-        <v>-31.27</v>
+        <v>12.73</v>
       </c>
       <c r="AA463" s="2" t="n">
-        <v>-33.44</v>
+        <v>18.76</v>
       </c>
       <c r="AB463" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="AC463" s="2" t="n">
-        <v>15.65</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>AMCR US</t>
+          <t>ALNY US</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Alnylam Pharmaceuticals</t>
         </is>
       </c>
       <c r="C464" s="2" t="n">
-        <v>45.15</v>
+        <v>266.11</v>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>1.52</v>
+        <v>-5.77</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>7.9</v>
+        <v>-9.4</v>
       </c>
       <c r="G464" s="2" t="n">
-        <v>96.45</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H464" s="2" t="inlineStr"/>
       <c r="I464" s="2" t="inlineStr"/>
@@ -32347,48 +32355,48 @@
       <c r="W464" s="2" t="inlineStr"/>
       <c r="X464" s="2" t="inlineStr"/>
       <c r="Y464" s="2" t="n">
-        <v>17.01</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="Z464" s="2" t="n">
-        <v>0.75</v>
+        <v>-31.27</v>
       </c>
       <c r="AA464" s="2" t="n">
-        <v>2.01</v>
+        <v>-33.44</v>
       </c>
       <c r="AB464" s="2" t="n">
-        <v>-1.95</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AC464" s="2" t="n">
-        <v>-3.43</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>AON US</t>
+          <t>AMCR US</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C465" s="2" t="n">
-        <v>323.09</v>
+        <v>45.15</v>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>0.21</v>
+        <v>1.52</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>-2.9</v>
+        <v>7.9</v>
       </c>
       <c r="G465" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>96.45</v>
       </c>
       <c r="H465" s="2" t="inlineStr"/>
       <c r="I465" s="2" t="inlineStr"/>
@@ -32410,48 +32418,48 @@
       <c r="W465" s="2" t="inlineStr"/>
       <c r="X465" s="2" t="inlineStr"/>
       <c r="Y465" s="2" t="n">
-        <v>-8.5</v>
+        <v>17.01</v>
       </c>
       <c r="Z465" s="2" t="n">
-        <v>-13.1</v>
+        <v>0.75</v>
       </c>
       <c r="AA465" s="2" t="n">
-        <v>-12.92</v>
+        <v>2.01</v>
       </c>
       <c r="AB465" s="2" t="n">
-        <v>-8.210000000000001</v>
+        <v>-1.95</v>
       </c>
       <c r="AC465" s="2" t="n">
-        <v>-7.13</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>APP US</t>
+          <t>AON US</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C466" s="2" t="n">
-        <v>320.56</v>
+        <v>323.09</v>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>-7.62</v>
+        <v>0.21</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>-27</v>
+        <v>-2.9</v>
       </c>
       <c r="G466" s="2" t="n">
-        <v>-8.69</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H466" s="2" t="inlineStr"/>
       <c r="I466" s="2" t="inlineStr"/>
@@ -32473,48 +32481,48 @@
       <c r="W466" s="2" t="inlineStr"/>
       <c r="X466" s="2" t="inlineStr"/>
       <c r="Y466" s="2" t="n">
-        <v>-66.33</v>
+        <v>-8.5</v>
       </c>
       <c r="Z466" s="2" t="n">
-        <v>-43.25</v>
+        <v>-13.1</v>
       </c>
       <c r="AA466" s="2" t="n">
-        <v>-49</v>
+        <v>-12.92</v>
       </c>
       <c r="AB466" s="2" t="n">
-        <v>0.96</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AC466" s="2" t="n">
-        <v>-2.41</v>
+        <v>-7.13</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>ARE US</t>
+          <t>APP US</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate Equities</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="C467" s="2" t="n">
-        <v>52.65</v>
+        <v>320.56</v>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>-0.76</v>
+        <v>-7.62</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>7.3</v>
+        <v>-27</v>
       </c>
       <c r="G467" s="2" t="n">
-        <v>5.27</v>
+        <v>-8.69</v>
       </c>
       <c r="H467" s="2" t="inlineStr"/>
       <c r="I467" s="2" t="inlineStr"/>
@@ -32536,48 +32544,48 @@
       <c r="W467" s="2" t="inlineStr"/>
       <c r="X467" s="2" t="inlineStr"/>
       <c r="Y467" s="2" t="n">
-        <v>4.33</v>
+        <v>-66.33</v>
       </c>
       <c r="Z467" s="2" t="n">
-        <v>-10.72</v>
+        <v>-43.25</v>
       </c>
       <c r="AA467" s="2" t="n">
-        <v>-5.9</v>
+        <v>-49</v>
       </c>
       <c r="AB467" s="2" t="n">
-        <v>2.91</v>
+        <v>0.96</v>
       </c>
       <c r="AC467" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>AXON US</t>
+          <t>ARE US</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Alexandria Real Estate Equities</t>
         </is>
       </c>
       <c r="C468" s="2" t="n">
-        <v>515.67</v>
+        <v>52.65</v>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.76</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="G468" s="2" t="n">
-        <v>87.58</v>
+        <v>5.27</v>
       </c>
       <c r="H468" s="2" t="inlineStr"/>
       <c r="I468" s="2" t="inlineStr"/>
@@ -32599,48 +32607,48 @@
       <c r="W468" s="2" t="inlineStr"/>
       <c r="X468" s="2" t="inlineStr"/>
       <c r="Y468" s="2" t="n">
-        <v>-7.75</v>
+        <v>4.33</v>
       </c>
       <c r="Z468" s="2" t="n">
-        <v>-14.2</v>
+        <v>-10.72</v>
       </c>
       <c r="AA468" s="2" t="n">
-        <v>-11.41</v>
+        <v>-5.9</v>
       </c>
       <c r="AB468" s="2" t="n">
-        <v>-13.07</v>
+        <v>2.91</v>
       </c>
       <c r="AC468" s="2" t="n">
-        <v>-4.75</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>BXP US</t>
+          <t>AXON US</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C469" s="2" t="n">
-        <v>67.69</v>
+        <v>515.67</v>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.25</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>10.4</v>
+        <v>6.8</v>
       </c>
       <c r="G469" s="2" t="n">
-        <v>8.73</v>
+        <v>87.58</v>
       </c>
       <c r="H469" s="2" t="inlineStr"/>
       <c r="I469" s="2" t="inlineStr"/>
@@ -32652,7 +32660,7 @@
       <c r="O469" s="2" t="inlineStr"/>
       <c r="P469" s="2" t="inlineStr"/>
       <c r="Q469" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R469" s="2" t="inlineStr"/>
       <c r="S469" s="2" t="inlineStr"/>
@@ -32662,48 +32670,48 @@
       <c r="W469" s="2" t="inlineStr"/>
       <c r="X469" s="2" t="inlineStr"/>
       <c r="Y469" s="2" t="n">
-        <v>-1.91</v>
+        <v>-7.75</v>
       </c>
       <c r="Z469" s="2" t="n">
-        <v>-3.99</v>
+        <v>-14.2</v>
       </c>
       <c r="AA469" s="2" t="n">
-        <v>0.93</v>
+        <v>-11.41</v>
       </c>
       <c r="AB469" s="2" t="n">
-        <v>-1.97</v>
+        <v>-13.07</v>
       </c>
       <c r="AC469" s="2" t="n">
-        <v>-1.3</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>CCEP US</t>
+          <t>BXP US</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C470" s="2" t="n">
-        <v>105.76</v>
+        <v>67.69</v>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>2.68</v>
+        <v>0.8</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>6.1</v>
+        <v>10.4</v>
       </c>
       <c r="G470" s="2" t="n">
-        <v>69.25</v>
+        <v>8.73</v>
       </c>
       <c r="H470" s="2" t="inlineStr"/>
       <c r="I470" s="2" t="inlineStr"/>
@@ -32715,7 +32723,7 @@
       <c r="O470" s="2" t="inlineStr"/>
       <c r="P470" s="2" t="inlineStr"/>
       <c r="Q470" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R470" s="2" t="inlineStr"/>
       <c r="S470" s="2" t="inlineStr"/>
@@ -32725,34 +32733,34 @@
       <c r="W470" s="2" t="inlineStr"/>
       <c r="X470" s="2" t="inlineStr"/>
       <c r="Y470" s="2" t="n">
-        <v>23.94</v>
+        <v>-1.91</v>
       </c>
       <c r="Z470" s="2" t="n">
-        <v>1.59</v>
+        <v>-3.99</v>
       </c>
       <c r="AA470" s="2" t="n">
-        <v>7.13</v>
+        <v>0.93</v>
       </c>
       <c r="AB470" s="2" t="n">
-        <v>-3.42</v>
+        <v>-1.97</v>
       </c>
       <c r="AC470" s="2" t="n">
-        <v>-2.07</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>CHD US</t>
+          <t>CCEP US</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Coca-Cola Europacific Partners</t>
         </is>
       </c>
       <c r="C471" s="2" t="n">
-        <v>98.55</v>
+        <v>105.76</v>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
@@ -32760,13 +32768,13 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>1.66</v>
+        <v>2.68</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="G471" s="2" t="n">
-        <v>81.45</v>
+        <v>69.25</v>
       </c>
       <c r="H471" s="2" t="inlineStr"/>
       <c r="I471" s="2" t="inlineStr"/>
@@ -32778,7 +32786,7 @@
       <c r="O471" s="2" t="inlineStr"/>
       <c r="P471" s="2" t="inlineStr"/>
       <c r="Q471" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R471" s="2" t="inlineStr"/>
       <c r="S471" s="2" t="inlineStr"/>
@@ -32788,48 +32796,48 @@
       <c r="W471" s="2" t="inlineStr"/>
       <c r="X471" s="2" t="inlineStr"/>
       <c r="Y471" s="2" t="n">
-        <v>21.45</v>
+        <v>23.94</v>
       </c>
       <c r="Z471" s="2" t="n">
-        <v>-3.1</v>
+        <v>1.59</v>
       </c>
       <c r="AA471" s="2" t="n">
-        <v>2.26</v>
+        <v>7.13</v>
       </c>
       <c r="AB471" s="2" t="n">
-        <v>-2.55</v>
+        <v>-3.42</v>
       </c>
       <c r="AC471" s="2" t="n">
-        <v>-3.04</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CIEN US</t>
+          <t>CHD US</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C472" s="2" t="n">
-        <v>321</v>
+        <v>98.55</v>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>4.84</v>
+        <v>1.66</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>-25</v>
+        <v>1.2</v>
       </c>
       <c r="G472" s="2" t="n">
-        <v>59.47</v>
+        <v>81.45</v>
       </c>
       <c r="H472" s="2" t="inlineStr"/>
       <c r="I472" s="2" t="inlineStr"/>
@@ -32851,34 +32859,34 @@
       <c r="W472" s="2" t="inlineStr"/>
       <c r="X472" s="2" t="inlineStr"/>
       <c r="Y472" s="2" t="n">
-        <v>51.59</v>
+        <v>21.45</v>
       </c>
       <c r="Z472" s="2" t="n">
-        <v>-10.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AA472" s="2" t="n">
-        <v>-18.04</v>
+        <v>2.26</v>
       </c>
       <c r="AB472" s="2" t="n">
-        <v>-17.39</v>
+        <v>-2.55</v>
       </c>
       <c r="AC472" s="2" t="n">
-        <v>-32.22</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>CL US</t>
+          <t>CIEN US</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C473" s="2" t="n">
-        <v>88.77</v>
+        <v>321</v>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
@@ -32886,13 +32894,13 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>1.39</v>
+        <v>4.84</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>-0.8</v>
+        <v>-25</v>
       </c>
       <c r="G473" s="2" t="n">
-        <v>-5.2</v>
+        <v>59.47</v>
       </c>
       <c r="H473" s="2" t="inlineStr"/>
       <c r="I473" s="2" t="inlineStr"/>
@@ -32904,7 +32912,7 @@
       <c r="O473" s="2" t="inlineStr"/>
       <c r="P473" s="2" t="inlineStr"/>
       <c r="Q473" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R473" s="2" t="inlineStr"/>
       <c r="S473" s="2" t="inlineStr"/>
@@ -32914,48 +32922,48 @@
       <c r="W473" s="2" t="inlineStr"/>
       <c r="X473" s="2" t="inlineStr"/>
       <c r="Y473" s="2" t="n">
-        <v>18.54</v>
+        <v>51.59</v>
       </c>
       <c r="Z473" s="2" t="n">
-        <v>-4.65</v>
+        <v>-10.9</v>
       </c>
       <c r="AA473" s="2" t="n">
-        <v>0.62</v>
+        <v>-18.04</v>
       </c>
       <c r="AB473" s="2" t="n">
-        <v>-2.05</v>
+        <v>-17.39</v>
       </c>
       <c r="AC473" s="2" t="n">
-        <v>-3.66</v>
+        <v>-32.22</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CMCSA US</t>
+          <t>CL US</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C474" s="2" t="n">
-        <v>26.49</v>
+        <v>88.77</v>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>-0.66</v>
+        <v>1.39</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="G474" s="2" t="n">
-        <v>117.36</v>
+        <v>-5.2</v>
       </c>
       <c r="H474" s="2" t="inlineStr"/>
       <c r="I474" s="2" t="inlineStr"/>
@@ -32967,7 +32975,7 @@
       <c r="O474" s="2" t="inlineStr"/>
       <c r="P474" s="2" t="inlineStr"/>
       <c r="Q474" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R474" s="2" t="inlineStr"/>
       <c r="S474" s="2" t="inlineStr"/>
@@ -32977,48 +32985,48 @@
       <c r="W474" s="2" t="inlineStr"/>
       <c r="X474" s="2" t="inlineStr"/>
       <c r="Y474" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>18.54</v>
       </c>
       <c r="Z474" s="2" t="n">
-        <v>-9.41</v>
+        <v>-4.65</v>
       </c>
       <c r="AA474" s="2" t="n">
-        <v>1.33</v>
+        <v>0.62</v>
       </c>
       <c r="AB474" s="2" t="n">
-        <v>-1.44</v>
+        <v>-2.05</v>
       </c>
       <c r="AC474" s="2" t="n">
-        <v>6.41</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>CMCSA US</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C475" s="2" t="n">
-        <v>39.67</v>
+        <v>26.49</v>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.66</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>-5.6</v>
+        <v>0.1</v>
       </c>
       <c r="G475" s="2" t="n">
-        <v>-12.14</v>
+        <v>117.36</v>
       </c>
       <c r="H475" s="2" t="inlineStr"/>
       <c r="I475" s="2" t="inlineStr"/>
@@ -33030,7 +33038,7 @@
       <c r="O475" s="2" t="inlineStr"/>
       <c r="P475" s="2" t="inlineStr"/>
       <c r="Q475" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R475" s="2" t="inlineStr"/>
       <c r="S475" s="2" t="inlineStr"/>
@@ -33040,34 +33048,34 @@
       <c r="W475" s="2" t="inlineStr"/>
       <c r="X475" s="2" t="inlineStr"/>
       <c r="Y475" s="2" t="n">
-        <v>2.46</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Z475" s="2" t="n">
-        <v>-10.48</v>
+        <v>-9.41</v>
       </c>
       <c r="AA475" s="2" t="n">
-        <v>0.45</v>
+        <v>1.33</v>
       </c>
       <c r="AB475" s="2" t="n">
-        <v>1.06</v>
+        <v>-1.44</v>
       </c>
       <c r="AC475" s="2" t="n">
-        <v>-0.51</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>COST US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C476" s="2" t="n">
-        <v>915.74</v>
+        <v>39.67</v>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
@@ -33075,13 +33083,13 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>-6.2</v>
+        <v>-5.6</v>
       </c>
       <c r="G476" s="2" t="n">
-        <v>67.48999999999999</v>
+        <v>-12.14</v>
       </c>
       <c r="H476" s="2" t="inlineStr"/>
       <c r="I476" s="2" t="inlineStr"/>
@@ -33093,7 +33101,7 @@
       <c r="O476" s="2" t="inlineStr"/>
       <c r="P476" s="2" t="inlineStr"/>
       <c r="Q476" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R476" s="2" t="inlineStr"/>
       <c r="S476" s="2" t="inlineStr"/>
@@ -33103,48 +33111,48 @@
       <c r="W476" s="2" t="inlineStr"/>
       <c r="X476" s="2" t="inlineStr"/>
       <c r="Y476" s="2" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="Z476" s="2" t="n">
-        <v>-12.36</v>
+        <v>-10.48</v>
       </c>
       <c r="AA476" s="2" t="n">
-        <v>-7.51</v>
+        <v>0.45</v>
       </c>
       <c r="AB476" s="2" t="n">
-        <v>-2.6</v>
+        <v>1.06</v>
       </c>
       <c r="AC476" s="2" t="n">
-        <v>-1.24</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>CVS US</t>
+          <t>COST US</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C477" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>915.74</v>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>2.62</v>
+        <v>0.15</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="G477" s="2" t="n">
-        <v>-20.52</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="H477" s="2" t="inlineStr"/>
       <c r="I477" s="2" t="inlineStr"/>
@@ -33156,11 +33164,9 @@
       <c r="O477" s="2" t="inlineStr"/>
       <c r="P477" s="2" t="inlineStr"/>
       <c r="Q477" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R477" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R477" s="2" t="inlineStr"/>
       <c r="S477" s="2" t="inlineStr"/>
       <c r="T477" s="2" t="inlineStr"/>
       <c r="U477" s="2" t="inlineStr"/>
@@ -33168,48 +33174,48 @@
       <c r="W477" s="2" t="inlineStr"/>
       <c r="X477" s="2" t="inlineStr"/>
       <c r="Y477" s="2" t="n">
-        <v>29.35</v>
+        <v>2.31</v>
       </c>
       <c r="Z477" s="2" t="n">
-        <v>6.16</v>
+        <v>-12.36</v>
       </c>
       <c r="AA477" s="2" t="n">
-        <v>2.61</v>
+        <v>-7.51</v>
       </c>
       <c r="AB477" s="2" t="n">
-        <v>3.68</v>
+        <v>-2.6</v>
       </c>
       <c r="AC477" s="2" t="n">
-        <v>0.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>DHR US</t>
+          <t>CVS US</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C478" s="2" t="n">
-        <v>207.66</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>-1.57</v>
+        <v>2.62</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G478" s="2" t="n">
-        <v>98.26000000000001</v>
+        <v>-20.52</v>
       </c>
       <c r="H478" s="2" t="inlineStr"/>
       <c r="I478" s="2" t="inlineStr"/>
@@ -33223,7 +33229,9 @@
       <c r="Q478" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R478" s="2" t="inlineStr"/>
+      <c r="R478" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S478" s="2" t="inlineStr"/>
       <c r="T478" s="2" t="inlineStr"/>
       <c r="U478" s="2" t="inlineStr"/>
@@ -33231,34 +33239,34 @@
       <c r="W478" s="2" t="inlineStr"/>
       <c r="X478" s="2" t="inlineStr"/>
       <c r="Y478" s="2" t="n">
-        <v>-5.5</v>
+        <v>29.35</v>
       </c>
       <c r="Z478" s="2" t="n">
-        <v>-6.83</v>
+        <v>6.16</v>
       </c>
       <c r="AA478" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>2.61</v>
       </c>
       <c r="AB478" s="2" t="n">
-        <v>-3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AC478" s="2" t="n">
-        <v>2.87</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>DIS US</t>
+          <t>DHR US</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C479" s="2" t="n">
-        <v>105.31</v>
+        <v>207.66</v>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
@@ -33266,13 +33274,13 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>-0.67</v>
+        <v>-1.57</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="G479" s="2" t="n">
-        <v>116.03</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="H479" s="2" t="inlineStr"/>
       <c r="I479" s="2" t="inlineStr"/>
@@ -33284,7 +33292,7 @@
       <c r="O479" s="2" t="inlineStr"/>
       <c r="P479" s="2" t="inlineStr"/>
       <c r="Q479" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R479" s="2" t="inlineStr"/>
       <c r="S479" s="2" t="inlineStr"/>
@@ -33294,34 +33302,34 @@
       <c r="W479" s="2" t="inlineStr"/>
       <c r="X479" s="2" t="inlineStr"/>
       <c r="Y479" s="2" t="n">
-        <v>-2.14</v>
+        <v>-5.5</v>
       </c>
       <c r="Z479" s="2" t="n">
-        <v>-8.66</v>
+        <v>-6.83</v>
       </c>
       <c r="AA479" s="2" t="n">
-        <v>1.96</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="AB479" s="2" t="n">
-        <v>-1.99</v>
+        <v>-3.6</v>
       </c>
       <c r="AC479" s="2" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>DLTR US</t>
+          <t>DIS US</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C480" s="2" t="n">
-        <v>131.42</v>
+        <v>105.31</v>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
@@ -33329,13 +33337,13 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.67</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="G480" s="2" t="n">
-        <v>64.8</v>
+        <v>116.03</v>
       </c>
       <c r="H480" s="2" t="inlineStr"/>
       <c r="I480" s="2" t="inlineStr"/>
@@ -33347,7 +33355,7 @@
       <c r="O480" s="2" t="inlineStr"/>
       <c r="P480" s="2" t="inlineStr"/>
       <c r="Q480" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R480" s="2" t="inlineStr"/>
       <c r="S480" s="2" t="inlineStr"/>
@@ -33357,48 +33365,48 @@
       <c r="W480" s="2" t="inlineStr"/>
       <c r="X480" s="2" t="inlineStr"/>
       <c r="Y480" s="2" t="n">
-        <v>28.78</v>
+        <v>-2.14</v>
       </c>
       <c r="Z480" s="2" t="n">
-        <v>6.13</v>
+        <v>-8.66</v>
       </c>
       <c r="AA480" s="2" t="n">
-        <v>11.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB480" s="2" t="n">
-        <v>2.41</v>
+        <v>-1.99</v>
       </c>
       <c r="AC480" s="2" t="n">
-        <v>1.21</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>DOC US</t>
+          <t>DLTR US</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Healthpeak Properties</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C481" s="2" t="n">
-        <v>20.65</v>
+        <v>131.42</v>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E481" s="2" t="n">
-        <v>3.21</v>
+        <v>0.01</v>
       </c>
       <c r="F481" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="G481" s="2" t="n">
-        <v>-0.5</v>
+        <v>64.8</v>
       </c>
       <c r="H481" s="2" t="inlineStr"/>
       <c r="I481" s="2" t="inlineStr"/>
@@ -33410,7 +33418,7 @@
       <c r="O481" s="2" t="inlineStr"/>
       <c r="P481" s="2" t="inlineStr"/>
       <c r="Q481" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R481" s="2" t="inlineStr"/>
       <c r="S481" s="2" t="inlineStr"/>
@@ -33420,34 +33428,34 @@
       <c r="W481" s="2" t="inlineStr"/>
       <c r="X481" s="2" t="inlineStr"/>
       <c r="Y481" s="2" t="n">
-        <v>30.5</v>
+        <v>28.78</v>
       </c>
       <c r="Z481" s="2" t="n">
-        <v>4.99</v>
+        <v>6.13</v>
       </c>
       <c r="AA481" s="2" t="n">
-        <v>10.42</v>
+        <v>11.9</v>
       </c>
       <c r="AB481" s="2" t="n">
-        <v>-1.77</v>
+        <v>2.41</v>
       </c>
       <c r="AC481" s="2" t="n">
-        <v>-3.43</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>DVA US</t>
+          <t>DOC US</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Healthpeak Properties</t>
         </is>
       </c>
       <c r="C482" s="2" t="n">
-        <v>183.99</v>
+        <v>20.65</v>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
@@ -33455,13 +33463,13 @@
         </is>
       </c>
       <c r="E482" s="2" t="n">
-        <v>5.46</v>
+        <v>3.21</v>
       </c>
       <c r="F482" s="2" t="n">
-        <v>1.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G482" s="2" t="n">
-        <v>-23.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H482" s="2" t="inlineStr"/>
       <c r="I482" s="2" t="inlineStr"/>
@@ -33483,48 +33491,48 @@
       <c r="W482" s="2" t="inlineStr"/>
       <c r="X482" s="2" t="inlineStr"/>
       <c r="Y482" s="2" t="n">
-        <v>46.27</v>
+        <v>30.5</v>
       </c>
       <c r="Z482" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="AA482" s="2" t="n">
-        <v>4.24</v>
+        <v>10.42</v>
       </c>
       <c r="AB482" s="2" t="n">
-        <v>1.64</v>
+        <v>-1.77</v>
       </c>
       <c r="AC482" s="2" t="n">
-        <v>-0.18</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>ECHO US</t>
+          <t>DVA US</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C483" s="2" t="n">
-        <v>89.8</v>
+        <v>183.99</v>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>-3.8</v>
+        <v>5.46</v>
       </c>
       <c r="F483" s="2" t="n">
-        <v>-17.9</v>
+        <v>1.7</v>
       </c>
       <c r="G483" s="2" t="n">
-        <v>17.06</v>
+        <v>-23.7</v>
       </c>
       <c r="H483" s="2" t="inlineStr"/>
       <c r="I483" s="2" t="inlineStr"/>
@@ -33536,7 +33544,7 @@
       <c r="O483" s="2" t="inlineStr"/>
       <c r="P483" s="2" t="inlineStr"/>
       <c r="Q483" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R483" s="2" t="inlineStr"/>
       <c r="S483" s="2" t="inlineStr"/>
@@ -33546,48 +33554,48 @@
       <c r="W483" s="2" t="inlineStr"/>
       <c r="X483" s="2" t="inlineStr"/>
       <c r="Y483" s="2" t="n">
-        <v>22.69</v>
+        <v>46.27</v>
       </c>
       <c r="Z483" s="2" t="n">
-        <v>-18.58</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AA483" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="AB483" s="2" t="n">
-        <v>2.43</v>
+        <v>1.64</v>
       </c>
       <c r="AC483" s="2" t="n">
-        <v>-2.29</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>ECL US</t>
+          <t>ECHO US</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C484" s="2" t="n">
-        <v>279.28</v>
+        <v>89.8</v>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E484" s="2" t="n">
-        <v>0.39</v>
+        <v>-3.8</v>
       </c>
       <c r="F484" s="2" t="n">
-        <v>2.1</v>
+        <v>-17.9</v>
       </c>
       <c r="G484" s="2" t="n">
-        <v>74.76000000000001</v>
+        <v>17.06</v>
       </c>
       <c r="H484" s="2" t="inlineStr"/>
       <c r="I484" s="2" t="inlineStr"/>
@@ -33599,7 +33607,7 @@
       <c r="O484" s="2" t="inlineStr"/>
       <c r="P484" s="2" t="inlineStr"/>
       <c r="Q484" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R484" s="2" t="inlineStr"/>
       <c r="S484" s="2" t="inlineStr"/>
@@ -33609,48 +33617,48 @@
       <c r="W484" s="2" t="inlineStr"/>
       <c r="X484" s="2" t="inlineStr"/>
       <c r="Y484" s="2" t="n">
-        <v>10.83</v>
+        <v>22.69</v>
       </c>
       <c r="Z484" s="2" t="n">
-        <v>-6.04</v>
+        <v>-18.58</v>
       </c>
       <c r="AA484" s="2" t="n">
-        <v>-4.89</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AB484" s="2" t="n">
-        <v>-2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AC484" s="2" t="n">
-        <v>-0.3</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ECL US</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C485" s="2" t="n">
-        <v>56.77</v>
+        <v>279.28</v>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E485" s="2" t="n">
-        <v>1.66</v>
+        <v>0.39</v>
       </c>
       <c r="F485" s="2" t="n">
-        <v>-19.6</v>
+        <v>2.1</v>
       </c>
       <c r="G485" s="2" t="n">
-        <v>2.13</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="H485" s="2" t="inlineStr"/>
       <c r="I485" s="2" t="inlineStr"/>
@@ -33672,48 +33680,48 @@
       <c r="W485" s="2" t="inlineStr"/>
       <c r="X485" s="2" t="inlineStr"/>
       <c r="Y485" s="2" t="n">
-        <v>-0.05</v>
+        <v>10.83</v>
       </c>
       <c r="Z485" s="2" t="n">
-        <v>-19.49</v>
+        <v>-6.04</v>
       </c>
       <c r="AA485" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-4.89</v>
       </c>
       <c r="AB485" s="2" t="n">
-        <v>-18.92</v>
+        <v>-2.31</v>
       </c>
       <c r="AC485" s="2" t="n">
-        <v>-16.9</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>ESS US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C486" s="2" t="n">
-        <v>278.61</v>
+        <v>56.77</v>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E486" s="2" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="F486" s="2" t="n">
-        <v>3.9</v>
+        <v>-19.6</v>
       </c>
       <c r="G486" s="2" t="n">
-        <v>3.29</v>
+        <v>2.13</v>
       </c>
       <c r="H486" s="2" t="inlineStr"/>
       <c r="I486" s="2" t="inlineStr"/>
@@ -33725,7 +33733,7 @@
       <c r="O486" s="2" t="inlineStr"/>
       <c r="P486" s="2" t="inlineStr"/>
       <c r="Q486" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R486" s="2" t="inlineStr"/>
       <c r="S486" s="2" t="inlineStr"/>
@@ -33735,48 +33743,48 @@
       <c r="W486" s="2" t="inlineStr"/>
       <c r="X486" s="2" t="inlineStr"/>
       <c r="Y486" s="2" t="n">
-        <v>15.46</v>
+        <v>-0.05</v>
       </c>
       <c r="Z486" s="2" t="n">
-        <v>-2.67</v>
+        <v>-19.49</v>
       </c>
       <c r="AA486" s="2" t="n">
-        <v>2.37</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AB486" s="2" t="n">
-        <v>-1.82</v>
+        <v>-18.92</v>
       </c>
       <c r="AC486" s="2" t="n">
-        <v>-2.35</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ESS US</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C487" s="2" t="n">
-        <v>107.27</v>
+        <v>278.61</v>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E487" s="2" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="F487" s="2" t="n">
-        <v>-1.2</v>
+        <v>3.9</v>
       </c>
       <c r="G487" s="2" t="n">
-        <v>-8.550000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="H487" s="2" t="inlineStr"/>
       <c r="I487" s="2" t="inlineStr"/>
@@ -33788,7 +33796,7 @@
       <c r="O487" s="2" t="inlineStr"/>
       <c r="P487" s="2" t="inlineStr"/>
       <c r="Q487" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R487" s="2" t="inlineStr"/>
       <c r="S487" s="2" t="inlineStr"/>
@@ -33798,48 +33806,48 @@
       <c r="W487" s="2" t="inlineStr"/>
       <c r="X487" s="2" t="inlineStr"/>
       <c r="Y487" s="2" t="n">
-        <v>16.6</v>
+        <v>15.46</v>
       </c>
       <c r="Z487" s="2" t="n">
-        <v>-3.72</v>
+        <v>-2.67</v>
       </c>
       <c r="AA487" s="2" t="n">
-        <v>7.91</v>
+        <v>2.37</v>
       </c>
       <c r="AB487" s="2" t="n">
-        <v>1.19</v>
+        <v>-1.82</v>
       </c>
       <c r="AC487" s="2" t="n">
-        <v>0.95</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>EXPE US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C488" s="2" t="n">
-        <v>298.04</v>
+        <v>107.27</v>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E488" s="2" t="n">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="F488" s="2" t="n">
-        <v>18</v>
+        <v>-1.2</v>
       </c>
       <c r="G488" s="2" t="n">
-        <v>101.92</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H488" s="2" t="inlineStr"/>
       <c r="I488" s="2" t="inlineStr"/>
@@ -33861,48 +33869,48 @@
       <c r="W488" s="2" t="inlineStr"/>
       <c r="X488" s="2" t="inlineStr"/>
       <c r="Y488" s="2" t="n">
-        <v>22.81</v>
+        <v>16.6</v>
       </c>
       <c r="Z488" s="2" t="n">
-        <v>8.69</v>
+        <v>-3.72</v>
       </c>
       <c r="AA488" s="2" t="n">
-        <v>20.99</v>
+        <v>7.91</v>
       </c>
       <c r="AB488" s="2" t="n">
-        <v>-12.03</v>
+        <v>1.19</v>
       </c>
       <c r="AC488" s="2" t="n">
-        <v>-6.36</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>FTV US</t>
+          <t>EXPE US</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C489" s="2" t="n">
-        <v>56.94</v>
+        <v>298.04</v>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E489" s="2" t="n">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
       <c r="F489" s="2" t="n">
-        <v>-3.9</v>
+        <v>18</v>
       </c>
       <c r="G489" s="2" t="n">
-        <v>6.83</v>
+        <v>101.92</v>
       </c>
       <c r="H489" s="2" t="inlineStr"/>
       <c r="I489" s="2" t="inlineStr"/>
@@ -33924,34 +33932,34 @@
       <c r="W489" s="2" t="inlineStr"/>
       <c r="X489" s="2" t="inlineStr"/>
       <c r="Y489" s="2" t="n">
-        <v>13.33</v>
+        <v>22.81</v>
       </c>
       <c r="Z489" s="2" t="n">
-        <v>-7.3</v>
+        <v>8.69</v>
       </c>
       <c r="AA489" s="2" t="n">
-        <v>-3.69</v>
+        <v>20.99</v>
       </c>
       <c r="AB489" s="2" t="n">
-        <v>-4.48</v>
+        <v>-12.03</v>
       </c>
       <c r="AC489" s="2" t="n">
-        <v>-7.48</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>HLT US</t>
+          <t>FTV US</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C490" s="2" t="n">
-        <v>311.18</v>
+        <v>56.94</v>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
@@ -33959,13 +33967,13 @@
         </is>
       </c>
       <c r="E490" s="2" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="F490" s="2" t="n">
-        <v>-3.1</v>
+        <v>-3.9</v>
       </c>
       <c r="G490" s="2" t="n">
-        <v>11.37</v>
+        <v>6.83</v>
       </c>
       <c r="H490" s="2" t="inlineStr"/>
       <c r="I490" s="2" t="inlineStr"/>
@@ -33987,56 +33995,52 @@
       <c r="W490" s="2" t="inlineStr"/>
       <c r="X490" s="2" t="inlineStr"/>
       <c r="Y490" s="2" t="n">
-        <v>17.86</v>
+        <v>13.33</v>
       </c>
       <c r="Z490" s="2" t="n">
-        <v>-6.07</v>
+        <v>-7.3</v>
       </c>
       <c r="AA490" s="2" t="n">
-        <v>4.46</v>
+        <v>-3.69</v>
       </c>
       <c r="AB490" s="2" t="n">
-        <v>-3.22</v>
+        <v>-4.48</v>
       </c>
       <c r="AC490" s="2" t="n">
-        <v>-1.37</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>HWM US</t>
+          <t>HLT US</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C491" s="2" t="n">
-        <v>259.27</v>
+        <v>311.18</v>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E491" s="2" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="F491" s="2" t="n">
-        <v>0.4</v>
+        <v>-3.1</v>
       </c>
       <c r="G491" s="2" t="n">
-        <v>4.33</v>
+        <v>11.37</v>
       </c>
       <c r="H491" s="2" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr"/>
-      <c r="J491" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="J491" s="2" t="inlineStr"/>
       <c r="K491" s="2" t="inlineStr"/>
       <c r="L491" s="2" t="inlineStr"/>
       <c r="M491" s="2" t="inlineStr"/>
@@ -34054,52 +34058,56 @@
       <c r="W491" s="2" t="inlineStr"/>
       <c r="X491" s="2" t="inlineStr"/>
       <c r="Y491" s="2" t="n">
-        <v>27.19</v>
+        <v>17.86</v>
       </c>
       <c r="Z491" s="2" t="n">
-        <v>1.19</v>
+        <v>-6.07</v>
       </c>
       <c r="AA491" s="2" t="n">
-        <v>5.3</v>
+        <v>4.46</v>
       </c>
       <c r="AB491" s="2" t="n">
-        <v>-2.64</v>
+        <v>-3.22</v>
       </c>
       <c r="AC491" s="2" t="n">
-        <v>-10.41</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>ICE US</t>
+          <t>HWM US</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C492" s="2" t="n">
-        <v>161.26</v>
+        <v>259.27</v>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E492" s="2" t="n">
-        <v>-0.9</v>
+        <v>2.96</v>
       </c>
       <c r="F492" s="2" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="G492" s="2" t="n">
-        <v>115.88</v>
+        <v>4.33</v>
       </c>
       <c r="H492" s="2" t="inlineStr"/>
       <c r="I492" s="2" t="inlineStr"/>
-      <c r="J492" s="2" t="inlineStr"/>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="K492" s="2" t="inlineStr"/>
       <c r="L492" s="2" t="inlineStr"/>
       <c r="M492" s="2" t="inlineStr"/>
@@ -34117,48 +34125,48 @@
       <c r="W492" s="2" t="inlineStr"/>
       <c r="X492" s="2" t="inlineStr"/>
       <c r="Y492" s="2" t="n">
-        <v>8.49</v>
+        <v>27.19</v>
       </c>
       <c r="Z492" s="2" t="n">
-        <v>-5.65</v>
+        <v>1.19</v>
       </c>
       <c r="AA492" s="2" t="n">
-        <v>-5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AB492" s="2" t="n">
-        <v>-0.21</v>
+        <v>-2.64</v>
       </c>
       <c r="AC492" s="2" t="n">
-        <v>9.02</v>
+        <v>-10.41</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>INTU US</t>
+          <t>ICE US</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C493" s="2" t="n">
-        <v>332.7</v>
+        <v>161.26</v>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E493" s="2" t="n">
-        <v>-7.71</v>
+        <v>-0.9</v>
       </c>
       <c r="F493" s="2" t="n">
-        <v>-7.3</v>
+        <v>6</v>
       </c>
       <c r="G493" s="2" t="n">
-        <v>115.64</v>
+        <v>115.88</v>
       </c>
       <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr"/>
@@ -34180,48 +34188,48 @@
       <c r="W493" s="2" t="inlineStr"/>
       <c r="X493" s="2" t="inlineStr"/>
       <c r="Y493" s="2" t="n">
-        <v>-91.27</v>
+        <v>8.49</v>
       </c>
       <c r="Z493" s="2" t="n">
-        <v>-36.75</v>
+        <v>-5.65</v>
       </c>
       <c r="AA493" s="2" t="n">
-        <v>-43.71</v>
+        <v>-5.45</v>
       </c>
       <c r="AB493" s="2" t="n">
-        <v>-3.77</v>
+        <v>-0.21</v>
       </c>
       <c r="AC493" s="2" t="n">
-        <v>5.82</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>INVH US</t>
+          <t>INTU US</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C494" s="2" t="n">
-        <v>28.39</v>
+        <v>332.7</v>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E494" s="2" t="n">
-        <v>1.6</v>
+        <v>-7.71</v>
       </c>
       <c r="F494" s="2" t="n">
-        <v>2</v>
+        <v>-7.3</v>
       </c>
       <c r="G494" s="2" t="n">
-        <v>-6.18</v>
+        <v>115.64</v>
       </c>
       <c r="H494" s="2" t="inlineStr"/>
       <c r="I494" s="2" t="inlineStr"/>
@@ -34243,48 +34251,48 @@
       <c r="W494" s="2" t="inlineStr"/>
       <c r="X494" s="2" t="inlineStr"/>
       <c r="Y494" s="2" t="n">
-        <v>6.03</v>
+        <v>-91.27</v>
       </c>
       <c r="Z494" s="2" t="n">
-        <v>-5.98</v>
+        <v>-36.75</v>
       </c>
       <c r="AA494" s="2" t="n">
-        <v>-1.11</v>
+        <v>-43.71</v>
       </c>
       <c r="AB494" s="2" t="n">
-        <v>-2.51</v>
+        <v>-3.77</v>
       </c>
       <c r="AC494" s="2" t="n">
-        <v>-4.67</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>IT US</t>
+          <t>INVH US</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C495" s="2" t="n">
-        <v>186.42</v>
+        <v>28.39</v>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E495" s="2" t="n">
-        <v>-3.54</v>
+        <v>1.6</v>
       </c>
       <c r="F495" s="2" t="n">
-        <v>18.1</v>
+        <v>2</v>
       </c>
       <c r="G495" s="2" t="n">
-        <v>115.12</v>
+        <v>-6.18</v>
       </c>
       <c r="H495" s="2" t="inlineStr"/>
       <c r="I495" s="2" t="inlineStr"/>
@@ -34306,48 +34314,48 @@
       <c r="W495" s="2" t="inlineStr"/>
       <c r="X495" s="2" t="inlineStr"/>
       <c r="Y495" s="2" t="n">
-        <v>-28.12</v>
+        <v>6.03</v>
       </c>
       <c r="Z495" s="2" t="n">
-        <v>-11.99</v>
+        <v>-5.98</v>
       </c>
       <c r="AA495" s="2" t="n">
-        <v>-21.13</v>
+        <v>-1.11</v>
       </c>
       <c r="AB495" s="2" t="n">
-        <v>-4.84</v>
+        <v>-2.51</v>
       </c>
       <c r="AC495" s="2" t="n">
-        <v>3.93</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>J US</t>
+          <t>IT US</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C496" s="2" t="n">
-        <v>146.23</v>
+        <v>186.42</v>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E496" s="2" t="n">
-        <v>1.09</v>
+        <v>-3.54</v>
       </c>
       <c r="F496" s="2" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="G496" s="2" t="n">
-        <v>101.58</v>
+        <v>115.12</v>
       </c>
       <c r="H496" s="2" t="inlineStr"/>
       <c r="I496" s="2" t="inlineStr"/>
@@ -34369,34 +34377,34 @@
       <c r="W496" s="2" t="inlineStr"/>
       <c r="X496" s="2" t="inlineStr"/>
       <c r="Y496" s="2" t="n">
-        <v>-4.56</v>
+        <v>-28.12</v>
       </c>
       <c r="Z496" s="2" t="n">
-        <v>-2.22</v>
+        <v>-11.99</v>
       </c>
       <c r="AA496" s="2" t="n">
-        <v>1.26</v>
+        <v>-21.13</v>
       </c>
       <c r="AB496" s="2" t="n">
-        <v>-3.62</v>
+        <v>-4.84</v>
       </c>
       <c r="AC496" s="2" t="n">
-        <v>2.85</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>KMB US</t>
+          <t>J US</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C497" s="2" t="n">
-        <v>104.96</v>
+        <v>146.23</v>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
@@ -34404,13 +34412,13 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="F497" s="2" t="n">
-        <v>3.4</v>
+        <v>11.8</v>
       </c>
       <c r="G497" s="2" t="n">
-        <v>0.93</v>
+        <v>101.58</v>
       </c>
       <c r="H497" s="2" t="inlineStr"/>
       <c r="I497" s="2" t="inlineStr"/>
@@ -34432,34 +34440,34 @@
       <c r="W497" s="2" t="inlineStr"/>
       <c r="X497" s="2" t="inlineStr"/>
       <c r="Y497" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>-4.56</v>
       </c>
       <c r="Z497" s="2" t="n">
-        <v>-7.28</v>
+        <v>-2.22</v>
       </c>
       <c r="AA497" s="2" t="n">
-        <v>-2.27</v>
+        <v>1.26</v>
       </c>
       <c r="AB497" s="2" t="n">
-        <v>-2.36</v>
+        <v>-3.62</v>
       </c>
       <c r="AC497" s="2" t="n">
-        <v>0.14</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>KVUE US</t>
+          <t>KMB US</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C498" s="2" t="n">
-        <v>18.74</v>
+        <v>104.96</v>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
@@ -34467,13 +34475,13 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="F498" s="2" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="G498" s="2" t="n">
-        <v>65.04000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="H498" s="2" t="inlineStr"/>
       <c r="I498" s="2" t="inlineStr"/>
@@ -34495,48 +34503,48 @@
       <c r="W498" s="2" t="inlineStr"/>
       <c r="X498" s="2" t="inlineStr"/>
       <c r="Y498" s="2" t="n">
-        <v>21.37</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Z498" s="2" t="n">
-        <v>-0.55</v>
+        <v>-7.28</v>
       </c>
       <c r="AA498" s="2" t="n">
-        <v>4.87</v>
+        <v>-2.27</v>
       </c>
       <c r="AB498" s="2" t="n">
-        <v>-1.89</v>
+        <v>-2.36</v>
       </c>
       <c r="AC498" s="2" t="n">
-        <v>1.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>LEN US</t>
+          <t>KVUE US</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C499" s="2" t="n">
-        <v>83.58</v>
+        <v>18.74</v>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E499" s="2" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="F499" s="2" t="n">
-        <v>-9.1</v>
+        <v>4.4</v>
       </c>
       <c r="G499" s="2" t="n">
-        <v>51.77</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H499" s="2" t="inlineStr"/>
       <c r="I499" s="2" t="inlineStr"/>
@@ -34548,7 +34556,7 @@
       <c r="O499" s="2" t="inlineStr"/>
       <c r="P499" s="2" t="inlineStr"/>
       <c r="Q499" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R499" s="2" t="inlineStr"/>
       <c r="S499" s="2" t="inlineStr"/>
@@ -34558,48 +34566,48 @@
       <c r="W499" s="2" t="inlineStr"/>
       <c r="X499" s="2" t="inlineStr"/>
       <c r="Y499" s="2" t="n">
-        <v>-47.09</v>
+        <v>21.37</v>
       </c>
       <c r="Z499" s="2" t="n">
-        <v>-26.5</v>
+        <v>-0.55</v>
       </c>
       <c r="AA499" s="2" t="n">
-        <v>-17.34</v>
+        <v>4.87</v>
       </c>
       <c r="AB499" s="2" t="n">
-        <v>-1.53</v>
+        <v>-1.89</v>
       </c>
       <c r="AC499" s="2" t="n">
-        <v>-0.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>LMT US</t>
+          <t>LEN US</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C500" s="2" t="n">
-        <v>525.28</v>
+        <v>83.58</v>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>0.34</v>
+        <v>-3.6</v>
       </c>
       <c r="F500" s="2" t="n">
-        <v>-7.4</v>
+        <v>-9.1</v>
       </c>
       <c r="G500" s="2" t="n">
-        <v>115.8</v>
+        <v>51.77</v>
       </c>
       <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr"/>
@@ -34611,7 +34619,7 @@
       <c r="O500" s="2" t="inlineStr"/>
       <c r="P500" s="2" t="inlineStr"/>
       <c r="Q500" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R500" s="2" t="inlineStr"/>
       <c r="S500" s="2" t="inlineStr"/>
@@ -34621,48 +34629,48 @@
       <c r="W500" s="2" t="inlineStr"/>
       <c r="X500" s="2" t="inlineStr"/>
       <c r="Y500" s="2" t="n">
-        <v>21.06</v>
+        <v>-47.09</v>
       </c>
       <c r="Z500" s="2" t="n">
-        <v>-10.3</v>
+        <v>-26.5</v>
       </c>
       <c r="AA500" s="2" t="n">
-        <v>-6.6</v>
+        <v>-17.34</v>
       </c>
       <c r="AB500" s="2" t="n">
-        <v>-6.12</v>
+        <v>-1.53</v>
       </c>
       <c r="AC500" s="2" t="n">
-        <v>-10.32</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>LVS US</t>
+          <t>LMT US</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C501" s="2" t="n">
-        <v>44.37</v>
+        <v>525.28</v>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E501" s="2" t="n">
-        <v>-3.44</v>
+        <v>0.34</v>
       </c>
       <c r="F501" s="2" t="n">
-        <v>-12.3</v>
+        <v>-7.4</v>
       </c>
       <c r="G501" s="2" t="n">
-        <v>53.43</v>
+        <v>115.8</v>
       </c>
       <c r="H501" s="2" t="inlineStr"/>
       <c r="I501" s="2" t="inlineStr"/>
@@ -34684,48 +34692,48 @@
       <c r="W501" s="2" t="inlineStr"/>
       <c r="X501" s="2" t="inlineStr"/>
       <c r="Y501" s="2" t="n">
-        <v>-49.35</v>
+        <v>21.06</v>
       </c>
       <c r="Z501" s="2" t="n">
-        <v>-25.16</v>
+        <v>-10.3</v>
       </c>
       <c r="AA501" s="2" t="n">
-        <v>-16.09</v>
+        <v>-6.6</v>
       </c>
       <c r="AB501" s="2" t="n">
-        <v>-0.65</v>
+        <v>-6.12</v>
       </c>
       <c r="AC501" s="2" t="n">
-        <v>-0.1</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>LYV US</t>
+          <t>LVS US</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C502" s="2" t="n">
-        <v>173.5</v>
+        <v>44.37</v>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E502" s="2" t="n">
-        <v>3.03</v>
+        <v>-3.44</v>
       </c>
       <c r="F502" s="2" t="n">
-        <v>3.8</v>
+        <v>-12.3</v>
       </c>
       <c r="G502" s="2" t="n">
-        <v>86.94</v>
+        <v>53.43</v>
       </c>
       <c r="H502" s="2" t="inlineStr"/>
       <c r="I502" s="2" t="inlineStr"/>
@@ -34747,48 +34755,48 @@
       <c r="W502" s="2" t="inlineStr"/>
       <c r="X502" s="2" t="inlineStr"/>
       <c r="Y502" s="2" t="n">
-        <v>32.65</v>
+        <v>-49.35</v>
       </c>
       <c r="Z502" s="2" t="n">
-        <v>-0.52</v>
+        <v>-25.16</v>
       </c>
       <c r="AA502" s="2" t="n">
-        <v>10.36</v>
+        <v>-16.09</v>
       </c>
       <c r="AB502" s="2" t="n">
-        <v>-4.55</v>
+        <v>-0.65</v>
       </c>
       <c r="AC502" s="2" t="n">
-        <v>-3.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>MAA US</t>
+          <t>LYV US</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C503" s="2" t="n">
-        <v>128.32</v>
+        <v>173.5</v>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>-0.08</v>
+        <v>3.03</v>
       </c>
       <c r="F503" s="2" t="n">
-        <v>-1.1</v>
+        <v>3.8</v>
       </c>
       <c r="G503" s="2" t="n">
-        <v>-10.82</v>
+        <v>86.94</v>
       </c>
       <c r="H503" s="2" t="inlineStr"/>
       <c r="I503" s="2" t="inlineStr"/>
@@ -34810,48 +34818,48 @@
       <c r="W503" s="2" t="inlineStr"/>
       <c r="X503" s="2" t="inlineStr"/>
       <c r="Y503" s="2" t="n">
-        <v>2.28</v>
+        <v>32.65</v>
       </c>
       <c r="Z503" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-0.52</v>
       </c>
       <c r="AA503" s="2" t="n">
-        <v>-5.27</v>
+        <v>10.36</v>
       </c>
       <c r="AB503" s="2" t="n">
-        <v>-0.55</v>
+        <v>-4.55</v>
       </c>
       <c r="AC503" s="2" t="n">
-        <v>-2.57</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>MDLZ US</t>
+          <t>MAA US</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C504" s="2" t="n">
-        <v>61.28</v>
+        <v>128.32</v>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>1.68</v>
+        <v>-0.08</v>
       </c>
       <c r="F504" s="2" t="n">
-        <v>2.5</v>
+        <v>-1.1</v>
       </c>
       <c r="G504" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>-10.82</v>
       </c>
       <c r="H504" s="2" t="inlineStr"/>
       <c r="I504" s="2" t="inlineStr"/>
@@ -34873,34 +34881,34 @@
       <c r="W504" s="2" t="inlineStr"/>
       <c r="X504" s="2" t="inlineStr"/>
       <c r="Y504" s="2" t="n">
-        <v>14.56</v>
+        <v>2.28</v>
       </c>
       <c r="Z504" s="2" t="n">
-        <v>-4.55</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AA504" s="2" t="n">
-        <v>0.62</v>
+        <v>-5.27</v>
       </c>
       <c r="AB504" s="2" t="n">
-        <v>-1.51</v>
+        <v>-0.55</v>
       </c>
       <c r="AC504" s="2" t="n">
-        <v>-0.51</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>MNST US</t>
+          <t>MDLZ US</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C505" s="2" t="n">
-        <v>43.82</v>
+        <v>61.28</v>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
@@ -34908,13 +34916,13 @@
         </is>
       </c>
       <c r="E505" s="2" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="F505" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G505" s="2" t="n">
-        <v>1.29</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H505" s="2" t="inlineStr"/>
       <c r="I505" s="2" t="inlineStr"/>
@@ -34926,7 +34934,7 @@
       <c r="O505" s="2" t="inlineStr"/>
       <c r="P505" s="2" t="inlineStr"/>
       <c r="Q505" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R505" s="2" t="inlineStr"/>
       <c r="S505" s="2" t="inlineStr"/>
@@ -34936,48 +34944,48 @@
       <c r="W505" s="2" t="inlineStr"/>
       <c r="X505" s="2" t="inlineStr"/>
       <c r="Y505" s="2" t="n">
-        <v>28.1</v>
+        <v>14.56</v>
       </c>
       <c r="Z505" s="2" t="n">
-        <v>0.08</v>
+        <v>-4.55</v>
       </c>
       <c r="AA505" s="2" t="n">
-        <v>5.38</v>
+        <v>0.62</v>
       </c>
       <c r="AB505" s="2" t="n">
-        <v>-7.39</v>
+        <v>-1.51</v>
       </c>
       <c r="AC505" s="2" t="n">
-        <v>-4.2</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>MOS US</t>
+          <t>MNST US</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>Mosaic Company (The)</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C506" s="2" t="n">
-        <v>25.85</v>
+        <v>43.82</v>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E506" s="2" t="n">
-        <v>-1.57</v>
+        <v>2.22</v>
       </c>
       <c r="F506" s="2" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="G506" s="2" t="n">
-        <v>95.56999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="H506" s="2" t="inlineStr"/>
       <c r="I506" s="2" t="inlineStr"/>
@@ -34989,7 +34997,7 @@
       <c r="O506" s="2" t="inlineStr"/>
       <c r="P506" s="2" t="inlineStr"/>
       <c r="Q506" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R506" s="2" t="inlineStr"/>
       <c r="S506" s="2" t="inlineStr"/>
@@ -34999,48 +35007,48 @@
       <c r="W506" s="2" t="inlineStr"/>
       <c r="X506" s="2" t="inlineStr"/>
       <c r="Y506" s="2" t="n">
-        <v>2.36</v>
+        <v>28.1</v>
       </c>
       <c r="Z506" s="2" t="n">
-        <v>-7.95</v>
+        <v>0.08</v>
       </c>
       <c r="AA506" s="2" t="n">
-        <v>-6.92</v>
+        <v>5.38</v>
       </c>
       <c r="AB506" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="AC506" s="2" t="n">
-        <v>13.5</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>MTD US</t>
+          <t>MOS US</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>Mosaic Company (The)</t>
         </is>
       </c>
       <c r="C507" s="2" t="n">
-        <v>1345.26</v>
+        <v>25.85</v>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E507" s="2" t="n">
-        <v>-0.44</v>
+        <v>-1.57</v>
       </c>
       <c r="F507" s="2" t="n">
-        <v>4.9</v>
+        <v>7.3</v>
       </c>
       <c r="G507" s="2" t="n">
-        <v>94.53</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="H507" s="2" t="inlineStr"/>
       <c r="I507" s="2" t="inlineStr"/>
@@ -35062,48 +35070,48 @@
       <c r="W507" s="2" t="inlineStr"/>
       <c r="X507" s="2" t="inlineStr"/>
       <c r="Y507" s="2" t="n">
-        <v>-4.86</v>
+        <v>2.36</v>
       </c>
       <c r="Z507" s="2" t="n">
-        <v>-7.42</v>
+        <v>-7.95</v>
       </c>
       <c r="AA507" s="2" t="n">
-        <v>-10.17</v>
+        <v>-6.92</v>
       </c>
       <c r="AB507" s="2" t="n">
-        <v>-3.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AC507" s="2" t="n">
-        <v>-4.54</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>NDAQ US</t>
+          <t>MTD US</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C508" s="2" t="n">
-        <v>96.88</v>
+        <v>1345.26</v>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E508" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.44</v>
       </c>
       <c r="F508" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="G508" s="2" t="n">
-        <v>107.47</v>
+        <v>94.53</v>
       </c>
       <c r="H508" s="2" t="inlineStr"/>
       <c r="I508" s="2" t="inlineStr"/>
@@ -35125,48 +35133,48 @@
       <c r="W508" s="2" t="inlineStr"/>
       <c r="X508" s="2" t="inlineStr"/>
       <c r="Y508" s="2" t="n">
-        <v>15.9</v>
+        <v>-4.86</v>
       </c>
       <c r="Z508" s="2" t="n">
-        <v>-1.46</v>
+        <v>-7.42</v>
       </c>
       <c r="AA508" s="2" t="n">
-        <v>-1.34</v>
+        <v>-10.17</v>
       </c>
       <c r="AB508" s="2" t="n">
-        <v>-2.29</v>
+        <v>-3.55</v>
       </c>
       <c r="AC508" s="2" t="n">
-        <v>3.95</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>NDSN US</t>
+          <t>NDAQ US</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C509" s="2" t="n">
-        <v>318.36</v>
+        <v>96.88</v>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E509" s="2" t="n">
-        <v>2.66</v>
+        <v>-0.11</v>
       </c>
       <c r="F509" s="2" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G509" s="2" t="n">
-        <v>92.69</v>
+        <v>107.47</v>
       </c>
       <c r="H509" s="2" t="inlineStr"/>
       <c r="I509" s="2" t="inlineStr"/>
@@ -35178,7 +35186,7 @@
       <c r="O509" s="2" t="inlineStr"/>
       <c r="P509" s="2" t="inlineStr"/>
       <c r="Q509" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R509" s="2" t="inlineStr"/>
       <c r="S509" s="2" t="inlineStr"/>
@@ -35188,48 +35196,48 @@
       <c r="W509" s="2" t="inlineStr"/>
       <c r="X509" s="2" t="inlineStr"/>
       <c r="Y509" s="2" t="n">
-        <v>41.03</v>
+        <v>15.9</v>
       </c>
       <c r="Z509" s="2" t="n">
-        <v>8.76</v>
+        <v>-1.46</v>
       </c>
       <c r="AA509" s="2" t="n">
-        <v>13.1</v>
+        <v>-1.34</v>
       </c>
       <c r="AB509" s="2" t="n">
-        <v>-2.64</v>
+        <v>-2.29</v>
       </c>
       <c r="AC509" s="2" t="n">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>PEP US</t>
+          <t>NDSN US</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C510" s="2" t="n">
-        <v>137.63</v>
+        <v>318.36</v>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E510" s="2" t="n">
-        <v>-0.1</v>
+        <v>2.66</v>
       </c>
       <c r="F510" s="2" t="n">
-        <v>-6.4</v>
+        <v>10.2</v>
       </c>
       <c r="G510" s="2" t="n">
-        <v>66.03</v>
+        <v>92.69</v>
       </c>
       <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr"/>
@@ -35251,34 +35259,34 @@
       <c r="W510" s="2" t="inlineStr"/>
       <c r="X510" s="2" t="inlineStr"/>
       <c r="Y510" s="2" t="n">
-        <v>-1.33</v>
+        <v>41.03</v>
       </c>
       <c r="Z510" s="2" t="n">
-        <v>-13.19</v>
+        <v>8.76</v>
       </c>
       <c r="AA510" s="2" t="n">
-        <v>-8.32</v>
+        <v>13.1</v>
       </c>
       <c r="AB510" s="2" t="n">
-        <v>-0.98</v>
+        <v>-2.64</v>
       </c>
       <c r="AC510" s="2" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>PLD US</t>
+          <t>PEP US</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C511" s="2" t="n">
-        <v>137.34</v>
+        <v>137.63</v>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
@@ -35286,13 +35294,13 @@
         </is>
       </c>
       <c r="E511" s="2" t="n">
-        <v>1.26</v>
+        <v>-0.1</v>
       </c>
       <c r="F511" s="2" t="n">
-        <v>-1.5</v>
+        <v>-6.4</v>
       </c>
       <c r="G511" s="2" t="n">
-        <v>4.24</v>
+        <v>66.03</v>
       </c>
       <c r="H511" s="2" t="inlineStr"/>
       <c r="I511" s="2" t="inlineStr"/>
@@ -35304,7 +35312,7 @@
       <c r="O511" s="2" t="inlineStr"/>
       <c r="P511" s="2" t="inlineStr"/>
       <c r="Q511" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R511" s="2" t="inlineStr"/>
       <c r="S511" s="2" t="inlineStr"/>
@@ -35314,48 +35322,48 @@
       <c r="W511" s="2" t="inlineStr"/>
       <c r="X511" s="2" t="inlineStr"/>
       <c r="Y511" s="2" t="n">
-        <v>16.2</v>
+        <v>-1.33</v>
       </c>
       <c r="Z511" s="2" t="n">
-        <v>-4.93</v>
+        <v>-13.19</v>
       </c>
       <c r="AA511" s="2" t="n">
-        <v>0.03</v>
+        <v>-8.32</v>
       </c>
       <c r="AB511" s="2" t="n">
-        <v>-2.53</v>
+        <v>-0.98</v>
       </c>
       <c r="AC511" s="2" t="n">
-        <v>-2.2</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>SLB US</t>
+          <t>PLD US</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C512" s="2" t="n">
-        <v>57.51</v>
+        <v>137.34</v>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E512" s="2" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="F512" s="2" t="n">
-        <v>12.2</v>
+        <v>-1.5</v>
       </c>
       <c r="G512" s="2" t="n">
-        <v>114.42</v>
+        <v>4.24</v>
       </c>
       <c r="H512" s="2" t="inlineStr"/>
       <c r="I512" s="2" t="inlineStr"/>
@@ -35377,48 +35385,48 @@
       <c r="W512" s="2" t="inlineStr"/>
       <c r="X512" s="2" t="inlineStr"/>
       <c r="Y512" s="2" t="n">
-        <v>60.3</v>
+        <v>16.2</v>
       </c>
       <c r="Z512" s="2" t="n">
-        <v>15.59</v>
+        <v>-4.93</v>
       </c>
       <c r="AA512" s="2" t="n">
-        <v>2.94</v>
+        <v>0.03</v>
       </c>
       <c r="AB512" s="2" t="n">
-        <v>0.1</v>
+        <v>-2.53</v>
       </c>
       <c r="AC512" s="2" t="n">
-        <v>12.64</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>SPGI US</t>
+          <t>SLB US</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C513" s="2" t="n">
-        <v>443.51</v>
+        <v>57.51</v>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E513" s="2" t="n">
-        <v>-2.37</v>
+        <v>2.35</v>
       </c>
       <c r="F513" s="2" t="n">
-        <v>8.4</v>
+        <v>12.2</v>
       </c>
       <c r="G513" s="2" t="n">
-        <v>47.27</v>
+        <v>114.42</v>
       </c>
       <c r="H513" s="2" t="inlineStr"/>
       <c r="I513" s="2" t="inlineStr"/>
@@ -35440,48 +35448,48 @@
       <c r="W513" s="2" t="inlineStr"/>
       <c r="X513" s="2" t="inlineStr"/>
       <c r="Y513" s="2" t="n">
-        <v>-7.47</v>
+        <v>60.3</v>
       </c>
       <c r="Z513" s="2" t="n">
-        <v>-7.56</v>
+        <v>15.59</v>
       </c>
       <c r="AA513" s="2" t="n">
-        <v>-7.23</v>
+        <v>2.94</v>
       </c>
       <c r="AB513" s="2" t="n">
-        <v>0.68</v>
+        <v>0.1</v>
       </c>
       <c r="AC513" s="2" t="n">
-        <v>10.58</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>SRE US</t>
+          <t>SPGI US</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C514" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>443.51</v>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E514" s="2" t="n">
-        <v>-0.29</v>
+        <v>-2.37</v>
       </c>
       <c r="F514" s="2" t="n">
-        <v>-7.7</v>
+        <v>8.4</v>
       </c>
       <c r="G514" s="2" t="n">
-        <v>-8.98</v>
+        <v>47.27</v>
       </c>
       <c r="H514" s="2" t="inlineStr"/>
       <c r="I514" s="2" t="inlineStr"/>
@@ -35493,7 +35501,7 @@
       <c r="O514" s="2" t="inlineStr"/>
       <c r="P514" s="2" t="inlineStr"/>
       <c r="Q514" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R514" s="2" t="inlineStr"/>
       <c r="S514" s="2" t="inlineStr"/>
@@ -35503,48 +35511,48 @@
       <c r="W514" s="2" t="inlineStr"/>
       <c r="X514" s="2" t="inlineStr"/>
       <c r="Y514" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="Z514" s="2" t="n">
-        <v>-14.58</v>
+        <v>-7.56</v>
       </c>
       <c r="AA514" s="2" t="n">
-        <v>-4.06</v>
+        <v>-7.23</v>
       </c>
       <c r="AB514" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.68</v>
       </c>
       <c r="AC514" s="2" t="n">
-        <v>1.3</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>STE US</t>
+          <t>SRE US</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C515" s="2" t="n">
-        <v>224.59</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.29</v>
       </c>
       <c r="F515" s="2" t="n">
-        <v>0.7</v>
+        <v>-7.7</v>
       </c>
       <c r="G515" s="2" t="n">
-        <v>97.2</v>
+        <v>-8.98</v>
       </c>
       <c r="H515" s="2" t="inlineStr"/>
       <c r="I515" s="2" t="inlineStr"/>
@@ -35556,7 +35564,7 @@
       <c r="O515" s="2" t="inlineStr"/>
       <c r="P515" s="2" t="inlineStr"/>
       <c r="Q515" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R515" s="2" t="inlineStr"/>
       <c r="S515" s="2" t="inlineStr"/>
@@ -35566,48 +35574,48 @@
       <c r="W515" s="2" t="inlineStr"/>
       <c r="X515" s="2" t="inlineStr"/>
       <c r="Y515" s="2" t="n">
-        <v>-17.34</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="Z515" s="2" t="n">
-        <v>-12.74</v>
+        <v>-14.58</v>
       </c>
       <c r="AA515" s="2" t="n">
-        <v>-15.37</v>
+        <v>-4.06</v>
       </c>
       <c r="AB515" s="2" t="n">
-        <v>-2.97</v>
+        <v>-0.15</v>
       </c>
       <c r="AC515" s="2" t="n">
-        <v>-2.69</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>STX US</t>
+          <t>STE US</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C516" s="2" t="n">
-        <v>849.28</v>
+        <v>224.59</v>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>11.03</v>
+        <v>-1.49</v>
       </c>
       <c r="F516" s="2" t="n">
-        <v>23</v>
+        <v>0.7</v>
       </c>
       <c r="G516" s="2" t="n">
-        <v>36.09</v>
+        <v>97.2</v>
       </c>
       <c r="H516" s="2" t="inlineStr"/>
       <c r="I516" s="2" t="inlineStr"/>
@@ -35619,7 +35627,7 @@
       <c r="O516" s="2" t="inlineStr"/>
       <c r="P516" s="2" t="inlineStr"/>
       <c r="Q516" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R516" s="2" t="inlineStr"/>
       <c r="S516" s="2" t="inlineStr"/>
@@ -35629,48 +35637,48 @@
       <c r="W516" s="2" t="inlineStr"/>
       <c r="X516" s="2" t="inlineStr"/>
       <c r="Y516" s="2" t="n">
-        <v>123.7</v>
+        <v>-17.34</v>
       </c>
       <c r="Z516" s="2" t="n">
-        <v>53.05</v>
+        <v>-12.74</v>
       </c>
       <c r="AA516" s="2" t="n">
-        <v>42.94</v>
+        <v>-15.37</v>
       </c>
       <c r="AB516" s="2" t="n">
-        <v>0.01</v>
+        <v>-2.97</v>
       </c>
       <c r="AC516" s="2" t="n">
-        <v>-7.93</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>STZ US</t>
+          <t>STX US</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="C517" s="2" t="n">
-        <v>128.18</v>
+        <v>849.28</v>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E517" s="2" t="n">
-        <v>-1.63</v>
+        <v>11.03</v>
       </c>
       <c r="F517" s="2" t="n">
-        <v>-10.9</v>
+        <v>23</v>
       </c>
       <c r="G517" s="2" t="n">
-        <v>13.78</v>
+        <v>36.09</v>
       </c>
       <c r="H517" s="2" t="inlineStr"/>
       <c r="I517" s="2" t="inlineStr"/>
@@ -35682,7 +35690,7 @@
       <c r="O517" s="2" t="inlineStr"/>
       <c r="P517" s="2" t="inlineStr"/>
       <c r="Q517" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R517" s="2" t="inlineStr"/>
       <c r="S517" s="2" t="inlineStr"/>
@@ -35692,34 +35700,34 @@
       <c r="W517" s="2" t="inlineStr"/>
       <c r="X517" s="2" t="inlineStr"/>
       <c r="Y517" s="2" t="n">
-        <v>1.71</v>
+        <v>123.7</v>
       </c>
       <c r="Z517" s="2" t="n">
-        <v>-17.37</v>
+        <v>53.05</v>
       </c>
       <c r="AA517" s="2" t="n">
-        <v>-12.71</v>
+        <v>42.94</v>
       </c>
       <c r="AB517" s="2" t="n">
-        <v>-1.19</v>
+        <v>0.01</v>
       </c>
       <c r="AC517" s="2" t="n">
-        <v>-1.96</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>SYK US</t>
+          <t>STZ US</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C518" s="2" t="n">
-        <v>303.13</v>
+        <v>128.18</v>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
@@ -35727,13 +35735,13 @@
         </is>
       </c>
       <c r="E518" s="2" t="n">
-        <v>-1.14</v>
+        <v>-1.63</v>
       </c>
       <c r="F518" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.9</v>
       </c>
       <c r="G518" s="2" t="n">
-        <v>8.09</v>
+        <v>13.78</v>
       </c>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr"/>
@@ -35755,48 +35763,48 @@
       <c r="W518" s="2" t="inlineStr"/>
       <c r="X518" s="2" t="inlineStr"/>
       <c r="Y518" s="2" t="n">
-        <v>-19.05</v>
+        <v>1.71</v>
       </c>
       <c r="Z518" s="2" t="n">
-        <v>-19.89</v>
+        <v>-17.37</v>
       </c>
       <c r="AA518" s="2" t="n">
-        <v>-22.34</v>
+        <v>-12.71</v>
       </c>
       <c r="AB518" s="2" t="n">
-        <v>-6.69</v>
+        <v>-1.19</v>
       </c>
       <c r="AC518" s="2" t="n">
-        <v>-6.7</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>SYY US</t>
+          <t>SYK US</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C519" s="2" t="n">
-        <v>80.05</v>
+        <v>303.13</v>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E519" s="2" t="n">
-        <v>1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="F519" s="2" t="n">
-        <v>-0.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G519" s="2" t="n">
-        <v>-1.92</v>
+        <v>8.09</v>
       </c>
       <c r="H519" s="2" t="inlineStr"/>
       <c r="I519" s="2" t="inlineStr"/>
@@ -35818,34 +35826,34 @@
       <c r="W519" s="2" t="inlineStr"/>
       <c r="X519" s="2" t="inlineStr"/>
       <c r="Y519" s="2" t="n">
-        <v>12.67</v>
+        <v>-19.05</v>
       </c>
       <c r="Z519" s="2" t="n">
-        <v>-6.81</v>
+        <v>-19.89</v>
       </c>
       <c r="AA519" s="2" t="n">
-        <v>-1.63</v>
+        <v>-22.34</v>
       </c>
       <c r="AB519" s="2" t="n">
-        <v>-2.01</v>
+        <v>-6.69</v>
       </c>
       <c r="AC519" s="2" t="n">
-        <v>-3.47</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>TPR US</t>
+          <t>SYY US</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C520" s="2" t="n">
-        <v>122.14</v>
+        <v>80.05</v>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
@@ -35853,13 +35861,13 @@
         </is>
       </c>
       <c r="E520" s="2" t="n">
-        <v>0.24</v>
+        <v>1.12</v>
       </c>
       <c r="F520" s="2" t="n">
-        <v>-14.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G520" s="2" t="n">
-        <v>-10.63</v>
+        <v>-1.92</v>
       </c>
       <c r="H520" s="2" t="inlineStr"/>
       <c r="I520" s="2" t="inlineStr"/>
@@ -35871,7 +35879,7 @@
       <c r="O520" s="2" t="inlineStr"/>
       <c r="P520" s="2" t="inlineStr"/>
       <c r="Q520" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R520" s="2" t="inlineStr"/>
       <c r="S520" s="2" t="inlineStr"/>
@@ -35881,19 +35889,19 @@
       <c r="W520" s="2" t="inlineStr"/>
       <c r="X520" s="2" t="inlineStr"/>
       <c r="Y520" s="2" t="n">
-        <v>20.89</v>
+        <v>12.67</v>
       </c>
       <c r="Z520" s="2" t="n">
-        <v>-15.2</v>
+        <v>-6.81</v>
       </c>
       <c r="AA520" s="2" t="n">
-        <v>-5.71</v>
+        <v>-1.63</v>
       </c>
       <c r="AB520" s="2" t="n">
-        <v>-2.09</v>
+        <v>-2.01</v>
       </c>
       <c r="AC520" s="2" t="n">
-        <v>-27.59</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="521">
@@ -36302,7 +36310,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-09-07 | 525 只</t>
+          <t>截至: 2026-09-08 | 525 只</t>
         </is>
       </c>
     </row>

--- a/US_Swing_Pattern.xlsx
+++ b/US_Swing_Pattern.xlsx
@@ -6134,7 +6134,7 @@
         <v>-3.2</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>13.96</v>
+        <v>13.93</v>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
@@ -10678,19 +10678,19 @@
       <c r="W147" s="2" t="inlineStr"/>
       <c r="X147" s="2" t="inlineStr"/>
       <c r="Y147" s="2" t="n">
-        <v>33.91</v>
+        <v>33.66</v>
       </c>
       <c r="Z147" s="2" t="n">
-        <v>10.45</v>
+        <v>10.46</v>
       </c>
       <c r="AA147" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB147" s="2" t="n">
         <v>2.5</v>
       </c>
       <c r="AC147" s="2" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="148">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="X187" s="2" t="inlineStr"/>
       <c r="Y187" s="2" t="n">
-        <v>22.69</v>
+        <v>22.7</v>
       </c>
       <c r="Z187" s="2" t="n">
         <v>11.89</v>
@@ -14994,7 +14994,7 @@
         <v>54.9</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>104.67</v>
+        <v>104.64</v>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
       <c r="I211" s="2" t="inlineStr"/>
@@ -17391,7 +17391,7 @@
         <v>-3.3</v>
       </c>
       <c r="G246" s="2" t="n">
-        <v>-11.85</v>
+        <v>-11.88</v>
       </c>
       <c r="H246" s="2" t="inlineStr"/>
       <c r="I246" s="2" t="inlineStr"/>
@@ -22868,7 +22868,7 @@
         <v>-4.1</v>
       </c>
       <c r="G325" s="2" t="n">
-        <v>-11.93</v>
+        <v>-11.91</v>
       </c>
       <c r="H325" s="2" t="inlineStr"/>
       <c r="I325" s="2" t="inlineStr"/>
@@ -23688,7 +23688,7 @@
         <v>-15.9</v>
       </c>
       <c r="G337" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="H337" s="2" t="inlineStr"/>
       <c r="I337" s="2" t="inlineStr"/>
@@ -23873,7 +23873,7 @@
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>116.165</v>
+        <v>116.17</v>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
@@ -23918,16 +23918,16 @@
         <v>47.56</v>
       </c>
       <c r="Z340" s="2" t="n">
-        <v>14.29</v>
+        <v>14.3</v>
       </c>
       <c r="AA340" s="2" t="n">
         <v>14.68</v>
       </c>
       <c r="AB340" s="2" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="AC340" s="2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="341">
@@ -26026,7 +26026,7 @@
         <v>-28.1</v>
       </c>
       <c r="G371" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>-12.1</v>
       </c>
       <c r="G498" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="H498" s="2" t="inlineStr"/>
       <c r="I498" s="2" t="inlineStr"/>
@@ -35029,7 +35029,7 @@
         <v>-10.4</v>
       </c>
       <c r="G504" s="2" t="n">
-        <v>-17.42</v>
+        <v>-17.48</v>
       </c>
       <c r="H504" s="2" t="inlineStr"/>
       <c r="I504" s="2" t="inlineStr"/>
@@ -35407,7 +35407,7 @@
         <v>-11.8</v>
       </c>
       <c r="G510" s="2" t="n">
-        <v>-4.82</v>
+        <v>-4.76</v>
       </c>
       <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr"/>
@@ -36100,7 +36100,7 @@
         <v>3.4</v>
       </c>
       <c r="G521" s="2" t="n">
-        <v>-14.06</v>
+        <v>-14.09</v>
       </c>
       <c r="H521" s="2" t="inlineStr"/>
       <c r="I521" s="2" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-09-12 | 526 只</t>
+          <t>截至: 2026-09-13 | 526 只</t>
         </is>
       </c>
     </row>
